--- a/coils_model/data/N7.xlsx
+++ b/coils_model/data/N7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86153\Desktop\diploma_project\coils_model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55209A1-39CE-40BD-8C2B-E6969CF003A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373650AB-356D-4B8F-9F26-4A35FF64C480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA28824C-3140-4F26-A808-D5842566BEDC}"/>
   </bookViews>
@@ -1111,16 +1111,16 @@
         <v>70</v>
       </c>
       <c r="G2" s="1">
-        <f>F2-(A2-1)*2*(C2+E2)</f>
-        <v>60.4</v>
+        <f>F2-(A2-1)*2*(C2+E2)-2*C2</f>
+        <v>59.6</v>
       </c>
       <c r="H2" s="1">
         <f>2.34*0.000001257*(0.5*A2^2*(F2+G2))/(1+2.73*(F2-G2)/(F2+G2))*1000</f>
-        <v>7.8245335835308536</v>
+        <v>7.6611175437338597</v>
       </c>
       <c r="I2" s="1">
         <f>0.0000000168*4*0.5*(F2+G2)/(0.00007*C2)</f>
-        <v>0.15648000000000001</v>
+        <v>0.15552000000000002</v>
       </c>
       <c r="J2">
         <v>6.78</v>
@@ -1156,16 +1156,16 @@
         <v>70</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G66" si="1">F3-(A3-1)*2*(C3+E3)</f>
-        <v>55.599999999999994</v>
+        <f t="shared" ref="G3:G66" si="1">F3-(A3-1)*2*(C3+E3)-2*C3</f>
+        <v>54.8</v>
       </c>
       <c r="H3" s="1">
         <f t="shared" ref="H3:H66" si="2">2.34*0.000001257*(0.5*A3^2*(F3+G3))/(1+2.73*(F3-G3)/(F3+G3))*1000</f>
-        <v>6.8935707875812531</v>
+        <v>6.7493909853658529</v>
       </c>
       <c r="I3" s="1">
         <f t="shared" ref="I3:I66" si="3">0.0000000168*4*0.5*(F3+G3)/(0.00007*C3)</f>
-        <v>0.15072000000000002</v>
+        <v>0.14976000000000003</v>
       </c>
       <c r="J3">
         <v>6.78</v>
@@ -1202,15 +1202,15 @@
       </c>
       <c r="G4" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>52.400000000000006</v>
       </c>
       <c r="H4" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.3341471070684321</v>
       </c>
       <c r="I4" s="1">
         <f t="shared" si="3"/>
-        <v>0.14784000000000003</v>
+        <v>0.14688000000000001</v>
       </c>
       <c r="J4">
         <v>6.78</v>
@@ -1247,15 +1247,15 @@
       </c>
       <c r="G5" s="1">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>56.8</v>
       </c>
       <c r="H5" s="1">
         <f t="shared" si="2"/>
-        <v>7.3444480159243586</v>
+        <v>7.1154980010218862</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" si="3"/>
-        <v>0.10240000000000002</v>
+        <v>0.10144000000000002</v>
       </c>
       <c r="J5">
         <v>6.78</v>
@@ -1292,15 +1292,15 @@
       </c>
       <c r="G6" s="1">
         <f t="shared" si="1"/>
-        <v>55.6</v>
+        <v>54.4</v>
       </c>
       <c r="H6" s="1">
         <f t="shared" si="2"/>
-        <v>6.8935707875812549</v>
+        <v>6.6784044525450925</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" si="3"/>
-        <v>0.10048000000000001</v>
+        <v>9.9520000000000011E-2</v>
       </c>
       <c r="J6">
         <v>6.78</v>
@@ -1337,15 +1337,15 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>52</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.267370270188148</v>
       </c>
       <c r="I7" s="1">
         <f t="shared" si="3"/>
-        <v>9.8560000000000023E-2</v>
+        <v>9.760000000000002E-2</v>
       </c>
       <c r="J7">
         <v>6.78</v>
@@ -1382,15 +1382,15 @@
       </c>
       <c r="G8" s="1">
         <f t="shared" si="1"/>
-        <v>50.8</v>
+        <v>49.599999999999994</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="2"/>
-        <v>6.0710398367263982</v>
+        <v>5.8805437124888744</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" si="3"/>
-        <v>9.6640000000000018E-2</v>
+        <v>9.5680000000000015E-2</v>
       </c>
       <c r="J8">
         <v>6.78</v>
@@ -1427,15 +1427,15 @@
       </c>
       <c r="G9" s="1">
         <f t="shared" si="1"/>
-        <v>55.599999999999994</v>
+        <v>53.999999999999993</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="2"/>
-        <v>6.8935707875812531</v>
+        <v>6.608141355916028</v>
       </c>
       <c r="I9" s="1">
         <f t="shared" si="3"/>
-        <v>7.536000000000001E-2</v>
+        <v>7.4400000000000008E-2</v>
       </c>
       <c r="J9">
         <v>6.78</v>
@@ -1472,15 +1472,15 @@
       </c>
       <c r="G10" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>51.6</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.201265482527119</v>
       </c>
       <c r="I10" s="1">
         <f t="shared" si="3"/>
-        <v>7.3920000000000013E-2</v>
+        <v>7.2960000000000011E-2</v>
       </c>
       <c r="J10">
         <v>6.78</v>
@@ -1517,15 +1517,15 @@
       </c>
       <c r="G11" s="1">
         <f t="shared" si="1"/>
-        <v>50.8</v>
+        <v>49.199999999999996</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" si="2"/>
-        <v>6.0710398367263982</v>
+        <v>5.8183058307482485</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" si="3"/>
-        <v>7.2480000000000017E-2</v>
+        <v>7.152E-2</v>
       </c>
       <c r="J11">
         <v>6.78</v>
@@ -1562,15 +1562,15 @@
       </c>
       <c r="G12" s="1">
         <f t="shared" si="1"/>
-        <v>48.4</v>
+        <v>46.8</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="2"/>
-        <v>5.6956770348292816</v>
+        <v>5.4576086475462979</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" si="3"/>
-        <v>7.1040000000000006E-2</v>
+        <v>7.0080000000000017E-2</v>
       </c>
       <c r="J12">
         <v>6.78</v>
@@ -1607,15 +1607,15 @@
       </c>
       <c r="G13" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>51.2</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.1358246572442106</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="3"/>
-        <v>5.9136000000000015E-2</v>
+        <v>5.8176000000000012E-2</v>
       </c>
       <c r="J13">
         <v>6.78</v>
@@ -1652,15 +1652,15 @@
       </c>
       <c r="G14" s="1">
         <f t="shared" si="1"/>
-        <v>50.8</v>
+        <v>48.8</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="2"/>
-        <v>6.0710398367263982</v>
+        <v>5.7566860162466886</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="3"/>
-        <v>5.7984000000000015E-2</v>
+        <v>5.7024000000000012E-2</v>
       </c>
       <c r="J14">
         <v>6.78</v>
@@ -1697,15 +1697,15 @@
       </c>
       <c r="G15" s="1">
         <f t="shared" si="1"/>
-        <v>48.4</v>
+        <v>46.4</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="2"/>
-        <v>5.6956770348292816</v>
+        <v>5.3995491800915785</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="3"/>
-        <v>5.6832000000000014E-2</v>
+        <v>5.5872000000000012E-2</v>
       </c>
       <c r="J15">
         <v>6.78</v>
@@ -1742,15 +1742,15 @@
       </c>
       <c r="G16" s="1">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="2"/>
-        <v>5.3420594279418241</v>
+        <v>5.0629326130392478</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="3"/>
-        <v>5.5680000000000014E-2</v>
+        <v>5.4720000000000012E-2</v>
       </c>
       <c r="J16">
         <v>6.78</v>
@@ -1787,15 +1787,15 @@
       </c>
       <c r="G17" s="1">
         <f t="shared" si="1"/>
-        <v>60.4</v>
+        <v>59.6</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="2"/>
-        <v>7.8245335835308536</v>
+        <v>7.6611175437338597</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="3"/>
-        <v>0.15648000000000001</v>
+        <v>0.15552000000000002</v>
       </c>
       <c r="J17">
         <v>6.78</v>
@@ -1832,15 +1832,15 @@
       </c>
       <c r="G18" s="1">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>57.2</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="2"/>
-        <v>7.3444480159243586</v>
+        <v>7.1910210404973354</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="3"/>
-        <v>0.15360000000000001</v>
+        <v>0.15264000000000003</v>
       </c>
       <c r="J18">
         <v>6.78</v>
@@ -1877,15 +1877,15 @@
       </c>
       <c r="G19" s="1">
         <f t="shared" si="1"/>
-        <v>55.599999999999994</v>
+        <v>54.8</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="2"/>
-        <v>6.8935707875812531</v>
+        <v>6.7493909853658529</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="3"/>
-        <v>0.15072000000000002</v>
+        <v>0.14976000000000003</v>
       </c>
       <c r="J19">
         <v>6.78</v>
@@ -1922,15 +1922,15 @@
       </c>
       <c r="G20" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>52.400000000000006</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.3341471070684321</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="3"/>
-        <v>0.14784000000000003</v>
+        <v>0.14688000000000001</v>
       </c>
       <c r="J20">
         <v>6.78</v>
@@ -1967,15 +1967,15 @@
       </c>
       <c r="G21" s="1">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>56.8</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="2"/>
-        <v>7.3444480159243586</v>
+        <v>7.1154980010218862</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="3"/>
-        <v>0.10240000000000002</v>
+        <v>0.10144000000000002</v>
       </c>
       <c r="J21">
         <v>6.78</v>
@@ -2012,15 +2012,15 @@
       </c>
       <c r="G22" s="1">
         <f t="shared" si="1"/>
-        <v>55.6</v>
+        <v>54.4</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="2"/>
-        <v>6.8935707875812549</v>
+        <v>6.6784044525450925</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="3"/>
-        <v>0.10048000000000001</v>
+        <v>9.9520000000000011E-2</v>
       </c>
       <c r="J22">
         <v>6.78</v>
@@ -2057,15 +2057,15 @@
       </c>
       <c r="G23" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>52</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.267370270188148</v>
       </c>
       <c r="I23" s="1">
         <f t="shared" si="3"/>
-        <v>9.8560000000000023E-2</v>
+        <v>9.760000000000002E-2</v>
       </c>
       <c r="J23">
         <v>6.78</v>
@@ -2102,15 +2102,15 @@
       </c>
       <c r="G24" s="1">
         <f t="shared" si="1"/>
-        <v>50.8</v>
+        <v>49.599999999999994</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" si="2"/>
-        <v>6.0710398367263982</v>
+        <v>5.8805437124888744</v>
       </c>
       <c r="I24" s="1">
         <f t="shared" si="3"/>
-        <v>9.6640000000000018E-2</v>
+        <v>9.5680000000000015E-2</v>
       </c>
       <c r="J24">
         <v>6.78</v>
@@ -2147,15 +2147,15 @@
       </c>
       <c r="G25" s="1">
         <f t="shared" si="1"/>
-        <v>55.599999999999994</v>
+        <v>53.999999999999993</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" si="2"/>
-        <v>6.8935707875812531</v>
+        <v>6.608141355916028</v>
       </c>
       <c r="I25" s="1">
         <f t="shared" si="3"/>
-        <v>7.536000000000001E-2</v>
+        <v>7.4400000000000008E-2</v>
       </c>
       <c r="J25">
         <v>6.78</v>
@@ -2192,15 +2192,15 @@
       </c>
       <c r="G26" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>51.6</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.201265482527119</v>
       </c>
       <c r="I26" s="1">
         <f t="shared" si="3"/>
-        <v>7.3920000000000013E-2</v>
+        <v>7.2960000000000011E-2</v>
       </c>
       <c r="J26">
         <v>6.78</v>
@@ -2237,15 +2237,15 @@
       </c>
       <c r="G27" s="1">
         <f t="shared" si="1"/>
-        <v>50.8</v>
+        <v>49.199999999999996</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" si="2"/>
-        <v>6.0710398367263982</v>
+        <v>5.8183058307482485</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" si="3"/>
-        <v>7.2480000000000017E-2</v>
+        <v>7.152E-2</v>
       </c>
       <c r="J27">
         <v>6.78</v>
@@ -2282,15 +2282,15 @@
       </c>
       <c r="G28" s="1">
         <f t="shared" si="1"/>
-        <v>48.4</v>
+        <v>46.8</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" si="2"/>
-        <v>5.6956770348292816</v>
+        <v>5.4576086475462979</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" si="3"/>
-        <v>7.1040000000000006E-2</v>
+        <v>7.0080000000000017E-2</v>
       </c>
       <c r="J28">
         <v>6.78</v>
@@ -2327,15 +2327,15 @@
       </c>
       <c r="G29" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>51.2</v>
       </c>
       <c r="H29" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.1358246572442106</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" si="3"/>
-        <v>5.9136000000000015E-2</v>
+        <v>5.8176000000000012E-2</v>
       </c>
       <c r="J29">
         <v>6.78</v>
@@ -2372,15 +2372,15 @@
       </c>
       <c r="G30" s="1">
         <f t="shared" si="1"/>
-        <v>50.8</v>
+        <v>48.8</v>
       </c>
       <c r="H30" s="1">
         <f t="shared" si="2"/>
-        <v>6.0710398367263982</v>
+        <v>5.7566860162466886</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" si="3"/>
-        <v>5.7984000000000015E-2</v>
+        <v>5.7024000000000012E-2</v>
       </c>
       <c r="J30">
         <v>6.78</v>
@@ -2417,15 +2417,15 @@
       </c>
       <c r="G31" s="1">
         <f t="shared" si="1"/>
-        <v>48.4</v>
+        <v>46.4</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" si="2"/>
-        <v>5.6956770348292816</v>
+        <v>5.3995491800915785</v>
       </c>
       <c r="I31" s="1">
         <f t="shared" si="3"/>
-        <v>5.6832000000000014E-2</v>
+        <v>5.5872000000000012E-2</v>
       </c>
       <c r="J31">
         <v>6.78</v>
@@ -2462,15 +2462,15 @@
       </c>
       <c r="G32" s="1">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H32" s="1">
         <f t="shared" si="2"/>
-        <v>5.3420594279418241</v>
+        <v>5.0629326130392478</v>
       </c>
       <c r="I32" s="1">
         <f t="shared" si="3"/>
-        <v>5.5680000000000014E-2</v>
+        <v>5.4720000000000012E-2</v>
       </c>
       <c r="J32">
         <v>6.78</v>
@@ -2507,15 +2507,15 @@
       </c>
       <c r="G33" s="1">
         <f t="shared" si="1"/>
-        <v>60.4</v>
+        <v>59.6</v>
       </c>
       <c r="H33" s="1">
         <f t="shared" si="2"/>
-        <v>7.8245335835308536</v>
+        <v>7.6611175437338597</v>
       </c>
       <c r="I33" s="1">
         <f t="shared" si="3"/>
-        <v>0.15648000000000001</v>
+        <v>0.15552000000000002</v>
       </c>
       <c r="J33">
         <v>6.78</v>
@@ -2552,15 +2552,15 @@
       </c>
       <c r="G34" s="1">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>57.2</v>
       </c>
       <c r="H34" s="1">
         <f t="shared" si="2"/>
-        <v>7.3444480159243586</v>
+        <v>7.1910210404973354</v>
       </c>
       <c r="I34" s="1">
         <f t="shared" si="3"/>
-        <v>0.15360000000000001</v>
+        <v>0.15264000000000003</v>
       </c>
       <c r="J34">
         <v>6.78</v>
@@ -2597,15 +2597,15 @@
       </c>
       <c r="G35" s="1">
         <f t="shared" si="1"/>
-        <v>55.599999999999994</v>
+        <v>54.8</v>
       </c>
       <c r="H35" s="1">
         <f t="shared" si="2"/>
-        <v>6.8935707875812531</v>
+        <v>6.7493909853658529</v>
       </c>
       <c r="I35" s="1">
         <f t="shared" si="3"/>
-        <v>0.15072000000000002</v>
+        <v>0.14976000000000003</v>
       </c>
       <c r="J35">
         <v>6.78</v>
@@ -2642,15 +2642,15 @@
       </c>
       <c r="G36" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>52.400000000000006</v>
       </c>
       <c r="H36" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.3341471070684321</v>
       </c>
       <c r="I36" s="1">
         <f t="shared" si="3"/>
-        <v>0.14784000000000003</v>
+        <v>0.14688000000000001</v>
       </c>
       <c r="J36">
         <v>6.78</v>
@@ -2687,15 +2687,15 @@
       </c>
       <c r="G37" s="1">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>56.8</v>
       </c>
       <c r="H37" s="1">
         <f t="shared" si="2"/>
-        <v>7.3444480159243586</v>
+        <v>7.1154980010218862</v>
       </c>
       <c r="I37" s="1">
         <f t="shared" si="3"/>
-        <v>0.10240000000000002</v>
+        <v>0.10144000000000002</v>
       </c>
       <c r="J37">
         <v>6.78</v>
@@ -2732,15 +2732,15 @@
       </c>
       <c r="G38" s="1">
         <f t="shared" si="1"/>
-        <v>55.6</v>
+        <v>54.4</v>
       </c>
       <c r="H38" s="1">
         <f t="shared" si="2"/>
-        <v>6.8935707875812549</v>
+        <v>6.6784044525450925</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" si="3"/>
-        <v>0.10048000000000001</v>
+        <v>9.9520000000000011E-2</v>
       </c>
       <c r="J38">
         <v>6.78</v>
@@ -2777,15 +2777,15 @@
       </c>
       <c r="G39" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>52</v>
       </c>
       <c r="H39" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.267370270188148</v>
       </c>
       <c r="I39" s="1">
         <f t="shared" si="3"/>
-        <v>9.8560000000000023E-2</v>
+        <v>9.760000000000002E-2</v>
       </c>
       <c r="J39">
         <v>6.78</v>
@@ -2822,15 +2822,15 @@
       </c>
       <c r="G40" s="1">
         <f t="shared" si="1"/>
-        <v>50.8</v>
+        <v>49.599999999999994</v>
       </c>
       <c r="H40" s="1">
         <f t="shared" si="2"/>
-        <v>6.0710398367263982</v>
+        <v>5.8805437124888744</v>
       </c>
       <c r="I40" s="1">
         <f t="shared" si="3"/>
-        <v>9.6640000000000018E-2</v>
+        <v>9.5680000000000015E-2</v>
       </c>
       <c r="J40">
         <v>6.78</v>
@@ -2867,15 +2867,15 @@
       </c>
       <c r="G41" s="1">
         <f t="shared" si="1"/>
-        <v>55.599999999999994</v>
+        <v>53.999999999999993</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" si="2"/>
-        <v>6.8935707875812531</v>
+        <v>6.608141355916028</v>
       </c>
       <c r="I41" s="1">
         <f t="shared" si="3"/>
-        <v>7.536000000000001E-2</v>
+        <v>7.4400000000000008E-2</v>
       </c>
       <c r="J41">
         <v>6.78</v>
@@ -2912,15 +2912,15 @@
       </c>
       <c r="G42" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>51.6</v>
       </c>
       <c r="H42" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.201265482527119</v>
       </c>
       <c r="I42" s="1">
         <f t="shared" si="3"/>
-        <v>7.3920000000000013E-2</v>
+        <v>7.2960000000000011E-2</v>
       </c>
       <c r="J42">
         <v>6.78</v>
@@ -2957,15 +2957,15 @@
       </c>
       <c r="G43" s="1">
         <f t="shared" si="1"/>
-        <v>50.8</v>
+        <v>49.199999999999996</v>
       </c>
       <c r="H43" s="1">
         <f t="shared" si="2"/>
-        <v>6.0710398367263982</v>
+        <v>5.8183058307482485</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="3"/>
-        <v>7.2480000000000017E-2</v>
+        <v>7.152E-2</v>
       </c>
       <c r="J43">
         <v>6.78</v>
@@ -3002,15 +3002,15 @@
       </c>
       <c r="G44" s="1">
         <f t="shared" si="1"/>
-        <v>48.4</v>
+        <v>46.8</v>
       </c>
       <c r="H44" s="1">
         <f t="shared" si="2"/>
-        <v>5.6956770348292816</v>
+        <v>5.4576086475462979</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" si="3"/>
-        <v>7.1040000000000006E-2</v>
+        <v>7.0080000000000017E-2</v>
       </c>
       <c r="J44">
         <v>6.78</v>
@@ -3047,15 +3047,15 @@
       </c>
       <c r="G45" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>51.2</v>
       </c>
       <c r="H45" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.1358246572442106</v>
       </c>
       <c r="I45" s="1">
         <f t="shared" si="3"/>
-        <v>5.9136000000000015E-2</v>
+        <v>5.8176000000000012E-2</v>
       </c>
       <c r="J45">
         <v>6.78</v>
@@ -3092,15 +3092,15 @@
       </c>
       <c r="G46" s="1">
         <f t="shared" si="1"/>
-        <v>50.8</v>
+        <v>48.8</v>
       </c>
       <c r="H46" s="1">
         <f t="shared" si="2"/>
-        <v>6.0710398367263982</v>
+        <v>5.7566860162466886</v>
       </c>
       <c r="I46" s="1">
         <f t="shared" si="3"/>
-        <v>5.7984000000000015E-2</v>
+        <v>5.7024000000000012E-2</v>
       </c>
       <c r="J46">
         <v>6.78</v>
@@ -3137,15 +3137,15 @@
       </c>
       <c r="G47" s="1">
         <f t="shared" si="1"/>
-        <v>48.4</v>
+        <v>46.4</v>
       </c>
       <c r="H47" s="1">
         <f t="shared" si="2"/>
-        <v>5.6956770348292816</v>
+        <v>5.3995491800915785</v>
       </c>
       <c r="I47" s="1">
         <f t="shared" si="3"/>
-        <v>5.6832000000000014E-2</v>
+        <v>5.5872000000000012E-2</v>
       </c>
       <c r="J47">
         <v>6.78</v>
@@ -3182,15 +3182,15 @@
       </c>
       <c r="G48" s="1">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H48" s="1">
         <f t="shared" si="2"/>
-        <v>5.3420594279418241</v>
+        <v>5.0629326130392478</v>
       </c>
       <c r="I48" s="1">
         <f t="shared" si="3"/>
-        <v>5.5680000000000014E-2</v>
+        <v>5.4720000000000012E-2</v>
       </c>
       <c r="J48">
         <v>6.78</v>
@@ -3227,15 +3227,15 @@
       </c>
       <c r="G49" s="1">
         <f t="shared" si="1"/>
-        <v>60.4</v>
+        <v>59.6</v>
       </c>
       <c r="H49" s="1">
         <f t="shared" si="2"/>
-        <v>7.8245335835308536</v>
+        <v>7.6611175437338597</v>
       </c>
       <c r="I49" s="1">
         <f t="shared" si="3"/>
-        <v>0.15648000000000001</v>
+        <v>0.15552000000000002</v>
       </c>
       <c r="J49">
         <v>6.78</v>
@@ -3272,15 +3272,15 @@
       </c>
       <c r="G50" s="1">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>57.2</v>
       </c>
       <c r="H50" s="1">
         <f t="shared" si="2"/>
-        <v>7.3444480159243586</v>
+        <v>7.1910210404973354</v>
       </c>
       <c r="I50" s="1">
         <f t="shared" si="3"/>
-        <v>0.15360000000000001</v>
+        <v>0.15264000000000003</v>
       </c>
       <c r="J50">
         <v>6.78</v>
@@ -3317,15 +3317,15 @@
       </c>
       <c r="G51" s="1">
         <f t="shared" si="1"/>
-        <v>55.599999999999994</v>
+        <v>54.8</v>
       </c>
       <c r="H51" s="1">
         <f t="shared" si="2"/>
-        <v>6.8935707875812531</v>
+        <v>6.7493909853658529</v>
       </c>
       <c r="I51" s="1">
         <f t="shared" si="3"/>
-        <v>0.15072000000000002</v>
+        <v>0.14976000000000003</v>
       </c>
       <c r="J51">
         <v>6.78</v>
@@ -3362,15 +3362,15 @@
       </c>
       <c r="G52" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>52.400000000000006</v>
       </c>
       <c r="H52" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.3341471070684321</v>
       </c>
       <c r="I52" s="1">
         <f t="shared" si="3"/>
-        <v>0.14784000000000003</v>
+        <v>0.14688000000000001</v>
       </c>
       <c r="J52">
         <v>6.78</v>
@@ -3407,15 +3407,15 @@
       </c>
       <c r="G53" s="1">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>56.8</v>
       </c>
       <c r="H53" s="1">
         <f t="shared" si="2"/>
-        <v>7.3444480159243586</v>
+        <v>7.1154980010218862</v>
       </c>
       <c r="I53" s="1">
         <f t="shared" si="3"/>
-        <v>0.10240000000000002</v>
+        <v>0.10144000000000002</v>
       </c>
       <c r="J53">
         <v>6.78</v>
@@ -3452,15 +3452,15 @@
       </c>
       <c r="G54" s="1">
         <f t="shared" si="1"/>
-        <v>55.6</v>
+        <v>54.4</v>
       </c>
       <c r="H54" s="1">
         <f t="shared" si="2"/>
-        <v>6.8935707875812549</v>
+        <v>6.6784044525450925</v>
       </c>
       <c r="I54" s="1">
         <f t="shared" si="3"/>
-        <v>0.10048000000000001</v>
+        <v>9.9520000000000011E-2</v>
       </c>
       <c r="J54">
         <v>6.78</v>
@@ -3497,15 +3497,15 @@
       </c>
       <c r="G55" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>52</v>
       </c>
       <c r="H55" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.267370270188148</v>
       </c>
       <c r="I55" s="1">
         <f t="shared" si="3"/>
-        <v>9.8560000000000023E-2</v>
+        <v>9.760000000000002E-2</v>
       </c>
       <c r="J55">
         <v>6.78</v>
@@ -3542,15 +3542,15 @@
       </c>
       <c r="G56" s="1">
         <f t="shared" si="1"/>
-        <v>50.8</v>
+        <v>49.599999999999994</v>
       </c>
       <c r="H56" s="1">
         <f t="shared" si="2"/>
-        <v>6.0710398367263982</v>
+        <v>5.8805437124888744</v>
       </c>
       <c r="I56" s="1">
         <f t="shared" si="3"/>
-        <v>9.6640000000000018E-2</v>
+        <v>9.5680000000000015E-2</v>
       </c>
       <c r="J56">
         <v>6.78</v>
@@ -3587,15 +3587,15 @@
       </c>
       <c r="G57" s="1">
         <f t="shared" si="1"/>
-        <v>55.599999999999994</v>
+        <v>53.999999999999993</v>
       </c>
       <c r="H57" s="1">
         <f t="shared" si="2"/>
-        <v>6.8935707875812531</v>
+        <v>6.608141355916028</v>
       </c>
       <c r="I57" s="1">
         <f t="shared" si="3"/>
-        <v>7.536000000000001E-2</v>
+        <v>7.4400000000000008E-2</v>
       </c>
       <c r="J57">
         <v>6.78</v>
@@ -3632,15 +3632,15 @@
       </c>
       <c r="G58" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>51.6</v>
       </c>
       <c r="H58" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.201265482527119</v>
       </c>
       <c r="I58" s="1">
         <f t="shared" si="3"/>
-        <v>7.3920000000000013E-2</v>
+        <v>7.2960000000000011E-2</v>
       </c>
       <c r="J58">
         <v>6.78</v>
@@ -3677,15 +3677,15 @@
       </c>
       <c r="G59" s="1">
         <f t="shared" si="1"/>
-        <v>50.8</v>
+        <v>49.199999999999996</v>
       </c>
       <c r="H59" s="1">
         <f t="shared" si="2"/>
-        <v>6.0710398367263982</v>
+        <v>5.8183058307482485</v>
       </c>
       <c r="I59" s="1">
         <f t="shared" si="3"/>
-        <v>7.2480000000000017E-2</v>
+        <v>7.152E-2</v>
       </c>
       <c r="J59">
         <v>6.78</v>
@@ -3722,15 +3722,15 @@
       </c>
       <c r="G60" s="1">
         <f t="shared" si="1"/>
-        <v>48.4</v>
+        <v>46.8</v>
       </c>
       <c r="H60" s="1">
         <f t="shared" si="2"/>
-        <v>5.6956770348292816</v>
+        <v>5.4576086475462979</v>
       </c>
       <c r="I60" s="1">
         <f t="shared" si="3"/>
-        <v>7.1040000000000006E-2</v>
+        <v>7.0080000000000017E-2</v>
       </c>
       <c r="J60">
         <v>6.78</v>
@@ -3767,15 +3767,15 @@
       </c>
       <c r="G61" s="1">
         <f t="shared" si="1"/>
-        <v>53.2</v>
+        <v>51.2</v>
       </c>
       <c r="H61" s="1">
         <f t="shared" si="2"/>
-        <v>6.4697499378602199</v>
+        <v>6.1358246572442106</v>
       </c>
       <c r="I61" s="1">
         <f t="shared" si="3"/>
-        <v>5.9136000000000015E-2</v>
+        <v>5.8176000000000012E-2</v>
       </c>
       <c r="J61">
         <v>6.78</v>
@@ -3812,15 +3812,15 @@
       </c>
       <c r="G62" s="1">
         <f t="shared" si="1"/>
-        <v>50.8</v>
+        <v>48.8</v>
       </c>
       <c r="H62" s="1">
         <f t="shared" si="2"/>
-        <v>6.0710398367263982</v>
+        <v>5.7566860162466886</v>
       </c>
       <c r="I62" s="1">
         <f t="shared" si="3"/>
-        <v>5.7984000000000015E-2</v>
+        <v>5.7024000000000012E-2</v>
       </c>
       <c r="J62">
         <v>6.78</v>
@@ -3857,15 +3857,15 @@
       </c>
       <c r="G63" s="1">
         <f t="shared" si="1"/>
-        <v>48.4</v>
+        <v>46.4</v>
       </c>
       <c r="H63" s="1">
         <f t="shared" si="2"/>
-        <v>5.6956770348292816</v>
+        <v>5.3995491800915785</v>
       </c>
       <c r="I63" s="1">
         <f t="shared" si="3"/>
-        <v>5.6832000000000014E-2</v>
+        <v>5.5872000000000012E-2</v>
       </c>
       <c r="J63">
         <v>6.78</v>
@@ -3902,15 +3902,15 @@
       </c>
       <c r="G64" s="1">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H64" s="1">
         <f t="shared" si="2"/>
-        <v>5.3420594279418241</v>
+        <v>5.0629326130392478</v>
       </c>
       <c r="I64" s="1">
         <f t="shared" si="3"/>
-        <v>5.5680000000000014E-2</v>
+        <v>5.4720000000000012E-2</v>
       </c>
       <c r="J64">
         <v>6.78</v>
@@ -3947,15 +3947,15 @@
       </c>
       <c r="G65" s="1">
         <f t="shared" si="1"/>
-        <v>60.4</v>
+        <v>59.6</v>
       </c>
       <c r="H65" s="1">
         <f t="shared" si="2"/>
-        <v>7.8245335835308536</v>
+        <v>7.6611175437338597</v>
       </c>
       <c r="I65" s="1">
         <f t="shared" si="3"/>
-        <v>0.15648000000000001</v>
+        <v>0.15552000000000002</v>
       </c>
       <c r="J65">
         <v>6.78</v>
@@ -3992,15 +3992,15 @@
       </c>
       <c r="G66" s="1">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>57.2</v>
       </c>
       <c r="H66" s="1">
         <f t="shared" si="2"/>
-        <v>7.3444480159243586</v>
+        <v>7.1910210404973354</v>
       </c>
       <c r="I66" s="1">
         <f t="shared" si="3"/>
-        <v>0.15360000000000001</v>
+        <v>0.15264000000000003</v>
       </c>
       <c r="J66">
         <v>6.78</v>
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="G67" s="1">
-        <f t="shared" ref="G67:G130" si="5">F67-(A67-1)*2*(C67+E67)</f>
-        <v>55.599999999999994</v>
+        <f t="shared" ref="G67:G130" si="5">F67-(A67-1)*2*(C67+E67)-2*C67</f>
+        <v>54.8</v>
       </c>
       <c r="H67" s="1">
         <f t="shared" ref="H67:H130" si="6">2.34*0.000001257*(0.5*A67^2*(F67+G67))/(1+2.73*(F67-G67)/(F67+G67))*1000</f>
-        <v>6.8935707875812531</v>
+        <v>6.7493909853658529</v>
       </c>
       <c r="I67" s="1">
         <f t="shared" ref="I67:I130" si="7">0.0000000168*4*0.5*(F67+G67)/(0.00007*C67)</f>
-        <v>0.15072000000000002</v>
+        <v>0.14976000000000003</v>
       </c>
       <c r="J67">
         <v>6.78</v>
@@ -4082,15 +4082,15 @@
       </c>
       <c r="G68" s="1">
         <f t="shared" si="5"/>
-        <v>53.2</v>
+        <v>52.400000000000006</v>
       </c>
       <c r="H68" s="1">
         <f t="shared" si="6"/>
-        <v>6.4697499378602199</v>
+        <v>6.3341471070684321</v>
       </c>
       <c r="I68" s="1">
         <f t="shared" si="7"/>
-        <v>0.14784000000000003</v>
+        <v>0.14688000000000001</v>
       </c>
       <c r="J68">
         <v>6.78</v>
@@ -4127,15 +4127,15 @@
       </c>
       <c r="G69" s="1">
         <f t="shared" si="5"/>
-        <v>58</v>
+        <v>56.8</v>
       </c>
       <c r="H69" s="1">
         <f t="shared" si="6"/>
-        <v>7.3444480159243586</v>
+        <v>7.1154980010218862</v>
       </c>
       <c r="I69" s="1">
         <f t="shared" si="7"/>
-        <v>0.10240000000000002</v>
+        <v>0.10144000000000002</v>
       </c>
       <c r="J69">
         <v>6.78</v>
@@ -4172,15 +4172,15 @@
       </c>
       <c r="G70" s="1">
         <f t="shared" si="5"/>
-        <v>55.6</v>
+        <v>54.4</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="6"/>
-        <v>6.8935707875812549</v>
+        <v>6.6784044525450925</v>
       </c>
       <c r="I70" s="1">
         <f t="shared" si="7"/>
-        <v>0.10048000000000001</v>
+        <v>9.9520000000000011E-2</v>
       </c>
       <c r="J70">
         <v>6.78</v>
@@ -4217,15 +4217,15 @@
       </c>
       <c r="G71" s="1">
         <f t="shared" si="5"/>
-        <v>53.2</v>
+        <v>52</v>
       </c>
       <c r="H71" s="1">
         <f t="shared" si="6"/>
-        <v>6.4697499378602199</v>
+        <v>6.267370270188148</v>
       </c>
       <c r="I71" s="1">
         <f t="shared" si="7"/>
-        <v>9.8560000000000023E-2</v>
+        <v>9.760000000000002E-2</v>
       </c>
       <c r="J71">
         <v>6.78</v>
@@ -4262,15 +4262,15 @@
       </c>
       <c r="G72" s="1">
         <f t="shared" si="5"/>
-        <v>50.8</v>
+        <v>49.599999999999994</v>
       </c>
       <c r="H72" s="1">
         <f t="shared" si="6"/>
-        <v>6.0710398367263982</v>
+        <v>5.8805437124888744</v>
       </c>
       <c r="I72" s="1">
         <f t="shared" si="7"/>
-        <v>9.6640000000000018E-2</v>
+        <v>9.5680000000000015E-2</v>
       </c>
       <c r="J72">
         <v>6.78</v>
@@ -4307,15 +4307,15 @@
       </c>
       <c r="G73" s="1">
         <f t="shared" si="5"/>
-        <v>55.599999999999994</v>
+        <v>53.999999999999993</v>
       </c>
       <c r="H73" s="1">
         <f t="shared" si="6"/>
-        <v>6.8935707875812531</v>
+        <v>6.608141355916028</v>
       </c>
       <c r="I73" s="1">
         <f t="shared" si="7"/>
-        <v>7.536000000000001E-2</v>
+        <v>7.4400000000000008E-2</v>
       </c>
       <c r="J73">
         <v>6.78</v>
@@ -4352,15 +4352,15 @@
       </c>
       <c r="G74" s="1">
         <f t="shared" si="5"/>
-        <v>53.2</v>
+        <v>51.6</v>
       </c>
       <c r="H74" s="1">
         <f t="shared" si="6"/>
-        <v>6.4697499378602199</v>
+        <v>6.201265482527119</v>
       </c>
       <c r="I74" s="1">
         <f t="shared" si="7"/>
-        <v>7.3920000000000013E-2</v>
+        <v>7.2960000000000011E-2</v>
       </c>
       <c r="J74">
         <v>6.78</v>
@@ -4397,15 +4397,15 @@
       </c>
       <c r="G75" s="1">
         <f t="shared" si="5"/>
-        <v>50.8</v>
+        <v>49.199999999999996</v>
       </c>
       <c r="H75" s="1">
         <f t="shared" si="6"/>
-        <v>6.0710398367263982</v>
+        <v>5.8183058307482485</v>
       </c>
       <c r="I75" s="1">
         <f t="shared" si="7"/>
-        <v>7.2480000000000017E-2</v>
+        <v>7.152E-2</v>
       </c>
       <c r="J75">
         <v>6.78</v>
@@ -4442,15 +4442,15 @@
       </c>
       <c r="G76" s="1">
         <f t="shared" si="5"/>
-        <v>48.4</v>
+        <v>46.8</v>
       </c>
       <c r="H76" s="1">
         <f t="shared" si="6"/>
-        <v>5.6956770348292816</v>
+        <v>5.4576086475462979</v>
       </c>
       <c r="I76" s="1">
         <f t="shared" si="7"/>
-        <v>7.1040000000000006E-2</v>
+        <v>7.0080000000000017E-2</v>
       </c>
       <c r="J76">
         <v>6.78</v>
@@ -4487,15 +4487,15 @@
       </c>
       <c r="G77" s="1">
         <f t="shared" si="5"/>
-        <v>53.2</v>
+        <v>51.2</v>
       </c>
       <c r="H77" s="1">
         <f t="shared" si="6"/>
-        <v>6.4697499378602199</v>
+        <v>6.1358246572442106</v>
       </c>
       <c r="I77" s="1">
         <f t="shared" si="7"/>
-        <v>5.9136000000000015E-2</v>
+        <v>5.8176000000000012E-2</v>
       </c>
       <c r="J77">
         <v>6.78</v>
@@ -4532,15 +4532,15 @@
       </c>
       <c r="G78" s="1">
         <f t="shared" si="5"/>
-        <v>50.8</v>
+        <v>48.8</v>
       </c>
       <c r="H78" s="1">
         <f t="shared" si="6"/>
-        <v>6.0710398367263982</v>
+        <v>5.7566860162466886</v>
       </c>
       <c r="I78" s="1">
         <f t="shared" si="7"/>
-        <v>5.7984000000000015E-2</v>
+        <v>5.7024000000000012E-2</v>
       </c>
       <c r="J78">
         <v>6.78</v>
@@ -4577,15 +4577,15 @@
       </c>
       <c r="G79" s="1">
         <f t="shared" si="5"/>
-        <v>48.4</v>
+        <v>46.4</v>
       </c>
       <c r="H79" s="1">
         <f t="shared" si="6"/>
-        <v>5.6956770348292816</v>
+        <v>5.3995491800915785</v>
       </c>
       <c r="I79" s="1">
         <f t="shared" si="7"/>
-        <v>5.6832000000000014E-2</v>
+        <v>5.5872000000000012E-2</v>
       </c>
       <c r="J79">
         <v>6.78</v>
@@ -4622,15 +4622,15 @@
       </c>
       <c r="G80" s="1">
         <f t="shared" si="5"/>
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H80" s="1">
         <f t="shared" si="6"/>
-        <v>5.3420594279418241</v>
+        <v>5.0629326130392478</v>
       </c>
       <c r="I80" s="1">
         <f t="shared" si="7"/>
-        <v>5.5680000000000014E-2</v>
+        <v>5.4720000000000012E-2</v>
       </c>
       <c r="J80">
         <v>6.78</v>
@@ -4667,15 +4667,15 @@
       </c>
       <c r="G81" s="1">
         <f t="shared" si="5"/>
-        <v>65.400000000000006</v>
+        <v>64.600000000000009</v>
       </c>
       <c r="H81" s="1">
         <f t="shared" si="6"/>
-        <v>8.5262013404494379</v>
+        <v>8.3598686811848211</v>
       </c>
       <c r="I81" s="1">
         <f t="shared" si="7"/>
-        <v>0.16848000000000005</v>
+        <v>0.16752000000000003</v>
       </c>
       <c r="J81">
         <v>6.78</v>
@@ -4712,15 +4712,15 @@
       </c>
       <c r="G82" s="1">
         <f t="shared" si="5"/>
-        <v>63</v>
+        <v>62.2</v>
       </c>
       <c r="H82" s="1">
         <f t="shared" si="6"/>
-        <v>8.0369126120871375</v>
+        <v>7.8801330817826925</v>
       </c>
       <c r="I82" s="1">
         <f t="shared" si="7"/>
-        <v>0.1656</v>
+        <v>0.16464000000000001</v>
       </c>
       <c r="J82">
         <v>6.78</v>
@@ -4757,15 +4757,15 @@
       </c>
       <c r="G83" s="1">
         <f t="shared" si="5"/>
-        <v>60.599999999999994</v>
+        <v>59.8</v>
       </c>
       <c r="H83" s="1">
         <f t="shared" si="6"/>
-        <v>7.5755992581503824</v>
+        <v>7.4277032607795972</v>
       </c>
       <c r="I83" s="1">
         <f t="shared" si="7"/>
-        <v>0.16272</v>
+        <v>0.16176000000000004</v>
       </c>
       <c r="J83">
         <v>6.78</v>
@@ -4802,15 +4802,15 @@
       </c>
       <c r="G84" s="1">
         <f t="shared" si="5"/>
-        <v>58.2</v>
+        <v>57.400000000000006</v>
       </c>
       <c r="H84" s="1">
         <f t="shared" si="6"/>
-        <v>7.1403152634499385</v>
+        <v>7.000694349538926</v>
       </c>
       <c r="I84" s="1">
         <f t="shared" si="7"/>
-        <v>0.15984000000000001</v>
+        <v>0.15888000000000002</v>
       </c>
       <c r="J84">
         <v>6.78</v>
@@ -4847,15 +4847,15 @@
       </c>
       <c r="G85" s="1">
         <f t="shared" si="5"/>
-        <v>63</v>
+        <v>61.8</v>
       </c>
       <c r="H85" s="1">
         <f t="shared" si="6"/>
-        <v>8.0369126120871375</v>
+        <v>7.8028850219537587</v>
       </c>
       <c r="I85" s="1">
         <f t="shared" si="7"/>
-        <v>0.11040000000000001</v>
+        <v>0.10944000000000004</v>
       </c>
       <c r="J85">
         <v>6.78</v>
@@ -4892,15 +4892,15 @@
       </c>
       <c r="G86" s="1">
         <f t="shared" si="5"/>
-        <v>60.6</v>
+        <v>59.4</v>
       </c>
       <c r="H86" s="1">
         <f t="shared" si="6"/>
-        <v>7.5755992581503824</v>
+        <v>7.3548180837209305</v>
       </c>
       <c r="I86" s="1">
         <f t="shared" si="7"/>
-        <v>0.10848000000000001</v>
+        <v>0.10752000000000002</v>
       </c>
       <c r="J86">
         <v>6.78</v>
@@ -4937,15 +4937,15 @@
       </c>
       <c r="G87" s="1">
         <f t="shared" si="5"/>
-        <v>58.2</v>
+        <v>57</v>
       </c>
       <c r="H87" s="1">
         <f t="shared" si="6"/>
-        <v>7.1403152634499385</v>
+        <v>6.9318749334216623</v>
       </c>
       <c r="I87" s="1">
         <f t="shared" si="7"/>
-        <v>0.10656000000000002</v>
+        <v>0.10560000000000001</v>
       </c>
       <c r="J87">
         <v>6.78</v>
@@ -4982,15 +4982,15 @@
       </c>
       <c r="G88" s="1">
         <f t="shared" si="5"/>
-        <v>55.8</v>
+        <v>54.599999999999994</v>
       </c>
       <c r="H88" s="1">
         <f t="shared" si="6"/>
-        <v>6.7292910134398731</v>
+        <v>6.5323666589469571</v>
       </c>
       <c r="I88" s="1">
         <f t="shared" si="7"/>
-        <v>0.10464000000000004</v>
+        <v>0.10368000000000001</v>
       </c>
       <c r="J88">
         <v>6.78</v>
@@ -5027,15 +5027,15 @@
       </c>
       <c r="G89" s="1">
         <f t="shared" si="5"/>
-        <v>60.599999999999994</v>
+        <v>58.999999999999993</v>
       </c>
       <c r="H89" s="1">
         <f t="shared" si="6"/>
-        <v>7.5755992581503824</v>
+        <v>7.2826304162539381</v>
       </c>
       <c r="I89" s="1">
         <f t="shared" si="7"/>
-        <v>8.1360000000000002E-2</v>
+        <v>8.0400000000000013E-2</v>
       </c>
       <c r="J89">
         <v>6.78</v>
@@ -5072,15 +5072,15 @@
       </c>
       <c r="G90" s="1">
         <f t="shared" si="5"/>
-        <v>58.2</v>
+        <v>56.6</v>
       </c>
       <c r="H90" s="1">
         <f t="shared" si="6"/>
-        <v>7.1403152634499385</v>
+        <v>6.8637061535571284</v>
       </c>
       <c r="I90" s="1">
         <f t="shared" si="7"/>
-        <v>7.9920000000000005E-2</v>
+        <v>7.8960000000000002E-2</v>
       </c>
       <c r="J90">
         <v>6.78</v>
@@ -5117,15 +5117,15 @@
       </c>
       <c r="G91" s="1">
         <f t="shared" si="5"/>
-        <v>55.8</v>
+        <v>54.199999999999996</v>
       </c>
       <c r="H91" s="1">
         <f t="shared" si="6"/>
-        <v>6.7292910134398731</v>
+        <v>6.4679501320457655</v>
       </c>
       <c r="I91" s="1">
         <f t="shared" si="7"/>
-        <v>7.8480000000000022E-2</v>
+        <v>7.7520000000000006E-2</v>
       </c>
       <c r="J91">
         <v>6.78</v>
@@ -5162,15 +5162,15 @@
       </c>
       <c r="G92" s="1">
         <f t="shared" si="5"/>
-        <v>53.4</v>
+        <v>51.8</v>
       </c>
       <c r="H92" s="1">
         <f t="shared" si="6"/>
-        <v>6.3409137493787631</v>
+        <v>6.0938445770101399</v>
       </c>
       <c r="I92" s="1">
         <f t="shared" si="7"/>
-        <v>7.7040000000000011E-2</v>
+        <v>7.6080000000000009E-2</v>
       </c>
       <c r="J92">
         <v>6.78</v>
@@ -5207,15 +5207,15 @@
       </c>
       <c r="G93" s="1">
         <f t="shared" si="5"/>
-        <v>58.2</v>
+        <v>56.2</v>
       </c>
       <c r="H93" s="1">
         <f t="shared" si="6"/>
-        <v>7.1403152634499385</v>
+        <v>6.7961806097083119</v>
       </c>
       <c r="I93" s="1">
         <f t="shared" si="7"/>
-        <v>6.3936000000000007E-2</v>
+        <v>6.2976000000000004E-2</v>
       </c>
       <c r="J93">
         <v>6.78</v>
@@ -5252,15 +5252,15 @@
       </c>
       <c r="G94" s="1">
         <f t="shared" si="5"/>
-        <v>55.8</v>
+        <v>53.8</v>
       </c>
       <c r="H94" s="1">
         <f t="shared" si="6"/>
-        <v>6.7292910134398731</v>
+        <v>6.4041347155842203</v>
       </c>
       <c r="I94" s="1">
         <f t="shared" si="7"/>
-        <v>6.278400000000002E-2</v>
+        <v>6.1824000000000011E-2</v>
       </c>
       <c r="J94">
         <v>6.78</v>
@@ -5297,15 +5297,15 @@
       </c>
       <c r="G95" s="1">
         <f t="shared" si="5"/>
-        <v>53.4</v>
+        <v>51.4</v>
       </c>
       <c r="H95" s="1">
         <f t="shared" si="6"/>
-        <v>6.3409137493787631</v>
+        <v>6.0334993282830611</v>
       </c>
       <c r="I95" s="1">
         <f t="shared" si="7"/>
-        <v>6.1632000000000013E-2</v>
+        <v>6.0672000000000011E-2</v>
       </c>
       <c r="J95">
         <v>6.78</v>
@@ -5342,15 +5342,15 @@
       </c>
       <c r="G96" s="1">
         <f t="shared" si="5"/>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H96" s="1">
         <f t="shared" si="6"/>
-        <v>5.9737105657894727</v>
+        <v>5.6829066702225868</v>
       </c>
       <c r="I96" s="1">
         <f t="shared" si="7"/>
-        <v>6.0480000000000013E-2</v>
+        <v>5.952000000000001E-2</v>
       </c>
       <c r="J96">
         <v>6.78</v>
@@ -5387,15 +5387,15 @@
       </c>
       <c r="G97" s="1">
         <f t="shared" si="5"/>
-        <v>65.400000000000006</v>
+        <v>64.600000000000009</v>
       </c>
       <c r="H97" s="1">
         <f t="shared" si="6"/>
-        <v>8.5262013404494379</v>
+        <v>8.3598686811848211</v>
       </c>
       <c r="I97" s="1">
         <f t="shared" si="7"/>
-        <v>0.16848000000000005</v>
+        <v>0.16752000000000003</v>
       </c>
       <c r="J97">
         <v>6.78</v>
@@ -5432,15 +5432,15 @@
       </c>
       <c r="G98" s="1">
         <f t="shared" si="5"/>
-        <v>63</v>
+        <v>62.2</v>
       </c>
       <c r="H98" s="1">
         <f t="shared" si="6"/>
-        <v>8.0369126120871375</v>
+        <v>7.8801330817826925</v>
       </c>
       <c r="I98" s="1">
         <f t="shared" si="7"/>
-        <v>0.1656</v>
+        <v>0.16464000000000001</v>
       </c>
       <c r="J98">
         <v>6.78</v>
@@ -5477,15 +5477,15 @@
       </c>
       <c r="G99" s="1">
         <f t="shared" si="5"/>
-        <v>60.599999999999994</v>
+        <v>59.8</v>
       </c>
       <c r="H99" s="1">
         <f t="shared" si="6"/>
-        <v>7.5755992581503824</v>
+        <v>7.4277032607795972</v>
       </c>
       <c r="I99" s="1">
         <f t="shared" si="7"/>
-        <v>0.16272</v>
+        <v>0.16176000000000004</v>
       </c>
       <c r="J99">
         <v>6.78</v>
@@ -5522,15 +5522,15 @@
       </c>
       <c r="G100" s="1">
         <f t="shared" si="5"/>
-        <v>58.2</v>
+        <v>57.400000000000006</v>
       </c>
       <c r="H100" s="1">
         <f t="shared" si="6"/>
-        <v>7.1403152634499385</v>
+        <v>7.000694349538926</v>
       </c>
       <c r="I100" s="1">
         <f t="shared" si="7"/>
-        <v>0.15984000000000001</v>
+        <v>0.15888000000000002</v>
       </c>
       <c r="J100">
         <v>6.78</v>
@@ -5567,15 +5567,15 @@
       </c>
       <c r="G101" s="1">
         <f t="shared" si="5"/>
-        <v>63</v>
+        <v>61.8</v>
       </c>
       <c r="H101" s="1">
         <f t="shared" si="6"/>
-        <v>8.0369126120871375</v>
+        <v>7.8028850219537587</v>
       </c>
       <c r="I101" s="1">
         <f t="shared" si="7"/>
-        <v>0.11040000000000001</v>
+        <v>0.10944000000000004</v>
       </c>
       <c r="J101">
         <v>6.78</v>
@@ -5612,15 +5612,15 @@
       </c>
       <c r="G102" s="1">
         <f t="shared" si="5"/>
-        <v>60.6</v>
+        <v>59.4</v>
       </c>
       <c r="H102" s="1">
         <f t="shared" si="6"/>
-        <v>7.5755992581503824</v>
+        <v>7.3548180837209305</v>
       </c>
       <c r="I102" s="1">
         <f t="shared" si="7"/>
-        <v>0.10848000000000001</v>
+        <v>0.10752000000000002</v>
       </c>
       <c r="J102">
         <v>6.78</v>
@@ -5657,15 +5657,15 @@
       </c>
       <c r="G103" s="1">
         <f t="shared" si="5"/>
-        <v>58.2</v>
+        <v>57</v>
       </c>
       <c r="H103" s="1">
         <f t="shared" si="6"/>
-        <v>7.1403152634499385</v>
+        <v>6.9318749334216623</v>
       </c>
       <c r="I103" s="1">
         <f t="shared" si="7"/>
-        <v>0.10656000000000002</v>
+        <v>0.10560000000000001</v>
       </c>
       <c r="J103">
         <v>6.78</v>
@@ -5702,15 +5702,15 @@
       </c>
       <c r="G104" s="1">
         <f t="shared" si="5"/>
-        <v>55.8</v>
+        <v>54.599999999999994</v>
       </c>
       <c r="H104" s="1">
         <f t="shared" si="6"/>
-        <v>6.7292910134398731</v>
+        <v>6.5323666589469571</v>
       </c>
       <c r="I104" s="1">
         <f t="shared" si="7"/>
-        <v>0.10464000000000004</v>
+        <v>0.10368000000000001</v>
       </c>
       <c r="J104">
         <v>6.78</v>
@@ -5747,15 +5747,15 @@
       </c>
       <c r="G105" s="1">
         <f t="shared" si="5"/>
-        <v>60.599999999999994</v>
+        <v>58.999999999999993</v>
       </c>
       <c r="H105" s="1">
         <f t="shared" si="6"/>
-        <v>7.5755992581503824</v>
+        <v>7.2826304162539381</v>
       </c>
       <c r="I105" s="1">
         <f t="shared" si="7"/>
-        <v>8.1360000000000002E-2</v>
+        <v>8.0400000000000013E-2</v>
       </c>
       <c r="J105">
         <v>6.78</v>
@@ -5792,15 +5792,15 @@
       </c>
       <c r="G106" s="1">
         <f t="shared" si="5"/>
-        <v>58.2</v>
+        <v>56.6</v>
       </c>
       <c r="H106" s="1">
         <f t="shared" si="6"/>
-        <v>7.1403152634499385</v>
+        <v>6.8637061535571284</v>
       </c>
       <c r="I106" s="1">
         <f t="shared" si="7"/>
-        <v>7.9920000000000005E-2</v>
+        <v>7.8960000000000002E-2</v>
       </c>
       <c r="J106">
         <v>6.78</v>
@@ -5837,15 +5837,15 @@
       </c>
       <c r="G107" s="1">
         <f t="shared" si="5"/>
-        <v>55.8</v>
+        <v>54.199999999999996</v>
       </c>
       <c r="H107" s="1">
         <f t="shared" si="6"/>
-        <v>6.7292910134398731</v>
+        <v>6.4679501320457655</v>
       </c>
       <c r="I107" s="1">
         <f t="shared" si="7"/>
-        <v>7.8480000000000022E-2</v>
+        <v>7.7520000000000006E-2</v>
       </c>
       <c r="J107">
         <v>6.78</v>
@@ -5882,15 +5882,15 @@
       </c>
       <c r="G108" s="1">
         <f t="shared" si="5"/>
-        <v>53.4</v>
+        <v>51.8</v>
       </c>
       <c r="H108" s="1">
         <f t="shared" si="6"/>
-        <v>6.3409137493787631</v>
+        <v>6.0938445770101399</v>
       </c>
       <c r="I108" s="1">
         <f t="shared" si="7"/>
-        <v>7.7040000000000011E-2</v>
+        <v>7.6080000000000009E-2</v>
       </c>
       <c r="J108">
         <v>6.78</v>
@@ -5927,15 +5927,15 @@
       </c>
       <c r="G109" s="1">
         <f t="shared" si="5"/>
-        <v>58.2</v>
+        <v>56.2</v>
       </c>
       <c r="H109" s="1">
         <f t="shared" si="6"/>
-        <v>7.1403152634499385</v>
+        <v>6.7961806097083119</v>
       </c>
       <c r="I109" s="1">
         <f t="shared" si="7"/>
-        <v>6.3936000000000007E-2</v>
+        <v>6.2976000000000004E-2</v>
       </c>
       <c r="J109">
         <v>6.78</v>
@@ -5972,15 +5972,15 @@
       </c>
       <c r="G110" s="1">
         <f t="shared" si="5"/>
-        <v>55.8</v>
+        <v>53.8</v>
       </c>
       <c r="H110" s="1">
         <f t="shared" si="6"/>
-        <v>6.7292910134398731</v>
+        <v>6.4041347155842203</v>
       </c>
       <c r="I110" s="1">
         <f t="shared" si="7"/>
-        <v>6.278400000000002E-2</v>
+        <v>6.1824000000000011E-2</v>
       </c>
       <c r="J110">
         <v>6.78</v>
@@ -6017,15 +6017,15 @@
       </c>
       <c r="G111" s="1">
         <f t="shared" si="5"/>
-        <v>53.4</v>
+        <v>51.4</v>
       </c>
       <c r="H111" s="1">
         <f t="shared" si="6"/>
-        <v>6.3409137493787631</v>
+        <v>6.0334993282830611</v>
       </c>
       <c r="I111" s="1">
         <f t="shared" si="7"/>
-        <v>6.1632000000000013E-2</v>
+        <v>6.0672000000000011E-2</v>
       </c>
       <c r="J111">
         <v>6.78</v>
@@ -6062,15 +6062,15 @@
       </c>
       <c r="G112" s="1">
         <f t="shared" si="5"/>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H112" s="1">
         <f t="shared" si="6"/>
-        <v>5.9737105657894727</v>
+        <v>5.6829066702225868</v>
       </c>
       <c r="I112" s="1">
         <f t="shared" si="7"/>
-        <v>6.0480000000000013E-2</v>
+        <v>5.952000000000001E-2</v>
       </c>
       <c r="J112">
         <v>6.78</v>
@@ -6107,15 +6107,15 @@
       </c>
       <c r="G113" s="1">
         <f t="shared" si="5"/>
-        <v>65.400000000000006</v>
+        <v>64.600000000000009</v>
       </c>
       <c r="H113" s="1">
         <f t="shared" si="6"/>
-        <v>8.5262013404494379</v>
+        <v>8.3598686811848211</v>
       </c>
       <c r="I113" s="1">
         <f t="shared" si="7"/>
-        <v>0.16848000000000005</v>
+        <v>0.16752000000000003</v>
       </c>
       <c r="J113">
         <v>6.78</v>
@@ -6152,15 +6152,15 @@
       </c>
       <c r="G114" s="1">
         <f t="shared" si="5"/>
-        <v>63</v>
+        <v>62.2</v>
       </c>
       <c r="H114" s="1">
         <f t="shared" si="6"/>
-        <v>8.0369126120871375</v>
+        <v>7.8801330817826925</v>
       </c>
       <c r="I114" s="1">
         <f t="shared" si="7"/>
-        <v>0.1656</v>
+        <v>0.16464000000000001</v>
       </c>
       <c r="J114">
         <v>6.78</v>
@@ -6197,15 +6197,15 @@
       </c>
       <c r="G115" s="1">
         <f t="shared" si="5"/>
-        <v>60.599999999999994</v>
+        <v>59.8</v>
       </c>
       <c r="H115" s="1">
         <f t="shared" si="6"/>
-        <v>7.5755992581503824</v>
+        <v>7.4277032607795972</v>
       </c>
       <c r="I115" s="1">
         <f t="shared" si="7"/>
-        <v>0.16272</v>
+        <v>0.16176000000000004</v>
       </c>
       <c r="J115">
         <v>6.78</v>
@@ -6242,15 +6242,15 @@
       </c>
       <c r="G116" s="1">
         <f t="shared" si="5"/>
-        <v>58.2</v>
+        <v>57.400000000000006</v>
       </c>
       <c r="H116" s="1">
         <f t="shared" si="6"/>
-        <v>7.1403152634499385</v>
+        <v>7.000694349538926</v>
       </c>
       <c r="I116" s="1">
         <f t="shared" si="7"/>
-        <v>0.15984000000000001</v>
+        <v>0.15888000000000002</v>
       </c>
       <c r="J116">
         <v>6.78</v>
@@ -6287,15 +6287,15 @@
       </c>
       <c r="G117" s="1">
         <f t="shared" si="5"/>
-        <v>63</v>
+        <v>61.8</v>
       </c>
       <c r="H117" s="1">
         <f t="shared" si="6"/>
-        <v>8.0369126120871375</v>
+        <v>7.8028850219537587</v>
       </c>
       <c r="I117" s="1">
         <f t="shared" si="7"/>
-        <v>0.11040000000000001</v>
+        <v>0.10944000000000004</v>
       </c>
       <c r="J117">
         <v>6.78</v>
@@ -6332,15 +6332,15 @@
       </c>
       <c r="G118" s="1">
         <f t="shared" si="5"/>
-        <v>60.6</v>
+        <v>59.4</v>
       </c>
       <c r="H118" s="1">
         <f t="shared" si="6"/>
-        <v>7.5755992581503824</v>
+        <v>7.3548180837209305</v>
       </c>
       <c r="I118" s="1">
         <f t="shared" si="7"/>
-        <v>0.10848000000000001</v>
+        <v>0.10752000000000002</v>
       </c>
       <c r="J118">
         <v>6.78</v>
@@ -6377,15 +6377,15 @@
       </c>
       <c r="G119" s="1">
         <f t="shared" si="5"/>
-        <v>58.2</v>
+        <v>57</v>
       </c>
       <c r="H119" s="1">
         <f t="shared" si="6"/>
-        <v>7.1403152634499385</v>
+        <v>6.9318749334216623</v>
       </c>
       <c r="I119" s="1">
         <f t="shared" si="7"/>
-        <v>0.10656000000000002</v>
+        <v>0.10560000000000001</v>
       </c>
       <c r="J119">
         <v>6.78</v>
@@ -6422,15 +6422,15 @@
       </c>
       <c r="G120" s="1">
         <f t="shared" si="5"/>
-        <v>55.8</v>
+        <v>54.599999999999994</v>
       </c>
       <c r="H120" s="1">
         <f t="shared" si="6"/>
-        <v>6.7292910134398731</v>
+        <v>6.5323666589469571</v>
       </c>
       <c r="I120" s="1">
         <f t="shared" si="7"/>
-        <v>0.10464000000000004</v>
+        <v>0.10368000000000001</v>
       </c>
       <c r="J120">
         <v>6.78</v>
@@ -6467,15 +6467,15 @@
       </c>
       <c r="G121" s="1">
         <f t="shared" si="5"/>
-        <v>60.599999999999994</v>
+        <v>58.999999999999993</v>
       </c>
       <c r="H121" s="1">
         <f t="shared" si="6"/>
-        <v>7.5755992581503824</v>
+        <v>7.2826304162539381</v>
       </c>
       <c r="I121" s="1">
         <f t="shared" si="7"/>
-        <v>8.1360000000000002E-2</v>
+        <v>8.0400000000000013E-2</v>
       </c>
       <c r="J121">
         <v>6.78</v>
@@ -6512,15 +6512,15 @@
       </c>
       <c r="G122" s="1">
         <f t="shared" si="5"/>
-        <v>58.2</v>
+        <v>56.6</v>
       </c>
       <c r="H122" s="1">
         <f t="shared" si="6"/>
-        <v>7.1403152634499385</v>
+        <v>6.8637061535571284</v>
       </c>
       <c r="I122" s="1">
         <f t="shared" si="7"/>
-        <v>7.9920000000000005E-2</v>
+        <v>7.8960000000000002E-2</v>
       </c>
       <c r="J122">
         <v>6.78</v>
@@ -6557,15 +6557,15 @@
       </c>
       <c r="G123" s="1">
         <f t="shared" si="5"/>
-        <v>55.8</v>
+        <v>54.199999999999996</v>
       </c>
       <c r="H123" s="1">
         <f t="shared" si="6"/>
-        <v>6.7292910134398731</v>
+        <v>6.4679501320457655</v>
       </c>
       <c r="I123" s="1">
         <f t="shared" si="7"/>
-        <v>7.8480000000000022E-2</v>
+        <v>7.7520000000000006E-2</v>
       </c>
       <c r="J123">
         <v>6.78</v>
@@ -6602,15 +6602,15 @@
       </c>
       <c r="G124" s="1">
         <f t="shared" si="5"/>
-        <v>53.4</v>
+        <v>51.8</v>
       </c>
       <c r="H124" s="1">
         <f t="shared" si="6"/>
-        <v>6.3409137493787631</v>
+        <v>6.0938445770101399</v>
       </c>
       <c r="I124" s="1">
         <f t="shared" si="7"/>
-        <v>7.7040000000000011E-2</v>
+        <v>7.6080000000000009E-2</v>
       </c>
       <c r="J124">
         <v>6.78</v>
@@ -6647,15 +6647,15 @@
       </c>
       <c r="G125" s="1">
         <f t="shared" si="5"/>
-        <v>58.2</v>
+        <v>56.2</v>
       </c>
       <c r="H125" s="1">
         <f t="shared" si="6"/>
-        <v>7.1403152634499385</v>
+        <v>6.7961806097083119</v>
       </c>
       <c r="I125" s="1">
         <f t="shared" si="7"/>
-        <v>6.3936000000000007E-2</v>
+        <v>6.2976000000000004E-2</v>
       </c>
       <c r="J125">
         <v>6.78</v>
@@ -6692,15 +6692,15 @@
       </c>
       <c r="G126" s="1">
         <f t="shared" si="5"/>
-        <v>55.8</v>
+        <v>53.8</v>
       </c>
       <c r="H126" s="1">
         <f t="shared" si="6"/>
-        <v>6.7292910134398731</v>
+        <v>6.4041347155842203</v>
       </c>
       <c r="I126" s="1">
         <f t="shared" si="7"/>
-        <v>6.278400000000002E-2</v>
+        <v>6.1824000000000011E-2</v>
       </c>
       <c r="J126">
         <v>6.78</v>
@@ -6737,15 +6737,15 @@
       </c>
       <c r="G127" s="1">
         <f t="shared" si="5"/>
-        <v>53.4</v>
+        <v>51.4</v>
       </c>
       <c r="H127" s="1">
         <f t="shared" si="6"/>
-        <v>6.3409137493787631</v>
+        <v>6.0334993282830611</v>
       </c>
       <c r="I127" s="1">
         <f t="shared" si="7"/>
-        <v>6.1632000000000013E-2</v>
+        <v>6.0672000000000011E-2</v>
       </c>
       <c r="J127">
         <v>6.78</v>
@@ -6782,15 +6782,15 @@
       </c>
       <c r="G128" s="1">
         <f t="shared" si="5"/>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H128" s="1">
         <f t="shared" si="6"/>
-        <v>5.9737105657894727</v>
+        <v>5.6829066702225868</v>
       </c>
       <c r="I128" s="1">
         <f t="shared" si="7"/>
-        <v>6.0480000000000013E-2</v>
+        <v>5.952000000000001E-2</v>
       </c>
       <c r="J128">
         <v>6.78</v>
@@ -6827,15 +6827,15 @@
       </c>
       <c r="G129" s="1">
         <f t="shared" si="5"/>
-        <v>65.400000000000006</v>
+        <v>64.600000000000009</v>
       </c>
       <c r="H129" s="1">
         <f t="shared" si="6"/>
-        <v>8.5262013404494379</v>
+        <v>8.3598686811848211</v>
       </c>
       <c r="I129" s="1">
         <f t="shared" si="7"/>
-        <v>0.16848000000000005</v>
+        <v>0.16752000000000003</v>
       </c>
       <c r="J129">
         <v>6.78</v>
@@ -6872,15 +6872,15 @@
       </c>
       <c r="G130" s="1">
         <f t="shared" si="5"/>
-        <v>63</v>
+        <v>62.2</v>
       </c>
       <c r="H130" s="1">
         <f t="shared" si="6"/>
-        <v>8.0369126120871375</v>
+        <v>7.8801330817826925</v>
       </c>
       <c r="I130" s="1">
         <f t="shared" si="7"/>
-        <v>0.1656</v>
+        <v>0.16464000000000001</v>
       </c>
       <c r="J130">
         <v>6.78</v>
@@ -6916,16 +6916,16 @@
         <v>75</v>
       </c>
       <c r="G131" s="1">
-        <f t="shared" ref="G131:G194" si="9">F131-(A131-1)*2*(C131+E131)</f>
-        <v>60.599999999999994</v>
+        <f t="shared" ref="G131:G194" si="9">F131-(A131-1)*2*(C131+E131)-2*C131</f>
+        <v>59.8</v>
       </c>
       <c r="H131" s="1">
         <f t="shared" ref="H131:H194" si="10">2.34*0.000001257*(0.5*A131^2*(F131+G131))/(1+2.73*(F131-G131)/(F131+G131))*1000</f>
-        <v>7.5755992581503824</v>
+        <v>7.4277032607795972</v>
       </c>
       <c r="I131" s="1">
         <f t="shared" ref="I131:I194" si="11">0.0000000168*4*0.5*(F131+G131)/(0.00007*C131)</f>
-        <v>0.16272</v>
+        <v>0.16176000000000004</v>
       </c>
       <c r="J131">
         <v>6.78</v>
@@ -6962,15 +6962,15 @@
       </c>
       <c r="G132" s="1">
         <f t="shared" si="9"/>
-        <v>58.2</v>
+        <v>57.400000000000006</v>
       </c>
       <c r="H132" s="1">
         <f t="shared" si="10"/>
-        <v>7.1403152634499385</v>
+        <v>7.000694349538926</v>
       </c>
       <c r="I132" s="1">
         <f t="shared" si="11"/>
-        <v>0.15984000000000001</v>
+        <v>0.15888000000000002</v>
       </c>
       <c r="J132">
         <v>6.78</v>
@@ -7007,15 +7007,15 @@
       </c>
       <c r="G133" s="1">
         <f t="shared" si="9"/>
-        <v>63</v>
+        <v>61.8</v>
       </c>
       <c r="H133" s="1">
         <f t="shared" si="10"/>
-        <v>8.0369126120871375</v>
+        <v>7.8028850219537587</v>
       </c>
       <c r="I133" s="1">
         <f t="shared" si="11"/>
-        <v>0.11040000000000001</v>
+        <v>0.10944000000000004</v>
       </c>
       <c r="J133">
         <v>6.78</v>
@@ -7052,15 +7052,15 @@
       </c>
       <c r="G134" s="1">
         <f t="shared" si="9"/>
-        <v>60.6</v>
+        <v>59.4</v>
       </c>
       <c r="H134" s="1">
         <f t="shared" si="10"/>
-        <v>7.5755992581503824</v>
+        <v>7.3548180837209305</v>
       </c>
       <c r="I134" s="1">
         <f t="shared" si="11"/>
-        <v>0.10848000000000001</v>
+        <v>0.10752000000000002</v>
       </c>
       <c r="J134">
         <v>6.78</v>
@@ -7097,15 +7097,15 @@
       </c>
       <c r="G135" s="1">
         <f t="shared" si="9"/>
-        <v>58.2</v>
+        <v>57</v>
       </c>
       <c r="H135" s="1">
         <f t="shared" si="10"/>
-        <v>7.1403152634499385</v>
+        <v>6.9318749334216623</v>
       </c>
       <c r="I135" s="1">
         <f t="shared" si="11"/>
-        <v>0.10656000000000002</v>
+        <v>0.10560000000000001</v>
       </c>
       <c r="J135">
         <v>6.78</v>
@@ -7142,15 +7142,15 @@
       </c>
       <c r="G136" s="1">
         <f t="shared" si="9"/>
-        <v>55.8</v>
+        <v>54.599999999999994</v>
       </c>
       <c r="H136" s="1">
         <f t="shared" si="10"/>
-        <v>6.7292910134398731</v>
+        <v>6.5323666589469571</v>
       </c>
       <c r="I136" s="1">
         <f t="shared" si="11"/>
-        <v>0.10464000000000004</v>
+        <v>0.10368000000000001</v>
       </c>
       <c r="J136">
         <v>6.78</v>
@@ -7187,15 +7187,15 @@
       </c>
       <c r="G137" s="1">
         <f t="shared" si="9"/>
-        <v>60.599999999999994</v>
+        <v>58.999999999999993</v>
       </c>
       <c r="H137" s="1">
         <f t="shared" si="10"/>
-        <v>7.5755992581503824</v>
+        <v>7.2826304162539381</v>
       </c>
       <c r="I137" s="1">
         <f t="shared" si="11"/>
-        <v>8.1360000000000002E-2</v>
+        <v>8.0400000000000013E-2</v>
       </c>
       <c r="J137">
         <v>6.78</v>
@@ -7232,15 +7232,15 @@
       </c>
       <c r="G138" s="1">
         <f t="shared" si="9"/>
-        <v>58.2</v>
+        <v>56.6</v>
       </c>
       <c r="H138" s="1">
         <f t="shared" si="10"/>
-        <v>7.1403152634499385</v>
+        <v>6.8637061535571284</v>
       </c>
       <c r="I138" s="1">
         <f t="shared" si="11"/>
-        <v>7.9920000000000005E-2</v>
+        <v>7.8960000000000002E-2</v>
       </c>
       <c r="J138">
         <v>6.78</v>
@@ -7277,15 +7277,15 @@
       </c>
       <c r="G139" s="1">
         <f t="shared" si="9"/>
-        <v>55.8</v>
+        <v>54.199999999999996</v>
       </c>
       <c r="H139" s="1">
         <f t="shared" si="10"/>
-        <v>6.7292910134398731</v>
+        <v>6.4679501320457655</v>
       </c>
       <c r="I139" s="1">
         <f t="shared" si="11"/>
-        <v>7.8480000000000022E-2</v>
+        <v>7.7520000000000006E-2</v>
       </c>
       <c r="J139">
         <v>6.78</v>
@@ -7322,15 +7322,15 @@
       </c>
       <c r="G140" s="1">
         <f t="shared" si="9"/>
-        <v>53.4</v>
+        <v>51.8</v>
       </c>
       <c r="H140" s="1">
         <f t="shared" si="10"/>
-        <v>6.3409137493787631</v>
+        <v>6.0938445770101399</v>
       </c>
       <c r="I140" s="1">
         <f t="shared" si="11"/>
-        <v>7.7040000000000011E-2</v>
+        <v>7.6080000000000009E-2</v>
       </c>
       <c r="J140">
         <v>6.78</v>
@@ -7367,15 +7367,15 @@
       </c>
       <c r="G141" s="1">
         <f t="shared" si="9"/>
-        <v>58.2</v>
+        <v>56.2</v>
       </c>
       <c r="H141" s="1">
         <f t="shared" si="10"/>
-        <v>7.1403152634499385</v>
+        <v>6.7961806097083119</v>
       </c>
       <c r="I141" s="1">
         <f t="shared" si="11"/>
-        <v>6.3936000000000007E-2</v>
+        <v>6.2976000000000004E-2</v>
       </c>
       <c r="J141">
         <v>6.78</v>
@@ -7412,15 +7412,15 @@
       </c>
       <c r="G142" s="1">
         <f t="shared" si="9"/>
-        <v>55.8</v>
+        <v>53.8</v>
       </c>
       <c r="H142" s="1">
         <f t="shared" si="10"/>
-        <v>6.7292910134398731</v>
+        <v>6.4041347155842203</v>
       </c>
       <c r="I142" s="1">
         <f t="shared" si="11"/>
-        <v>6.278400000000002E-2</v>
+        <v>6.1824000000000011E-2</v>
       </c>
       <c r="J142">
         <v>6.78</v>
@@ -7457,15 +7457,15 @@
       </c>
       <c r="G143" s="1">
         <f t="shared" si="9"/>
-        <v>53.4</v>
+        <v>51.4</v>
       </c>
       <c r="H143" s="1">
         <f t="shared" si="10"/>
-        <v>6.3409137493787631</v>
+        <v>6.0334993282830611</v>
       </c>
       <c r="I143" s="1">
         <f t="shared" si="11"/>
-        <v>6.1632000000000013E-2</v>
+        <v>6.0672000000000011E-2</v>
       </c>
       <c r="J143">
         <v>6.78</v>
@@ -7502,15 +7502,15 @@
       </c>
       <c r="G144" s="1">
         <f t="shared" si="9"/>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H144" s="1">
         <f t="shared" si="10"/>
-        <v>5.9737105657894727</v>
+        <v>5.6829066702225868</v>
       </c>
       <c r="I144" s="1">
         <f t="shared" si="11"/>
-        <v>6.0480000000000013E-2</v>
+        <v>5.952000000000001E-2</v>
       </c>
       <c r="J144">
         <v>6.78</v>
@@ -7547,15 +7547,15 @@
       </c>
       <c r="G145" s="1">
         <f t="shared" si="9"/>
-        <v>65.400000000000006</v>
+        <v>64.600000000000009</v>
       </c>
       <c r="H145" s="1">
         <f t="shared" si="10"/>
-        <v>8.5262013404494379</v>
+        <v>8.3598686811848211</v>
       </c>
       <c r="I145" s="1">
         <f t="shared" si="11"/>
-        <v>0.16848000000000005</v>
+        <v>0.16752000000000003</v>
       </c>
       <c r="J145">
         <v>6.78</v>
@@ -7592,15 +7592,15 @@
       </c>
       <c r="G146" s="1">
         <f t="shared" si="9"/>
-        <v>63</v>
+        <v>62.2</v>
       </c>
       <c r="H146" s="1">
         <f t="shared" si="10"/>
-        <v>8.0369126120871375</v>
+        <v>7.8801330817826925</v>
       </c>
       <c r="I146" s="1">
         <f t="shared" si="11"/>
-        <v>0.1656</v>
+        <v>0.16464000000000001</v>
       </c>
       <c r="J146">
         <v>6.78</v>
@@ -7637,15 +7637,15 @@
       </c>
       <c r="G147" s="1">
         <f t="shared" si="9"/>
-        <v>60.599999999999994</v>
+        <v>59.8</v>
       </c>
       <c r="H147" s="1">
         <f t="shared" si="10"/>
-        <v>7.5755992581503824</v>
+        <v>7.4277032607795972</v>
       </c>
       <c r="I147" s="1">
         <f t="shared" si="11"/>
-        <v>0.16272</v>
+        <v>0.16176000000000004</v>
       </c>
       <c r="J147">
         <v>6.78</v>
@@ -7682,15 +7682,15 @@
       </c>
       <c r="G148" s="1">
         <f t="shared" si="9"/>
-        <v>58.2</v>
+        <v>57.400000000000006</v>
       </c>
       <c r="H148" s="1">
         <f t="shared" si="10"/>
-        <v>7.1403152634499385</v>
+        <v>7.000694349538926</v>
       </c>
       <c r="I148" s="1">
         <f t="shared" si="11"/>
-        <v>0.15984000000000001</v>
+        <v>0.15888000000000002</v>
       </c>
       <c r="J148">
         <v>6.78</v>
@@ -7727,15 +7727,15 @@
       </c>
       <c r="G149" s="1">
         <f t="shared" si="9"/>
-        <v>63</v>
+        <v>61.8</v>
       </c>
       <c r="H149" s="1">
         <f t="shared" si="10"/>
-        <v>8.0369126120871375</v>
+        <v>7.8028850219537587</v>
       </c>
       <c r="I149" s="1">
         <f t="shared" si="11"/>
-        <v>0.11040000000000001</v>
+        <v>0.10944000000000004</v>
       </c>
       <c r="J149">
         <v>6.78</v>
@@ -7772,15 +7772,15 @@
       </c>
       <c r="G150" s="1">
         <f t="shared" si="9"/>
-        <v>60.6</v>
+        <v>59.4</v>
       </c>
       <c r="H150" s="1">
         <f t="shared" si="10"/>
-        <v>7.5755992581503824</v>
+        <v>7.3548180837209305</v>
       </c>
       <c r="I150" s="1">
         <f t="shared" si="11"/>
-        <v>0.10848000000000001</v>
+        <v>0.10752000000000002</v>
       </c>
       <c r="J150">
         <v>6.78</v>
@@ -7817,15 +7817,15 @@
       </c>
       <c r="G151" s="1">
         <f t="shared" si="9"/>
-        <v>58.2</v>
+        <v>57</v>
       </c>
       <c r="H151" s="1">
         <f t="shared" si="10"/>
-        <v>7.1403152634499385</v>
+        <v>6.9318749334216623</v>
       </c>
       <c r="I151" s="1">
         <f t="shared" si="11"/>
-        <v>0.10656000000000002</v>
+        <v>0.10560000000000001</v>
       </c>
       <c r="J151">
         <v>6.78</v>
@@ -7862,15 +7862,15 @@
       </c>
       <c r="G152" s="1">
         <f t="shared" si="9"/>
-        <v>55.8</v>
+        <v>54.599999999999994</v>
       </c>
       <c r="H152" s="1">
         <f t="shared" si="10"/>
-        <v>6.7292910134398731</v>
+        <v>6.5323666589469571</v>
       </c>
       <c r="I152" s="1">
         <f t="shared" si="11"/>
-        <v>0.10464000000000004</v>
+        <v>0.10368000000000001</v>
       </c>
       <c r="J152">
         <v>6.78</v>
@@ -7907,15 +7907,15 @@
       </c>
       <c r="G153" s="1">
         <f t="shared" si="9"/>
-        <v>60.599999999999994</v>
+        <v>58.999999999999993</v>
       </c>
       <c r="H153" s="1">
         <f t="shared" si="10"/>
-        <v>7.5755992581503824</v>
+        <v>7.2826304162539381</v>
       </c>
       <c r="I153" s="1">
         <f t="shared" si="11"/>
-        <v>8.1360000000000002E-2</v>
+        <v>8.0400000000000013E-2</v>
       </c>
       <c r="J153">
         <v>6.78</v>
@@ -7952,15 +7952,15 @@
       </c>
       <c r="G154" s="1">
         <f t="shared" si="9"/>
-        <v>58.2</v>
+        <v>56.6</v>
       </c>
       <c r="H154" s="1">
         <f t="shared" si="10"/>
-        <v>7.1403152634499385</v>
+        <v>6.8637061535571284</v>
       </c>
       <c r="I154" s="1">
         <f t="shared" si="11"/>
-        <v>7.9920000000000005E-2</v>
+        <v>7.8960000000000002E-2</v>
       </c>
       <c r="J154">
         <v>6.78</v>
@@ -7997,15 +7997,15 @@
       </c>
       <c r="G155" s="1">
         <f t="shared" si="9"/>
-        <v>55.8</v>
+        <v>54.199999999999996</v>
       </c>
       <c r="H155" s="1">
         <f t="shared" si="10"/>
-        <v>6.7292910134398731</v>
+        <v>6.4679501320457655</v>
       </c>
       <c r="I155" s="1">
         <f t="shared" si="11"/>
-        <v>7.8480000000000022E-2</v>
+        <v>7.7520000000000006E-2</v>
       </c>
       <c r="J155">
         <v>6.78</v>
@@ -8042,15 +8042,15 @@
       </c>
       <c r="G156" s="1">
         <f t="shared" si="9"/>
-        <v>53.4</v>
+        <v>51.8</v>
       </c>
       <c r="H156" s="1">
         <f t="shared" si="10"/>
-        <v>6.3409137493787631</v>
+        <v>6.0938445770101399</v>
       </c>
       <c r="I156" s="1">
         <f t="shared" si="11"/>
-        <v>7.7040000000000011E-2</v>
+        <v>7.6080000000000009E-2</v>
       </c>
       <c r="J156">
         <v>6.78</v>
@@ -8087,15 +8087,15 @@
       </c>
       <c r="G157" s="1">
         <f t="shared" si="9"/>
-        <v>58.2</v>
+        <v>56.2</v>
       </c>
       <c r="H157" s="1">
         <f t="shared" si="10"/>
-        <v>7.1403152634499385</v>
+        <v>6.7961806097083119</v>
       </c>
       <c r="I157" s="1">
         <f t="shared" si="11"/>
-        <v>6.3936000000000007E-2</v>
+        <v>6.2976000000000004E-2</v>
       </c>
       <c r="J157">
         <v>6.78</v>
@@ -8132,15 +8132,15 @@
       </c>
       <c r="G158" s="1">
         <f t="shared" si="9"/>
-        <v>55.8</v>
+        <v>53.8</v>
       </c>
       <c r="H158" s="1">
         <f t="shared" si="10"/>
-        <v>6.7292910134398731</v>
+        <v>6.4041347155842203</v>
       </c>
       <c r="I158" s="1">
         <f t="shared" si="11"/>
-        <v>6.278400000000002E-2</v>
+        <v>6.1824000000000011E-2</v>
       </c>
       <c r="J158">
         <v>6.78</v>
@@ -8177,15 +8177,15 @@
       </c>
       <c r="G159" s="1">
         <f t="shared" si="9"/>
-        <v>53.4</v>
+        <v>51.4</v>
       </c>
       <c r="H159" s="1">
         <f t="shared" si="10"/>
-        <v>6.3409137493787631</v>
+        <v>6.0334993282830611</v>
       </c>
       <c r="I159" s="1">
         <f t="shared" si="11"/>
-        <v>6.1632000000000013E-2</v>
+        <v>6.0672000000000011E-2</v>
       </c>
       <c r="J159">
         <v>6.78</v>
@@ -8222,15 +8222,15 @@
       </c>
       <c r="G160" s="1">
         <f t="shared" si="9"/>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H160" s="1">
         <f t="shared" si="10"/>
-        <v>5.9737105657894727</v>
+        <v>5.6829066702225868</v>
       </c>
       <c r="I160" s="1">
         <f t="shared" si="11"/>
-        <v>6.0480000000000013E-2</v>
+        <v>5.952000000000001E-2</v>
       </c>
       <c r="J160">
         <v>6.78</v>
@@ -8267,15 +8267,15 @@
       </c>
       <c r="G161" s="1">
         <f t="shared" si="9"/>
-        <v>70.400000000000006</v>
+        <v>69.600000000000009</v>
       </c>
       <c r="H161" s="1">
         <f t="shared" si="10"/>
-        <v>9.2300173967747803</v>
+        <v>9.0610791384421798</v>
       </c>
       <c r="I161" s="1">
         <f t="shared" si="11"/>
-        <v>0.18048000000000003</v>
+        <v>0.17952000000000004</v>
       </c>
       <c r="J161">
         <v>6.78</v>
@@ -8312,15 +8312,15 @@
       </c>
       <c r="G162" s="1">
         <f t="shared" si="9"/>
-        <v>68</v>
+        <v>67.2</v>
       </c>
       <c r="H162" s="1">
         <f t="shared" si="10"/>
-        <v>8.7324944359371539</v>
+        <v>8.5727067862262789</v>
       </c>
       <c r="I162" s="1">
         <f t="shared" si="11"/>
-        <v>0.17760000000000001</v>
+        <v>0.17663999999999999</v>
       </c>
       <c r="J162">
         <v>6.78</v>
@@ -8357,15 +8357,15 @@
       </c>
       <c r="G163" s="1">
         <f t="shared" si="9"/>
-        <v>65.599999999999994</v>
+        <v>64.8</v>
       </c>
       <c r="H163" s="1">
         <f t="shared" si="10"/>
-        <v>8.2618037291338577</v>
+        <v>8.110559468922574</v>
       </c>
       <c r="I163" s="1">
         <f t="shared" si="11"/>
-        <v>0.17472000000000001</v>
+        <v>0.17376000000000003</v>
       </c>
       <c r="J163">
         <v>6.78</v>
@@ -8402,15 +8402,15 @@
       </c>
       <c r="G164" s="1">
         <f t="shared" si="9"/>
-        <v>63.2</v>
+        <v>62.400000000000006</v>
       </c>
       <c r="H164" s="1">
         <f t="shared" si="10"/>
-        <v>7.8161775016629269</v>
+        <v>7.6729219727463658</v>
       </c>
       <c r="I164" s="1">
         <f t="shared" si="11"/>
-        <v>0.17184000000000002</v>
+        <v>0.17088000000000003</v>
       </c>
       <c r="J164">
         <v>6.78</v>
@@ -8447,15 +8447,15 @@
       </c>
       <c r="G165" s="1">
         <f t="shared" si="9"/>
-        <v>68</v>
+        <v>66.8</v>
       </c>
       <c r="H165" s="1">
         <f t="shared" si="10"/>
-        <v>8.7324944359371539</v>
+        <v>8.493909300216588</v>
       </c>
       <c r="I165" s="1">
         <f t="shared" si="11"/>
-        <v>0.11840000000000001</v>
+        <v>0.11744000000000003</v>
       </c>
       <c r="J165">
         <v>6.78</v>
@@ -8492,15 +8492,15 @@
       </c>
       <c r="G166" s="1">
         <f t="shared" si="9"/>
-        <v>65.599999999999994</v>
+        <v>64.399999999999991</v>
       </c>
       <c r="H166" s="1">
         <f t="shared" si="10"/>
-        <v>8.2618037291338577</v>
+        <v>8.035961908152391</v>
       </c>
       <c r="I166" s="1">
         <f t="shared" si="11"/>
-        <v>0.11648000000000001</v>
+        <v>0.11551999999999998</v>
       </c>
       <c r="J166">
         <v>6.78</v>
@@ -8537,15 +8537,15 @@
       </c>
       <c r="G167" s="1">
         <f t="shared" si="9"/>
-        <v>63.2</v>
+        <v>62</v>
       </c>
       <c r="H167" s="1">
         <f t="shared" si="10"/>
-        <v>7.8161775016629269</v>
+        <v>7.6022531382232916</v>
       </c>
       <c r="I167" s="1">
         <f t="shared" si="11"/>
-        <v>0.11456000000000001</v>
+        <v>0.11360000000000001</v>
       </c>
       <c r="J167">
         <v>6.78</v>
@@ -8582,15 +8582,15 @@
       </c>
       <c r="G168" s="1">
         <f t="shared" si="9"/>
-        <v>60.8</v>
+        <v>59.599999999999994</v>
       </c>
       <c r="H168" s="1">
         <f t="shared" si="10"/>
-        <v>7.3939999289831064</v>
+        <v>7.1912370168240365</v>
       </c>
       <c r="I168" s="1">
         <f t="shared" si="11"/>
-        <v>0.11264000000000003</v>
+        <v>0.11168000000000002</v>
       </c>
       <c r="J168">
         <v>6.78</v>
@@ -8627,15 +8627,15 @@
       </c>
       <c r="G169" s="1">
         <f t="shared" si="9"/>
-        <v>65.599999999999994</v>
+        <v>63.999999999999993</v>
       </c>
       <c r="H169" s="1">
         <f t="shared" si="10"/>
-        <v>8.2618037291338577</v>
+        <v>7.9620373196930929</v>
       </c>
       <c r="I169" s="1">
         <f t="shared" si="11"/>
-        <v>8.7360000000000007E-2</v>
+        <v>8.6400000000000005E-2</v>
       </c>
       <c r="J169">
         <v>6.78</v>
@@ -8672,15 +8672,15 @@
       </c>
       <c r="G170" s="1">
         <f t="shared" si="9"/>
-        <v>63.2</v>
+        <v>61.6</v>
       </c>
       <c r="H170" s="1">
         <f t="shared" si="10"/>
-        <v>7.8161775016629269</v>
+        <v>7.5322143658701348</v>
       </c>
       <c r="I170" s="1">
         <f t="shared" si="11"/>
-        <v>8.592000000000001E-2</v>
+        <v>8.4960000000000008E-2</v>
       </c>
       <c r="J170">
         <v>6.78</v>
@@ -8717,15 +8717,15 @@
       </c>
       <c r="G171" s="1">
         <f t="shared" si="9"/>
-        <v>60.8</v>
+        <v>59.199999999999996</v>
       </c>
       <c r="H171" s="1">
         <f t="shared" si="10"/>
-        <v>7.3939999289831064</v>
+        <v>7.1248392899338704</v>
       </c>
       <c r="I171" s="1">
         <f t="shared" si="11"/>
-        <v>8.4480000000000013E-2</v>
+        <v>8.3520000000000011E-2</v>
       </c>
       <c r="J171">
         <v>6.78</v>
@@ -8762,15 +8762,15 @@
       </c>
       <c r="G172" s="1">
         <f t="shared" si="9"/>
-        <v>58.4</v>
+        <v>56.8</v>
       </c>
       <c r="H172" s="1">
         <f t="shared" si="10"/>
-        <v>6.9937911539540352</v>
+        <v>6.7385149880801061</v>
       </c>
       <c r="I172" s="1">
         <f t="shared" si="11"/>
-        <v>8.3040000000000003E-2</v>
+        <v>8.2080000000000014E-2</v>
       </c>
       <c r="J172">
         <v>6.78</v>
@@ -8807,15 +8807,15 @@
       </c>
       <c r="G173" s="1">
         <f t="shared" si="9"/>
-        <v>63.2</v>
+        <v>61.2</v>
       </c>
       <c r="H173" s="1">
         <f t="shared" si="10"/>
-        <v>7.8161775016629269</v>
+        <v>7.4627988616816587</v>
       </c>
       <c r="I173" s="1">
         <f t="shared" si="11"/>
-        <v>6.8736000000000005E-2</v>
+        <v>6.7776000000000003E-2</v>
       </c>
       <c r="J173">
         <v>6.78</v>
@@ -8852,15 +8852,15 @@
       </c>
       <c r="G174" s="1">
         <f t="shared" si="9"/>
-        <v>60.8</v>
+        <v>58.8</v>
       </c>
       <c r="H174" s="1">
         <f t="shared" si="10"/>
-        <v>7.3939999289831064</v>
+        <v>7.059026051609754</v>
       </c>
       <c r="I174" s="1">
         <f t="shared" si="11"/>
-        <v>6.7584000000000019E-2</v>
+        <v>6.6624000000000017E-2</v>
       </c>
       <c r="J174">
         <v>6.78</v>
@@ -8897,15 +8897,15 @@
       </c>
       <c r="G175" s="1">
         <f t="shared" si="9"/>
-        <v>58.4</v>
+        <v>56.4</v>
       </c>
       <c r="H175" s="1">
         <f t="shared" si="10"/>
-        <v>6.9937911539540352</v>
+        <v>6.6760825308104454</v>
       </c>
       <c r="I175" s="1">
         <f t="shared" si="11"/>
-        <v>6.6432000000000005E-2</v>
+        <v>6.5472000000000016E-2</v>
       </c>
       <c r="J175">
         <v>6.78</v>
@@ -8942,15 +8942,15 @@
       </c>
       <c r="G176" s="1">
         <f t="shared" si="9"/>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H176" s="1">
         <f t="shared" si="10"/>
-        <v>6.614193279872965</v>
+        <v>6.3127025678602786</v>
       </c>
       <c r="I176" s="1">
         <f t="shared" si="11"/>
-        <v>6.5280000000000005E-2</v>
+        <v>6.4320000000000016E-2</v>
       </c>
       <c r="J176">
         <v>6.78</v>
@@ -8987,15 +8987,15 @@
       </c>
       <c r="G177" s="1">
         <f t="shared" si="9"/>
-        <v>70.400000000000006</v>
+        <v>69.600000000000009</v>
       </c>
       <c r="H177" s="1">
         <f t="shared" si="10"/>
-        <v>9.2300173967747803</v>
+        <v>9.0610791384421798</v>
       </c>
       <c r="I177" s="1">
         <f t="shared" si="11"/>
-        <v>0.18048000000000003</v>
+        <v>0.17952000000000004</v>
       </c>
       <c r="J177">
         <v>6.78</v>
@@ -9032,15 +9032,15 @@
       </c>
       <c r="G178" s="1">
         <f t="shared" si="9"/>
-        <v>68</v>
+        <v>67.2</v>
       </c>
       <c r="H178" s="1">
         <f t="shared" si="10"/>
-        <v>8.7324944359371539</v>
+        <v>8.5727067862262789</v>
       </c>
       <c r="I178" s="1">
         <f t="shared" si="11"/>
-        <v>0.17760000000000001</v>
+        <v>0.17663999999999999</v>
       </c>
       <c r="J178">
         <v>6.78</v>
@@ -9077,15 +9077,15 @@
       </c>
       <c r="G179" s="1">
         <f t="shared" si="9"/>
-        <v>65.599999999999994</v>
+        <v>64.8</v>
       </c>
       <c r="H179" s="1">
         <f t="shared" si="10"/>
-        <v>8.2618037291338577</v>
+        <v>8.110559468922574</v>
       </c>
       <c r="I179" s="1">
         <f t="shared" si="11"/>
-        <v>0.17472000000000001</v>
+        <v>0.17376000000000003</v>
       </c>
       <c r="J179">
         <v>6.78</v>
@@ -9122,15 +9122,15 @@
       </c>
       <c r="G180" s="1">
         <f t="shared" si="9"/>
-        <v>63.2</v>
+        <v>62.400000000000006</v>
       </c>
       <c r="H180" s="1">
         <f t="shared" si="10"/>
-        <v>7.8161775016629269</v>
+        <v>7.6729219727463658</v>
       </c>
       <c r="I180" s="1">
         <f t="shared" si="11"/>
-        <v>0.17184000000000002</v>
+        <v>0.17088000000000003</v>
       </c>
       <c r="J180">
         <v>6.78</v>
@@ -9167,15 +9167,15 @@
       </c>
       <c r="G181" s="1">
         <f t="shared" si="9"/>
-        <v>68</v>
+        <v>66.8</v>
       </c>
       <c r="H181" s="1">
         <f t="shared" si="10"/>
-        <v>8.7324944359371539</v>
+        <v>8.493909300216588</v>
       </c>
       <c r="I181" s="1">
         <f t="shared" si="11"/>
-        <v>0.11840000000000001</v>
+        <v>0.11744000000000003</v>
       </c>
       <c r="J181">
         <v>6.78</v>
@@ -9212,15 +9212,15 @@
       </c>
       <c r="G182" s="1">
         <f t="shared" si="9"/>
-        <v>65.599999999999994</v>
+        <v>64.399999999999991</v>
       </c>
       <c r="H182" s="1">
         <f t="shared" si="10"/>
-        <v>8.2618037291338577</v>
+        <v>8.035961908152391</v>
       </c>
       <c r="I182" s="1">
         <f t="shared" si="11"/>
-        <v>0.11648000000000001</v>
+        <v>0.11551999999999998</v>
       </c>
       <c r="J182">
         <v>6.78</v>
@@ -9257,15 +9257,15 @@
       </c>
       <c r="G183" s="1">
         <f t="shared" si="9"/>
-        <v>63.2</v>
+        <v>62</v>
       </c>
       <c r="H183" s="1">
         <f t="shared" si="10"/>
-        <v>7.8161775016629269</v>
+        <v>7.6022531382232916</v>
       </c>
       <c r="I183" s="1">
         <f t="shared" si="11"/>
-        <v>0.11456000000000001</v>
+        <v>0.11360000000000001</v>
       </c>
       <c r="J183">
         <v>6.78</v>
@@ -9302,15 +9302,15 @@
       </c>
       <c r="G184" s="1">
         <f t="shared" si="9"/>
-        <v>60.8</v>
+        <v>59.599999999999994</v>
       </c>
       <c r="H184" s="1">
         <f t="shared" si="10"/>
-        <v>7.3939999289831064</v>
+        <v>7.1912370168240365</v>
       </c>
       <c r="I184" s="1">
         <f t="shared" si="11"/>
-        <v>0.11264000000000003</v>
+        <v>0.11168000000000002</v>
       </c>
       <c r="J184">
         <v>6.78</v>
@@ -9347,15 +9347,15 @@
       </c>
       <c r="G185" s="1">
         <f t="shared" si="9"/>
-        <v>65.599999999999994</v>
+        <v>63.999999999999993</v>
       </c>
       <c r="H185" s="1">
         <f t="shared" si="10"/>
-        <v>8.2618037291338577</v>
+        <v>7.9620373196930929</v>
       </c>
       <c r="I185" s="1">
         <f t="shared" si="11"/>
-        <v>8.7360000000000007E-2</v>
+        <v>8.6400000000000005E-2</v>
       </c>
       <c r="J185">
         <v>6.78</v>
@@ -9392,15 +9392,15 @@
       </c>
       <c r="G186" s="1">
         <f t="shared" si="9"/>
-        <v>63.2</v>
+        <v>61.6</v>
       </c>
       <c r="H186" s="1">
         <f t="shared" si="10"/>
-        <v>7.8161775016629269</v>
+        <v>7.5322143658701348</v>
       </c>
       <c r="I186" s="1">
         <f t="shared" si="11"/>
-        <v>8.592000000000001E-2</v>
+        <v>8.4960000000000008E-2</v>
       </c>
       <c r="J186">
         <v>6.78</v>
@@ -9437,15 +9437,15 @@
       </c>
       <c r="G187" s="1">
         <f t="shared" si="9"/>
-        <v>60.8</v>
+        <v>59.199999999999996</v>
       </c>
       <c r="H187" s="1">
         <f t="shared" si="10"/>
-        <v>7.3939999289831064</v>
+        <v>7.1248392899338704</v>
       </c>
       <c r="I187" s="1">
         <f t="shared" si="11"/>
-        <v>8.4480000000000013E-2</v>
+        <v>8.3520000000000011E-2</v>
       </c>
       <c r="J187">
         <v>6.78</v>
@@ -9482,15 +9482,15 @@
       </c>
       <c r="G188" s="1">
         <f t="shared" si="9"/>
-        <v>58.4</v>
+        <v>56.8</v>
       </c>
       <c r="H188" s="1">
         <f t="shared" si="10"/>
-        <v>6.9937911539540352</v>
+        <v>6.7385149880801061</v>
       </c>
       <c r="I188" s="1">
         <f t="shared" si="11"/>
-        <v>8.3040000000000003E-2</v>
+        <v>8.2080000000000014E-2</v>
       </c>
       <c r="J188">
         <v>6.78</v>
@@ -9527,15 +9527,15 @@
       </c>
       <c r="G189" s="1">
         <f t="shared" si="9"/>
-        <v>63.2</v>
+        <v>61.2</v>
       </c>
       <c r="H189" s="1">
         <f t="shared" si="10"/>
-        <v>7.8161775016629269</v>
+        <v>7.4627988616816587</v>
       </c>
       <c r="I189" s="1">
         <f t="shared" si="11"/>
-        <v>6.8736000000000005E-2</v>
+        <v>6.7776000000000003E-2</v>
       </c>
       <c r="J189">
         <v>6.78</v>
@@ -9572,15 +9572,15 @@
       </c>
       <c r="G190" s="1">
         <f t="shared" si="9"/>
-        <v>60.8</v>
+        <v>58.8</v>
       </c>
       <c r="H190" s="1">
         <f t="shared" si="10"/>
-        <v>7.3939999289831064</v>
+        <v>7.059026051609754</v>
       </c>
       <c r="I190" s="1">
         <f t="shared" si="11"/>
-        <v>6.7584000000000019E-2</v>
+        <v>6.6624000000000017E-2</v>
       </c>
       <c r="J190">
         <v>6.78</v>
@@ -9617,15 +9617,15 @@
       </c>
       <c r="G191" s="1">
         <f t="shared" si="9"/>
-        <v>58.4</v>
+        <v>56.4</v>
       </c>
       <c r="H191" s="1">
         <f t="shared" si="10"/>
-        <v>6.9937911539540352</v>
+        <v>6.6760825308104454</v>
       </c>
       <c r="I191" s="1">
         <f t="shared" si="11"/>
-        <v>6.6432000000000005E-2</v>
+        <v>6.5472000000000016E-2</v>
       </c>
       <c r="J191">
         <v>6.78</v>
@@ -9662,15 +9662,15 @@
       </c>
       <c r="G192" s="1">
         <f t="shared" si="9"/>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H192" s="1">
         <f t="shared" si="10"/>
-        <v>6.614193279872965</v>
+        <v>6.3127025678602786</v>
       </c>
       <c r="I192" s="1">
         <f t="shared" si="11"/>
-        <v>6.5280000000000005E-2</v>
+        <v>6.4320000000000016E-2</v>
       </c>
       <c r="J192">
         <v>6.78</v>
@@ -9707,15 +9707,15 @@
       </c>
       <c r="G193" s="1">
         <f t="shared" si="9"/>
-        <v>53.599999999999994</v>
+        <v>51.199999999999996</v>
       </c>
       <c r="H193" s="1">
         <f t="shared" si="10"/>
-        <v>6.2539580601034634</v>
+        <v>5.9119360492908335</v>
       </c>
       <c r="I193" s="1">
         <f t="shared" si="11"/>
-        <v>5.3440000000000008E-2</v>
+        <v>5.2480000000000006E-2</v>
       </c>
       <c r="J193">
         <v>6.78</v>
@@ -9752,15 +9752,15 @@
       </c>
       <c r="G194" s="1">
         <f t="shared" si="9"/>
-        <v>70.400000000000006</v>
+        <v>69.600000000000009</v>
       </c>
       <c r="H194" s="1">
         <f t="shared" si="10"/>
-        <v>9.2300173967747803</v>
+        <v>9.0610791384421798</v>
       </c>
       <c r="I194" s="1">
         <f t="shared" si="11"/>
-        <v>0.18048000000000003</v>
+        <v>0.17952000000000004</v>
       </c>
       <c r="J194">
         <v>6.78</v>
@@ -9796,16 +9796,16 @@
         <v>80</v>
       </c>
       <c r="G195" s="1">
-        <f t="shared" ref="G195:G258" si="13">F195-(A195-1)*2*(C195+E195)</f>
-        <v>68</v>
+        <f t="shared" ref="G195:G258" si="13">F195-(A195-1)*2*(C195+E195)-2*C195</f>
+        <v>67.2</v>
       </c>
       <c r="H195" s="1">
         <f t="shared" ref="H195:H258" si="14">2.34*0.000001257*(0.5*A195^2*(F195+G195))/(1+2.73*(F195-G195)/(F195+G195))*1000</f>
-        <v>8.7324944359371539</v>
+        <v>8.5727067862262789</v>
       </c>
       <c r="I195" s="1">
         <f t="shared" ref="I195:I258" si="15">0.0000000168*4*0.5*(F195+G195)/(0.00007*C195)</f>
-        <v>0.17760000000000001</v>
+        <v>0.17663999999999999</v>
       </c>
       <c r="J195">
         <v>6.78</v>
@@ -9842,15 +9842,15 @@
       </c>
       <c r="G196" s="1">
         <f t="shared" si="13"/>
-        <v>65.599999999999994</v>
+        <v>64.8</v>
       </c>
       <c r="H196" s="1">
         <f t="shared" si="14"/>
-        <v>8.2618037291338577</v>
+        <v>8.110559468922574</v>
       </c>
       <c r="I196" s="1">
         <f t="shared" si="15"/>
-        <v>0.17472000000000001</v>
+        <v>0.17376000000000003</v>
       </c>
       <c r="J196">
         <v>6.78</v>
@@ -9887,15 +9887,15 @@
       </c>
       <c r="G197" s="1">
         <f t="shared" si="13"/>
-        <v>63.2</v>
+        <v>62.400000000000006</v>
       </c>
       <c r="H197" s="1">
         <f t="shared" si="14"/>
-        <v>7.8161775016629269</v>
+        <v>7.6729219727463658</v>
       </c>
       <c r="I197" s="1">
         <f t="shared" si="15"/>
-        <v>0.17184000000000002</v>
+        <v>0.17088000000000003</v>
       </c>
       <c r="J197">
         <v>6.78</v>
@@ -9932,15 +9932,15 @@
       </c>
       <c r="G198" s="1">
         <f t="shared" si="13"/>
-        <v>68</v>
+        <v>66.8</v>
       </c>
       <c r="H198" s="1">
         <f t="shared" si="14"/>
-        <v>8.7324944359371539</v>
+        <v>8.493909300216588</v>
       </c>
       <c r="I198" s="1">
         <f t="shared" si="15"/>
-        <v>0.11840000000000001</v>
+        <v>0.11744000000000003</v>
       </c>
       <c r="J198">
         <v>6.78</v>
@@ -9977,15 +9977,15 @@
       </c>
       <c r="G199" s="1">
         <f t="shared" si="13"/>
-        <v>65.599999999999994</v>
+        <v>64.399999999999991</v>
       </c>
       <c r="H199" s="1">
         <f t="shared" si="14"/>
-        <v>8.2618037291338577</v>
+        <v>8.035961908152391</v>
       </c>
       <c r="I199" s="1">
         <f t="shared" si="15"/>
-        <v>0.11648000000000001</v>
+        <v>0.11551999999999998</v>
       </c>
       <c r="J199">
         <v>6.78</v>
@@ -10022,15 +10022,15 @@
       </c>
       <c r="G200" s="1">
         <f t="shared" si="13"/>
-        <v>63.2</v>
+        <v>62</v>
       </c>
       <c r="H200" s="1">
         <f t="shared" si="14"/>
-        <v>7.8161775016629269</v>
+        <v>7.6022531382232916</v>
       </c>
       <c r="I200" s="1">
         <f t="shared" si="15"/>
-        <v>0.11456000000000001</v>
+        <v>0.11360000000000001</v>
       </c>
       <c r="J200">
         <v>6.78</v>
@@ -10067,15 +10067,15 @@
       </c>
       <c r="G201" s="1">
         <f t="shared" si="13"/>
-        <v>60.8</v>
+        <v>59.599999999999994</v>
       </c>
       <c r="H201" s="1">
         <f t="shared" si="14"/>
-        <v>7.3939999289831064</v>
+        <v>7.1912370168240365</v>
       </c>
       <c r="I201" s="1">
         <f t="shared" si="15"/>
-        <v>0.11264000000000003</v>
+        <v>0.11168000000000002</v>
       </c>
       <c r="J201">
         <v>6.78</v>
@@ -10112,15 +10112,15 @@
       </c>
       <c r="G202" s="1">
         <f t="shared" si="13"/>
-        <v>65.599999999999994</v>
+        <v>63.999999999999993</v>
       </c>
       <c r="H202" s="1">
         <f t="shared" si="14"/>
-        <v>8.2618037291338577</v>
+        <v>7.9620373196930929</v>
       </c>
       <c r="I202" s="1">
         <f t="shared" si="15"/>
-        <v>8.7360000000000007E-2</v>
+        <v>8.6400000000000005E-2</v>
       </c>
       <c r="J202">
         <v>6.78</v>
@@ -10157,15 +10157,15 @@
       </c>
       <c r="G203" s="1">
         <f t="shared" si="13"/>
-        <v>63.2</v>
+        <v>61.6</v>
       </c>
       <c r="H203" s="1">
         <f t="shared" si="14"/>
-        <v>7.8161775016629269</v>
+        <v>7.5322143658701348</v>
       </c>
       <c r="I203" s="1">
         <f t="shared" si="15"/>
-        <v>8.592000000000001E-2</v>
+        <v>8.4960000000000008E-2</v>
       </c>
       <c r="J203">
         <v>6.78</v>
@@ -10202,15 +10202,15 @@
       </c>
       <c r="G204" s="1">
         <f t="shared" si="13"/>
-        <v>60.8</v>
+        <v>59.199999999999996</v>
       </c>
       <c r="H204" s="1">
         <f t="shared" si="14"/>
-        <v>7.3939999289831064</v>
+        <v>7.1248392899338704</v>
       </c>
       <c r="I204" s="1">
         <f t="shared" si="15"/>
-        <v>8.4480000000000013E-2</v>
+        <v>8.3520000000000011E-2</v>
       </c>
       <c r="J204">
         <v>6.78</v>
@@ -10247,15 +10247,15 @@
       </c>
       <c r="G205" s="1">
         <f t="shared" si="13"/>
-        <v>58.4</v>
+        <v>56.8</v>
       </c>
       <c r="H205" s="1">
         <f t="shared" si="14"/>
-        <v>6.9937911539540352</v>
+        <v>6.7385149880801061</v>
       </c>
       <c r="I205" s="1">
         <f t="shared" si="15"/>
-        <v>8.3040000000000003E-2</v>
+        <v>8.2080000000000014E-2</v>
       </c>
       <c r="J205">
         <v>6.78</v>
@@ -10292,15 +10292,15 @@
       </c>
       <c r="G206" s="1">
         <f t="shared" si="13"/>
-        <v>63.2</v>
+        <v>61.2</v>
       </c>
       <c r="H206" s="1">
         <f t="shared" si="14"/>
-        <v>7.8161775016629269</v>
+        <v>7.4627988616816587</v>
       </c>
       <c r="I206" s="1">
         <f t="shared" si="15"/>
-        <v>6.8736000000000005E-2</v>
+        <v>6.7776000000000003E-2</v>
       </c>
       <c r="J206">
         <v>6.78</v>
@@ -10337,15 +10337,15 @@
       </c>
       <c r="G207" s="1">
         <f t="shared" si="13"/>
-        <v>60.8</v>
+        <v>58.8</v>
       </c>
       <c r="H207" s="1">
         <f t="shared" si="14"/>
-        <v>7.3939999289831064</v>
+        <v>7.059026051609754</v>
       </c>
       <c r="I207" s="1">
         <f t="shared" si="15"/>
-        <v>6.7584000000000019E-2</v>
+        <v>6.6624000000000017E-2</v>
       </c>
       <c r="J207">
         <v>6.78</v>
@@ -10382,15 +10382,15 @@
       </c>
       <c r="G208" s="1">
         <f t="shared" si="13"/>
-        <v>58.4</v>
+        <v>56.4</v>
       </c>
       <c r="H208" s="1">
         <f t="shared" si="14"/>
-        <v>6.9937911539540352</v>
+        <v>6.6760825308104454</v>
       </c>
       <c r="I208" s="1">
         <f t="shared" si="15"/>
-        <v>6.6432000000000005E-2</v>
+        <v>6.5472000000000016E-2</v>
       </c>
       <c r="J208">
         <v>6.78</v>
@@ -10427,15 +10427,15 @@
       </c>
       <c r="G209" s="1">
         <f t="shared" si="13"/>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H209" s="1">
         <f t="shared" si="14"/>
-        <v>6.614193279872965</v>
+        <v>6.3127025678602786</v>
       </c>
       <c r="I209" s="1">
         <f t="shared" si="15"/>
-        <v>6.5280000000000005E-2</v>
+        <v>6.4320000000000016E-2</v>
       </c>
       <c r="J209">
         <v>6.78</v>
@@ -10472,15 +10472,15 @@
       </c>
       <c r="G210" s="1">
         <f t="shared" si="13"/>
-        <v>70.400000000000006</v>
+        <v>69.600000000000009</v>
       </c>
       <c r="H210" s="1">
         <f t="shared" si="14"/>
-        <v>9.2300173967747803</v>
+        <v>9.0610791384421798</v>
       </c>
       <c r="I210" s="1">
         <f t="shared" si="15"/>
-        <v>0.18048000000000003</v>
+        <v>0.17952000000000004</v>
       </c>
       <c r="J210">
         <v>6.78</v>
@@ -10517,15 +10517,15 @@
       </c>
       <c r="G211" s="1">
         <f t="shared" si="13"/>
-        <v>68</v>
+        <v>67.2</v>
       </c>
       <c r="H211" s="1">
         <f t="shared" si="14"/>
-        <v>8.7324944359371539</v>
+        <v>8.5727067862262789</v>
       </c>
       <c r="I211" s="1">
         <f t="shared" si="15"/>
-        <v>0.17760000000000001</v>
+        <v>0.17663999999999999</v>
       </c>
       <c r="J211">
         <v>6.78</v>
@@ -10562,15 +10562,15 @@
       </c>
       <c r="G212" s="1">
         <f t="shared" si="13"/>
-        <v>65.599999999999994</v>
+        <v>64.8</v>
       </c>
       <c r="H212" s="1">
         <f t="shared" si="14"/>
-        <v>8.2618037291338577</v>
+        <v>8.110559468922574</v>
       </c>
       <c r="I212" s="1">
         <f t="shared" si="15"/>
-        <v>0.17472000000000001</v>
+        <v>0.17376000000000003</v>
       </c>
       <c r="J212">
         <v>6.78</v>
@@ -10607,15 +10607,15 @@
       </c>
       <c r="G213" s="1">
         <f t="shared" si="13"/>
-        <v>63.2</v>
+        <v>62.400000000000006</v>
       </c>
       <c r="H213" s="1">
         <f t="shared" si="14"/>
-        <v>7.8161775016629269</v>
+        <v>7.6729219727463658</v>
       </c>
       <c r="I213" s="1">
         <f t="shared" si="15"/>
-        <v>0.17184000000000002</v>
+        <v>0.17088000000000003</v>
       </c>
       <c r="J213">
         <v>6.78</v>
@@ -10652,15 +10652,15 @@
       </c>
       <c r="G214" s="1">
         <f t="shared" si="13"/>
-        <v>68</v>
+        <v>66.8</v>
       </c>
       <c r="H214" s="1">
         <f t="shared" si="14"/>
-        <v>8.7324944359371539</v>
+        <v>8.493909300216588</v>
       </c>
       <c r="I214" s="1">
         <f t="shared" si="15"/>
-        <v>0.11840000000000001</v>
+        <v>0.11744000000000003</v>
       </c>
       <c r="J214">
         <v>6.78</v>
@@ -10697,15 +10697,15 @@
       </c>
       <c r="G215" s="1">
         <f t="shared" si="13"/>
-        <v>65.599999999999994</v>
+        <v>64.399999999999991</v>
       </c>
       <c r="H215" s="1">
         <f t="shared" si="14"/>
-        <v>8.2618037291338577</v>
+        <v>8.035961908152391</v>
       </c>
       <c r="I215" s="1">
         <f t="shared" si="15"/>
-        <v>0.11648000000000001</v>
+        <v>0.11551999999999998</v>
       </c>
       <c r="J215">
         <v>6.78</v>
@@ -10742,15 +10742,15 @@
       </c>
       <c r="G216" s="1">
         <f t="shared" si="13"/>
-        <v>63.2</v>
+        <v>62</v>
       </c>
       <c r="H216" s="1">
         <f t="shared" si="14"/>
-        <v>7.8161775016629269</v>
+        <v>7.6022531382232916</v>
       </c>
       <c r="I216" s="1">
         <f t="shared" si="15"/>
-        <v>0.11456000000000001</v>
+        <v>0.11360000000000001</v>
       </c>
       <c r="J216">
         <v>6.78</v>
@@ -10787,15 +10787,15 @@
       </c>
       <c r="G217" s="1">
         <f t="shared" si="13"/>
-        <v>60.8</v>
+        <v>59.599999999999994</v>
       </c>
       <c r="H217" s="1">
         <f t="shared" si="14"/>
-        <v>7.3939999289831064</v>
+        <v>7.1912370168240365</v>
       </c>
       <c r="I217" s="1">
         <f t="shared" si="15"/>
-        <v>0.11264000000000003</v>
+        <v>0.11168000000000002</v>
       </c>
       <c r="J217">
         <v>6.78</v>
@@ -10832,15 +10832,15 @@
       </c>
       <c r="G218" s="1">
         <f t="shared" si="13"/>
-        <v>65.599999999999994</v>
+        <v>63.999999999999993</v>
       </c>
       <c r="H218" s="1">
         <f t="shared" si="14"/>
-        <v>8.2618037291338577</v>
+        <v>7.9620373196930929</v>
       </c>
       <c r="I218" s="1">
         <f t="shared" si="15"/>
-        <v>8.7360000000000007E-2</v>
+        <v>8.6400000000000005E-2</v>
       </c>
       <c r="J218">
         <v>6.78</v>
@@ -10877,15 +10877,15 @@
       </c>
       <c r="G219" s="1">
         <f t="shared" si="13"/>
-        <v>63.2</v>
+        <v>61.6</v>
       </c>
       <c r="H219" s="1">
         <f t="shared" si="14"/>
-        <v>7.8161775016629269</v>
+        <v>7.5322143658701348</v>
       </c>
       <c r="I219" s="1">
         <f t="shared" si="15"/>
-        <v>8.592000000000001E-2</v>
+        <v>8.4960000000000008E-2</v>
       </c>
       <c r="J219">
         <v>6.78</v>
@@ -10922,15 +10922,15 @@
       </c>
       <c r="G220" s="1">
         <f t="shared" si="13"/>
-        <v>60.8</v>
+        <v>59.199999999999996</v>
       </c>
       <c r="H220" s="1">
         <f t="shared" si="14"/>
-        <v>7.3939999289831064</v>
+        <v>7.1248392899338704</v>
       </c>
       <c r="I220" s="1">
         <f t="shared" si="15"/>
-        <v>8.4480000000000013E-2</v>
+        <v>8.3520000000000011E-2</v>
       </c>
       <c r="J220">
         <v>6.78</v>
@@ -10967,15 +10967,15 @@
       </c>
       <c r="G221" s="1">
         <f t="shared" si="13"/>
-        <v>58.4</v>
+        <v>56.8</v>
       </c>
       <c r="H221" s="1">
         <f t="shared" si="14"/>
-        <v>6.9937911539540352</v>
+        <v>6.7385149880801061</v>
       </c>
       <c r="I221" s="1">
         <f t="shared" si="15"/>
-        <v>8.3040000000000003E-2</v>
+        <v>8.2080000000000014E-2</v>
       </c>
       <c r="J221">
         <v>6.78</v>
@@ -11012,15 +11012,15 @@
       </c>
       <c r="G222" s="1">
         <f t="shared" si="13"/>
-        <v>63.2</v>
+        <v>61.2</v>
       </c>
       <c r="H222" s="1">
         <f t="shared" si="14"/>
-        <v>7.8161775016629269</v>
+        <v>7.4627988616816587</v>
       </c>
       <c r="I222" s="1">
         <f t="shared" si="15"/>
-        <v>6.8736000000000005E-2</v>
+        <v>6.7776000000000003E-2</v>
       </c>
       <c r="J222">
         <v>6.78</v>
@@ -11057,15 +11057,15 @@
       </c>
       <c r="G223" s="1">
         <f t="shared" si="13"/>
-        <v>60.8</v>
+        <v>58.8</v>
       </c>
       <c r="H223" s="1">
         <f t="shared" si="14"/>
-        <v>7.3939999289831064</v>
+        <v>7.059026051609754</v>
       </c>
       <c r="I223" s="1">
         <f t="shared" si="15"/>
-        <v>6.7584000000000019E-2</v>
+        <v>6.6624000000000017E-2</v>
       </c>
       <c r="J223">
         <v>6.78</v>
@@ -11102,15 +11102,15 @@
       </c>
       <c r="G224" s="1">
         <f t="shared" si="13"/>
-        <v>58.4</v>
+        <v>56.4</v>
       </c>
       <c r="H224" s="1">
         <f t="shared" si="14"/>
-        <v>6.9937911539540352</v>
+        <v>6.6760825308104454</v>
       </c>
       <c r="I224" s="1">
         <f t="shared" si="15"/>
-        <v>6.6432000000000005E-2</v>
+        <v>6.5472000000000016E-2</v>
       </c>
       <c r="J224">
         <v>6.78</v>
@@ -11147,15 +11147,15 @@
       </c>
       <c r="G225" s="1">
         <f t="shared" si="13"/>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H225" s="1">
         <f t="shared" si="14"/>
-        <v>6.614193279872965</v>
+        <v>6.3127025678602786</v>
       </c>
       <c r="I225" s="1">
         <f t="shared" si="15"/>
-        <v>6.5280000000000005E-2</v>
+        <v>6.4320000000000016E-2</v>
       </c>
       <c r="J225">
         <v>6.78</v>
@@ -11192,15 +11192,15 @@
       </c>
       <c r="G226" s="1">
         <f t="shared" si="13"/>
-        <v>70.400000000000006</v>
+        <v>69.600000000000009</v>
       </c>
       <c r="H226" s="1">
         <f t="shared" si="14"/>
-        <v>9.2300173967747803</v>
+        <v>9.0610791384421798</v>
       </c>
       <c r="I226" s="1">
         <f t="shared" si="15"/>
-        <v>0.18048000000000003</v>
+        <v>0.17952000000000004</v>
       </c>
       <c r="J226">
         <v>6.78</v>
@@ -11237,15 +11237,15 @@
       </c>
       <c r="G227" s="1">
         <f t="shared" si="13"/>
-        <v>68</v>
+        <v>67.2</v>
       </c>
       <c r="H227" s="1">
         <f t="shared" si="14"/>
-        <v>8.7324944359371539</v>
+        <v>8.5727067862262789</v>
       </c>
       <c r="I227" s="1">
         <f t="shared" si="15"/>
-        <v>0.17760000000000001</v>
+        <v>0.17663999999999999</v>
       </c>
       <c r="J227">
         <v>6.78</v>
@@ -11282,15 +11282,15 @@
       </c>
       <c r="G228" s="1">
         <f t="shared" si="13"/>
-        <v>65.599999999999994</v>
+        <v>64.8</v>
       </c>
       <c r="H228" s="1">
         <f t="shared" si="14"/>
-        <v>8.2618037291338577</v>
+        <v>8.110559468922574</v>
       </c>
       <c r="I228" s="1">
         <f t="shared" si="15"/>
-        <v>0.17472000000000001</v>
+        <v>0.17376000000000003</v>
       </c>
       <c r="J228">
         <v>6.78</v>
@@ -11327,15 +11327,15 @@
       </c>
       <c r="G229" s="1">
         <f t="shared" si="13"/>
-        <v>63.2</v>
+        <v>62.400000000000006</v>
       </c>
       <c r="H229" s="1">
         <f t="shared" si="14"/>
-        <v>7.8161775016629269</v>
+        <v>7.6729219727463658</v>
       </c>
       <c r="I229" s="1">
         <f t="shared" si="15"/>
-        <v>0.17184000000000002</v>
+        <v>0.17088000000000003</v>
       </c>
       <c r="J229">
         <v>6.78</v>
@@ -11372,15 +11372,15 @@
       </c>
       <c r="G230" s="1">
         <f t="shared" si="13"/>
-        <v>68</v>
+        <v>66.8</v>
       </c>
       <c r="H230" s="1">
         <f t="shared" si="14"/>
-        <v>8.7324944359371539</v>
+        <v>8.493909300216588</v>
       </c>
       <c r="I230" s="1">
         <f t="shared" si="15"/>
-        <v>0.11840000000000001</v>
+        <v>0.11744000000000003</v>
       </c>
       <c r="J230">
         <v>6.78</v>
@@ -11417,15 +11417,15 @@
       </c>
       <c r="G231" s="1">
         <f t="shared" si="13"/>
-        <v>65.599999999999994</v>
+        <v>64.399999999999991</v>
       </c>
       <c r="H231" s="1">
         <f t="shared" si="14"/>
-        <v>8.2618037291338577</v>
+        <v>8.035961908152391</v>
       </c>
       <c r="I231" s="1">
         <f t="shared" si="15"/>
-        <v>0.11648000000000001</v>
+        <v>0.11551999999999998</v>
       </c>
       <c r="J231">
         <v>6.78</v>
@@ -11462,15 +11462,15 @@
       </c>
       <c r="G232" s="1">
         <f t="shared" si="13"/>
-        <v>63.2</v>
+        <v>62</v>
       </c>
       <c r="H232" s="1">
         <f t="shared" si="14"/>
-        <v>7.8161775016629269</v>
+        <v>7.6022531382232916</v>
       </c>
       <c r="I232" s="1">
         <f t="shared" si="15"/>
-        <v>0.11456000000000001</v>
+        <v>0.11360000000000001</v>
       </c>
       <c r="J232">
         <v>6.78</v>
@@ -11507,15 +11507,15 @@
       </c>
       <c r="G233" s="1">
         <f t="shared" si="13"/>
-        <v>60.8</v>
+        <v>59.599999999999994</v>
       </c>
       <c r="H233" s="1">
         <f t="shared" si="14"/>
-        <v>7.3939999289831064</v>
+        <v>7.1912370168240365</v>
       </c>
       <c r="I233" s="1">
         <f t="shared" si="15"/>
-        <v>0.11264000000000003</v>
+        <v>0.11168000000000002</v>
       </c>
       <c r="J233">
         <v>6.78</v>
@@ -11552,15 +11552,15 @@
       </c>
       <c r="G234" s="1">
         <f t="shared" si="13"/>
-        <v>65.599999999999994</v>
+        <v>63.999999999999993</v>
       </c>
       <c r="H234" s="1">
         <f t="shared" si="14"/>
-        <v>8.2618037291338577</v>
+        <v>7.9620373196930929</v>
       </c>
       <c r="I234" s="1">
         <f t="shared" si="15"/>
-        <v>8.7360000000000007E-2</v>
+        <v>8.6400000000000005E-2</v>
       </c>
       <c r="J234">
         <v>6.78</v>
@@ -11597,15 +11597,15 @@
       </c>
       <c r="G235" s="1">
         <f t="shared" si="13"/>
-        <v>63.2</v>
+        <v>61.6</v>
       </c>
       <c r="H235" s="1">
         <f t="shared" si="14"/>
-        <v>7.8161775016629269</v>
+        <v>7.5322143658701348</v>
       </c>
       <c r="I235" s="1">
         <f t="shared" si="15"/>
-        <v>8.592000000000001E-2</v>
+        <v>8.4960000000000008E-2</v>
       </c>
       <c r="J235">
         <v>6.78</v>
@@ -11642,15 +11642,15 @@
       </c>
       <c r="G236" s="1">
         <f t="shared" si="13"/>
-        <v>60.8</v>
+        <v>59.199999999999996</v>
       </c>
       <c r="H236" s="1">
         <f t="shared" si="14"/>
-        <v>7.3939999289831064</v>
+        <v>7.1248392899338704</v>
       </c>
       <c r="I236" s="1">
         <f t="shared" si="15"/>
-        <v>8.4480000000000013E-2</v>
+        <v>8.3520000000000011E-2</v>
       </c>
       <c r="J236">
         <v>6.78</v>
@@ -11687,15 +11687,15 @@
       </c>
       <c r="G237" s="1">
         <f t="shared" si="13"/>
-        <v>58.4</v>
+        <v>56.8</v>
       </c>
       <c r="H237" s="1">
         <f t="shared" si="14"/>
-        <v>6.9937911539540352</v>
+        <v>6.7385149880801061</v>
       </c>
       <c r="I237" s="1">
         <f t="shared" si="15"/>
-        <v>8.3040000000000003E-2</v>
+        <v>8.2080000000000014E-2</v>
       </c>
       <c r="J237">
         <v>6.78</v>
@@ -11732,15 +11732,15 @@
       </c>
       <c r="G238" s="1">
         <f t="shared" si="13"/>
-        <v>63.2</v>
+        <v>61.2</v>
       </c>
       <c r="H238" s="1">
         <f t="shared" si="14"/>
-        <v>7.8161775016629269</v>
+        <v>7.4627988616816587</v>
       </c>
       <c r="I238" s="1">
         <f t="shared" si="15"/>
-        <v>6.8736000000000005E-2</v>
+        <v>6.7776000000000003E-2</v>
       </c>
       <c r="J238">
         <v>6.78</v>
@@ -11777,15 +11777,15 @@
       </c>
       <c r="G239" s="1">
         <f t="shared" si="13"/>
-        <v>60.8</v>
+        <v>58.8</v>
       </c>
       <c r="H239" s="1">
         <f t="shared" si="14"/>
-        <v>7.3939999289831064</v>
+        <v>7.059026051609754</v>
       </c>
       <c r="I239" s="1">
         <f t="shared" si="15"/>
-        <v>6.7584000000000019E-2</v>
+        <v>6.6624000000000017E-2</v>
       </c>
       <c r="J239">
         <v>6.78</v>
@@ -11822,15 +11822,15 @@
       </c>
       <c r="G240" s="1">
         <f t="shared" si="13"/>
-        <v>58.4</v>
+        <v>56.4</v>
       </c>
       <c r="H240" s="1">
         <f t="shared" si="14"/>
-        <v>6.9937911539540352</v>
+        <v>6.6760825308104454</v>
       </c>
       <c r="I240" s="1">
         <f t="shared" si="15"/>
-        <v>6.6432000000000005E-2</v>
+        <v>6.5472000000000016E-2</v>
       </c>
       <c r="J240">
         <v>6.78</v>
@@ -11867,15 +11867,15 @@
       </c>
       <c r="G241" s="1">
         <f t="shared" si="13"/>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H241" s="1">
         <f t="shared" si="14"/>
-        <v>6.614193279872965</v>
+        <v>6.3127025678602786</v>
       </c>
       <c r="I241" s="1">
         <f t="shared" si="15"/>
-        <v>6.5280000000000005E-2</v>
+        <v>6.4320000000000016E-2</v>
       </c>
       <c r="J241">
         <v>6.78</v>
@@ -11912,15 +11912,15 @@
       </c>
       <c r="G242" s="1">
         <f t="shared" si="13"/>
-        <v>75.400000000000006</v>
+        <v>74.600000000000009</v>
       </c>
       <c r="H242" s="1">
         <f t="shared" si="14"/>
-        <v>9.9356363815570621</v>
+        <v>9.7643564541554984</v>
       </c>
       <c r="I242" s="1">
         <f t="shared" si="15"/>
-        <v>0.19248000000000004</v>
+        <v>0.19152000000000005</v>
       </c>
       <c r="J242">
         <v>6.78</v>
@@ -11957,15 +11957,15 @@
       </c>
       <c r="G243" s="1">
         <f t="shared" si="13"/>
-        <v>73</v>
+        <v>72.2</v>
       </c>
       <c r="H243" s="1">
         <f t="shared" si="14"/>
-        <v>9.4307032545607044</v>
+        <v>9.2682016743192595</v>
       </c>
       <c r="I243" s="1">
         <f t="shared" si="15"/>
-        <v>0.18960000000000002</v>
+        <v>0.18864</v>
       </c>
       <c r="J243">
         <v>6.78</v>
@@ -12002,15 +12002,15 @@
       </c>
       <c r="G244" s="1">
         <f t="shared" si="13"/>
-        <v>70.599999999999994</v>
+        <v>69.8</v>
       </c>
       <c r="H244" s="1">
         <f t="shared" si="14"/>
-        <v>8.9515414488671805</v>
+        <v>8.7972651586502018</v>
       </c>
       <c r="I244" s="1">
         <f t="shared" si="15"/>
-        <v>0.18672</v>
+        <v>0.18576000000000004</v>
       </c>
       <c r="J244">
         <v>6.78</v>
@@ -12047,15 +12047,15 @@
       </c>
       <c r="G245" s="1">
         <f t="shared" si="13"/>
-        <v>68.2</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="H245" s="1">
         <f t="shared" si="14"/>
-        <v>8.4965383796889427</v>
+        <v>8.3499798239224141</v>
       </c>
       <c r="I245" s="1">
         <f t="shared" si="15"/>
-        <v>0.18384</v>
+        <v>0.18288000000000004</v>
       </c>
       <c r="J245">
         <v>6.78</v>
@@ -12092,15 +12092,15 @@
       </c>
       <c r="G246" s="1">
         <f t="shared" si="13"/>
-        <v>73</v>
+        <v>71.8</v>
       </c>
       <c r="H246" s="1">
         <f t="shared" si="14"/>
-        <v>9.4307032545607044</v>
+        <v>9.1880049781907953</v>
       </c>
       <c r="I246" s="1">
         <f t="shared" si="15"/>
-        <v>0.12640000000000001</v>
+        <v>0.12544000000000002</v>
       </c>
       <c r="J246">
         <v>6.78</v>
@@ -12137,15 +12137,15 @@
       </c>
       <c r="G247" s="1">
         <f t="shared" si="13"/>
-        <v>70.599999999999994</v>
+        <v>69.399999999999991</v>
       </c>
       <c r="H247" s="1">
         <f t="shared" si="14"/>
-        <v>8.9515414488671805</v>
+        <v>8.7211155479602773</v>
       </c>
       <c r="I247" s="1">
         <f t="shared" si="15"/>
-        <v>0.12448000000000001</v>
+        <v>0.12352</v>
       </c>
       <c r="J247">
         <v>6.78</v>
@@ -12182,15 +12182,15 @@
       </c>
       <c r="G248" s="1">
         <f t="shared" si="13"/>
-        <v>68.2</v>
+        <v>67</v>
       </c>
       <c r="H248" s="1">
         <f t="shared" si="14"/>
-        <v>8.4965383796889427</v>
+        <v>8.2776288467733909</v>
       </c>
       <c r="I248" s="1">
         <f t="shared" si="15"/>
-        <v>0.12256</v>
+        <v>0.12160000000000003</v>
       </c>
       <c r="J248">
         <v>6.78</v>
@@ -12227,15 +12227,15 @@
       </c>
       <c r="G249" s="1">
         <f t="shared" si="13"/>
-        <v>65.8</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="H249" s="1">
         <f t="shared" si="14"/>
-        <v>8.064213252098261</v>
+        <v>7.8561249245445515</v>
       </c>
       <c r="I249" s="1">
         <f t="shared" si="15"/>
-        <v>0.12064000000000002</v>
+        <v>0.11968000000000001</v>
       </c>
       <c r="J249">
         <v>6.78</v>
@@ -12272,15 +12272,15 @@
       </c>
       <c r="G250" s="1">
         <f t="shared" si="13"/>
-        <v>70.599999999999994</v>
+        <v>69</v>
       </c>
       <c r="H250" s="1">
         <f t="shared" si="14"/>
-        <v>8.9515414488671805</v>
+        <v>8.6456157322946154</v>
       </c>
       <c r="I250" s="1">
         <f t="shared" si="15"/>
-        <v>9.3359999999999999E-2</v>
+        <v>9.240000000000001E-2</v>
       </c>
       <c r="J250">
         <v>6.78</v>
@@ -12317,15 +12317,15 @@
       </c>
       <c r="G251" s="1">
         <f t="shared" si="13"/>
-        <v>68.2</v>
+        <v>66.600000000000009</v>
       </c>
       <c r="H251" s="1">
         <f t="shared" si="14"/>
-        <v>8.4965383796889427</v>
+        <v>8.2058882494034666</v>
       </c>
       <c r="I251" s="1">
         <f t="shared" si="15"/>
-        <v>9.1920000000000002E-2</v>
+        <v>9.0960000000000013E-2</v>
       </c>
       <c r="J251">
         <v>6.78</v>
@@ -12362,15 +12362,15 @@
       </c>
       <c r="G252" s="1">
         <f t="shared" si="13"/>
-        <v>65.8</v>
+        <v>64.2</v>
       </c>
       <c r="H252" s="1">
         <f t="shared" si="14"/>
-        <v>8.064213252098261</v>
+        <v>7.7879181462560192</v>
       </c>
       <c r="I252" s="1">
         <f t="shared" si="15"/>
-        <v>9.0480000000000019E-2</v>
+        <v>8.9520000000000002E-2</v>
       </c>
       <c r="J252">
         <v>6.78</v>
@@ -12407,15 +12407,15 @@
       </c>
       <c r="G253" s="1">
         <f t="shared" si="13"/>
-        <v>63.4</v>
+        <v>61.8</v>
       </c>
       <c r="H253" s="1">
         <f t="shared" si="14"/>
-        <v>7.6532038672967868</v>
+        <v>7.390415734640424</v>
       </c>
       <c r="I253" s="1">
         <f t="shared" si="15"/>
-        <v>8.9040000000000022E-2</v>
+        <v>8.8080000000000019E-2</v>
       </c>
       <c r="J253">
         <v>6.78</v>
@@ -12452,15 +12452,15 @@
       </c>
       <c r="G254" s="1">
         <f t="shared" si="13"/>
-        <v>68.2</v>
+        <v>66.2</v>
       </c>
       <c r="H254" s="1">
         <f t="shared" si="14"/>
-        <v>8.4965383796889427</v>
+        <v>8.1347517750311056</v>
       </c>
       <c r="I254" s="1">
         <f t="shared" si="15"/>
-        <v>7.3536000000000004E-2</v>
+        <v>7.2576000000000002E-2</v>
       </c>
       <c r="J254">
         <v>6.78</v>
@@ -12497,15 +12497,15 @@
       </c>
       <c r="G255" s="1">
         <f t="shared" si="13"/>
-        <v>65.8</v>
+        <v>63.8</v>
       </c>
       <c r="H255" s="1">
         <f t="shared" si="14"/>
-        <v>8.064213252098261</v>
+        <v>7.7202796903675326</v>
       </c>
       <c r="I255" s="1">
         <f t="shared" si="15"/>
-        <v>7.2384000000000018E-2</v>
+        <v>7.1424000000000015E-2</v>
       </c>
       <c r="J255">
         <v>6.78</v>
@@ -12542,15 +12542,15 @@
       </c>
       <c r="G256" s="1">
         <f t="shared" si="13"/>
-        <v>63.4</v>
+        <v>61.4</v>
       </c>
       <c r="H256" s="1">
         <f t="shared" si="14"/>
-        <v>7.6532038672967868</v>
+        <v>7.3260703377995338</v>
       </c>
       <c r="I256" s="1">
         <f t="shared" si="15"/>
-        <v>7.1232000000000018E-2</v>
+        <v>7.0272000000000015E-2</v>
       </c>
       <c r="J256">
         <v>6.78</v>
@@ -12587,15 +12587,15 @@
       </c>
       <c r="G257" s="1">
         <f t="shared" si="13"/>
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H257" s="1">
         <f t="shared" si="14"/>
-        <v>7.2622549827912248</v>
+        <v>6.9509496890873574</v>
       </c>
       <c r="I257" s="1">
         <f t="shared" si="15"/>
-        <v>7.0080000000000003E-2</v>
+        <v>6.9120000000000015E-2</v>
       </c>
       <c r="J257">
         <v>6.78</v>
@@ -12632,15 +12632,15 @@
       </c>
       <c r="G258" s="1">
         <f t="shared" si="13"/>
-        <v>75.400000000000006</v>
+        <v>74.600000000000009</v>
       </c>
       <c r="H258" s="1">
         <f t="shared" si="14"/>
-        <v>9.9356363815570621</v>
+        <v>9.7643564541554984</v>
       </c>
       <c r="I258" s="1">
         <f t="shared" si="15"/>
-        <v>0.19248000000000004</v>
+        <v>0.19152000000000005</v>
       </c>
       <c r="J258">
         <v>6.78</v>
@@ -12676,16 +12676,16 @@
         <v>85</v>
       </c>
       <c r="G259" s="1">
-        <f t="shared" ref="G259:G322" si="17">F259-(A259-1)*2*(C259+E259)</f>
-        <v>73</v>
+        <f t="shared" ref="G259:G322" si="17">F259-(A259-1)*2*(C259+E259)-2*C259</f>
+        <v>72.2</v>
       </c>
       <c r="H259" s="1">
         <f t="shared" ref="H259:H322" si="18">2.34*0.000001257*(0.5*A259^2*(F259+G259))/(1+2.73*(F259-G259)/(F259+G259))*1000</f>
-        <v>9.4307032545607044</v>
+        <v>9.2682016743192595</v>
       </c>
       <c r="I259" s="1">
         <f t="shared" ref="I259:I322" si="19">0.0000000168*4*0.5*(F259+G259)/(0.00007*C259)</f>
-        <v>0.18960000000000002</v>
+        <v>0.18864</v>
       </c>
       <c r="J259">
         <v>6.78</v>
@@ -12722,15 +12722,15 @@
       </c>
       <c r="G260" s="1">
         <f t="shared" si="17"/>
-        <v>70.599999999999994</v>
+        <v>69.8</v>
       </c>
       <c r="H260" s="1">
         <f t="shared" si="18"/>
-        <v>8.9515414488671805</v>
+        <v>8.7972651586502018</v>
       </c>
       <c r="I260" s="1">
         <f t="shared" si="19"/>
-        <v>0.18672</v>
+        <v>0.18576000000000004</v>
       </c>
       <c r="J260">
         <v>6.78</v>
@@ -12767,15 +12767,15 @@
       </c>
       <c r="G261" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="H261" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.3499798239224141</v>
       </c>
       <c r="I261" s="1">
         <f t="shared" si="19"/>
-        <v>0.18384</v>
+        <v>0.18288000000000004</v>
       </c>
       <c r="J261">
         <v>6.78</v>
@@ -12812,15 +12812,15 @@
       </c>
       <c r="G262" s="1">
         <f t="shared" si="17"/>
-        <v>73</v>
+        <v>71.8</v>
       </c>
       <c r="H262" s="1">
         <f t="shared" si="18"/>
-        <v>9.4307032545607044</v>
+        <v>9.1880049781907953</v>
       </c>
       <c r="I262" s="1">
         <f t="shared" si="19"/>
-        <v>0.12640000000000001</v>
+        <v>0.12544000000000002</v>
       </c>
       <c r="J262">
         <v>6.78</v>
@@ -12857,15 +12857,15 @@
       </c>
       <c r="G263" s="1">
         <f t="shared" si="17"/>
-        <v>70.599999999999994</v>
+        <v>69.399999999999991</v>
       </c>
       <c r="H263" s="1">
         <f t="shared" si="18"/>
-        <v>8.9515414488671805</v>
+        <v>8.7211155479602773</v>
       </c>
       <c r="I263" s="1">
         <f t="shared" si="19"/>
-        <v>0.12448000000000001</v>
+        <v>0.12352</v>
       </c>
       <c r="J263">
         <v>6.78</v>
@@ -12902,15 +12902,15 @@
       </c>
       <c r="G264" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>67</v>
       </c>
       <c r="H264" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.2776288467733909</v>
       </c>
       <c r="I264" s="1">
         <f t="shared" si="19"/>
-        <v>0.12256</v>
+        <v>0.12160000000000003</v>
       </c>
       <c r="J264">
         <v>6.78</v>
@@ -12947,15 +12947,15 @@
       </c>
       <c r="G265" s="1">
         <f t="shared" si="17"/>
-        <v>65.8</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="H265" s="1">
         <f t="shared" si="18"/>
-        <v>8.064213252098261</v>
+        <v>7.8561249245445515</v>
       </c>
       <c r="I265" s="1">
         <f t="shared" si="19"/>
-        <v>0.12064000000000002</v>
+        <v>0.11968000000000001</v>
       </c>
       <c r="J265">
         <v>6.78</v>
@@ -12992,15 +12992,15 @@
       </c>
       <c r="G266" s="1">
         <f t="shared" si="17"/>
-        <v>70.599999999999994</v>
+        <v>69</v>
       </c>
       <c r="H266" s="1">
         <f t="shared" si="18"/>
-        <v>8.9515414488671805</v>
+        <v>8.6456157322946154</v>
       </c>
       <c r="I266" s="1">
         <f t="shared" si="19"/>
-        <v>9.3359999999999999E-2</v>
+        <v>9.240000000000001E-2</v>
       </c>
       <c r="J266">
         <v>6.78</v>
@@ -13037,15 +13037,15 @@
       </c>
       <c r="G267" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>66.600000000000009</v>
       </c>
       <c r="H267" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.2058882494034666</v>
       </c>
       <c r="I267" s="1">
         <f t="shared" si="19"/>
-        <v>9.1920000000000002E-2</v>
+        <v>9.0960000000000013E-2</v>
       </c>
       <c r="J267">
         <v>6.78</v>
@@ -13082,15 +13082,15 @@
       </c>
       <c r="G268" s="1">
         <f t="shared" si="17"/>
-        <v>65.8</v>
+        <v>64.2</v>
       </c>
       <c r="H268" s="1">
         <f t="shared" si="18"/>
-        <v>8.064213252098261</v>
+        <v>7.7879181462560192</v>
       </c>
       <c r="I268" s="1">
         <f t="shared" si="19"/>
-        <v>9.0480000000000019E-2</v>
+        <v>8.9520000000000002E-2</v>
       </c>
       <c r="J268">
         <v>6.78</v>
@@ -13127,15 +13127,15 @@
       </c>
       <c r="G269" s="1">
         <f t="shared" si="17"/>
-        <v>63.4</v>
+        <v>61.8</v>
       </c>
       <c r="H269" s="1">
         <f t="shared" si="18"/>
-        <v>7.6532038672967868</v>
+        <v>7.390415734640424</v>
       </c>
       <c r="I269" s="1">
         <f t="shared" si="19"/>
-        <v>8.9040000000000022E-2</v>
+        <v>8.8080000000000019E-2</v>
       </c>
       <c r="J269">
         <v>6.78</v>
@@ -13172,15 +13172,15 @@
       </c>
       <c r="G270" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>66.2</v>
       </c>
       <c r="H270" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.1347517750311056</v>
       </c>
       <c r="I270" s="1">
         <f t="shared" si="19"/>
-        <v>7.3536000000000004E-2</v>
+        <v>7.2576000000000002E-2</v>
       </c>
       <c r="J270">
         <v>6.78</v>
@@ -13217,15 +13217,15 @@
       </c>
       <c r="G271" s="1">
         <f t="shared" si="17"/>
-        <v>65.8</v>
+        <v>63.8</v>
       </c>
       <c r="H271" s="1">
         <f t="shared" si="18"/>
-        <v>8.064213252098261</v>
+        <v>7.7202796903675326</v>
       </c>
       <c r="I271" s="1">
         <f t="shared" si="19"/>
-        <v>7.2384000000000018E-2</v>
+        <v>7.1424000000000015E-2</v>
       </c>
       <c r="J271">
         <v>6.78</v>
@@ -13262,15 +13262,15 @@
       </c>
       <c r="G272" s="1">
         <f t="shared" si="17"/>
-        <v>63.4</v>
+        <v>61.4</v>
       </c>
       <c r="H272" s="1">
         <f t="shared" si="18"/>
-        <v>7.6532038672967868</v>
+        <v>7.3260703377995338</v>
       </c>
       <c r="I272" s="1">
         <f t="shared" si="19"/>
-        <v>7.1232000000000018E-2</v>
+        <v>7.0272000000000015E-2</v>
       </c>
       <c r="J272">
         <v>6.78</v>
@@ -13307,15 +13307,15 @@
       </c>
       <c r="G273" s="1">
         <f t="shared" si="17"/>
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H273" s="1">
         <f t="shared" si="18"/>
-        <v>7.2622549827912248</v>
+        <v>6.9509496890873574</v>
       </c>
       <c r="I273" s="1">
         <f t="shared" si="19"/>
-        <v>7.0080000000000003E-2</v>
+        <v>6.9120000000000015E-2</v>
       </c>
       <c r="J273">
         <v>6.78</v>
@@ -13352,15 +13352,15 @@
       </c>
       <c r="G274" s="1">
         <f t="shared" si="17"/>
-        <v>75.400000000000006</v>
+        <v>74.600000000000009</v>
       </c>
       <c r="H274" s="1">
         <f t="shared" si="18"/>
-        <v>9.9356363815570621</v>
+        <v>9.7643564541554984</v>
       </c>
       <c r="I274" s="1">
         <f t="shared" si="19"/>
-        <v>0.19248000000000004</v>
+        <v>0.19152000000000005</v>
       </c>
       <c r="J274">
         <v>6.78</v>
@@ -13397,15 +13397,15 @@
       </c>
       <c r="G275" s="1">
         <f t="shared" si="17"/>
-        <v>73</v>
+        <v>72.2</v>
       </c>
       <c r="H275" s="1">
         <f t="shared" si="18"/>
-        <v>9.4307032545607044</v>
+        <v>9.2682016743192595</v>
       </c>
       <c r="I275" s="1">
         <f t="shared" si="19"/>
-        <v>0.18960000000000002</v>
+        <v>0.18864</v>
       </c>
       <c r="J275">
         <v>6.78</v>
@@ -13442,15 +13442,15 @@
       </c>
       <c r="G276" s="1">
         <f t="shared" si="17"/>
-        <v>70.599999999999994</v>
+        <v>69.8</v>
       </c>
       <c r="H276" s="1">
         <f t="shared" si="18"/>
-        <v>8.9515414488671805</v>
+        <v>8.7972651586502018</v>
       </c>
       <c r="I276" s="1">
         <f t="shared" si="19"/>
-        <v>0.18672</v>
+        <v>0.18576000000000004</v>
       </c>
       <c r="J276">
         <v>6.78</v>
@@ -13487,15 +13487,15 @@
       </c>
       <c r="G277" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="H277" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.3499798239224141</v>
       </c>
       <c r="I277" s="1">
         <f t="shared" si="19"/>
-        <v>0.18384</v>
+        <v>0.18288000000000004</v>
       </c>
       <c r="J277">
         <v>6.78</v>
@@ -13532,15 +13532,15 @@
       </c>
       <c r="G278" s="1">
         <f t="shared" si="17"/>
-        <v>73</v>
+        <v>71.8</v>
       </c>
       <c r="H278" s="1">
         <f t="shared" si="18"/>
-        <v>9.4307032545607044</v>
+        <v>9.1880049781907953</v>
       </c>
       <c r="I278" s="1">
         <f t="shared" si="19"/>
-        <v>0.12640000000000001</v>
+        <v>0.12544000000000002</v>
       </c>
       <c r="J278">
         <v>6.78</v>
@@ -13577,15 +13577,15 @@
       </c>
       <c r="G279" s="1">
         <f t="shared" si="17"/>
-        <v>70.599999999999994</v>
+        <v>69.399999999999991</v>
       </c>
       <c r="H279" s="1">
         <f t="shared" si="18"/>
-        <v>8.9515414488671805</v>
+        <v>8.7211155479602773</v>
       </c>
       <c r="I279" s="1">
         <f t="shared" si="19"/>
-        <v>0.12448000000000001</v>
+        <v>0.12352</v>
       </c>
       <c r="J279">
         <v>6.78</v>
@@ -13622,15 +13622,15 @@
       </c>
       <c r="G280" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>67</v>
       </c>
       <c r="H280" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.2776288467733909</v>
       </c>
       <c r="I280" s="1">
         <f t="shared" si="19"/>
-        <v>0.12256</v>
+        <v>0.12160000000000003</v>
       </c>
       <c r="J280">
         <v>6.78</v>
@@ -13667,15 +13667,15 @@
       </c>
       <c r="G281" s="1">
         <f t="shared" si="17"/>
-        <v>65.8</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="H281" s="1">
         <f t="shared" si="18"/>
-        <v>8.064213252098261</v>
+        <v>7.8561249245445515</v>
       </c>
       <c r="I281" s="1">
         <f t="shared" si="19"/>
-        <v>0.12064000000000002</v>
+        <v>0.11968000000000001</v>
       </c>
       <c r="J281">
         <v>6.78</v>
@@ -13712,15 +13712,15 @@
       </c>
       <c r="G282" s="1">
         <f t="shared" si="17"/>
-        <v>70.599999999999994</v>
+        <v>69</v>
       </c>
       <c r="H282" s="1">
         <f t="shared" si="18"/>
-        <v>8.9515414488671805</v>
+        <v>8.6456157322946154</v>
       </c>
       <c r="I282" s="1">
         <f t="shared" si="19"/>
-        <v>9.3359999999999999E-2</v>
+        <v>9.240000000000001E-2</v>
       </c>
       <c r="J282">
         <v>6.78</v>
@@ -13757,15 +13757,15 @@
       </c>
       <c r="G283" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>66.600000000000009</v>
       </c>
       <c r="H283" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.2058882494034666</v>
       </c>
       <c r="I283" s="1">
         <f t="shared" si="19"/>
-        <v>9.1920000000000002E-2</v>
+        <v>9.0960000000000013E-2</v>
       </c>
       <c r="J283">
         <v>6.78</v>
@@ -13802,15 +13802,15 @@
       </c>
       <c r="G284" s="1">
         <f t="shared" si="17"/>
-        <v>65.8</v>
+        <v>64.2</v>
       </c>
       <c r="H284" s="1">
         <f t="shared" si="18"/>
-        <v>8.064213252098261</v>
+        <v>7.7879181462560192</v>
       </c>
       <c r="I284" s="1">
         <f t="shared" si="19"/>
-        <v>9.0480000000000019E-2</v>
+        <v>8.9520000000000002E-2</v>
       </c>
       <c r="J284">
         <v>6.78</v>
@@ -13847,15 +13847,15 @@
       </c>
       <c r="G285" s="1">
         <f t="shared" si="17"/>
-        <v>63.4</v>
+        <v>61.8</v>
       </c>
       <c r="H285" s="1">
         <f t="shared" si="18"/>
-        <v>7.6532038672967868</v>
+        <v>7.390415734640424</v>
       </c>
       <c r="I285" s="1">
         <f t="shared" si="19"/>
-        <v>8.9040000000000022E-2</v>
+        <v>8.8080000000000019E-2</v>
       </c>
       <c r="J285">
         <v>6.78</v>
@@ -13892,15 +13892,15 @@
       </c>
       <c r="G286" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>66.2</v>
       </c>
       <c r="H286" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.1347517750311056</v>
       </c>
       <c r="I286" s="1">
         <f t="shared" si="19"/>
-        <v>7.3536000000000004E-2</v>
+        <v>7.2576000000000002E-2</v>
       </c>
       <c r="J286">
         <v>6.78</v>
@@ -13937,15 +13937,15 @@
       </c>
       <c r="G287" s="1">
         <f t="shared" si="17"/>
-        <v>65.8</v>
+        <v>63.8</v>
       </c>
       <c r="H287" s="1">
         <f t="shared" si="18"/>
-        <v>8.064213252098261</v>
+        <v>7.7202796903675326</v>
       </c>
       <c r="I287" s="1">
         <f t="shared" si="19"/>
-        <v>7.2384000000000018E-2</v>
+        <v>7.1424000000000015E-2</v>
       </c>
       <c r="J287">
         <v>6.78</v>
@@ -13982,15 +13982,15 @@
       </c>
       <c r="G288" s="1">
         <f t="shared" si="17"/>
-        <v>63.4</v>
+        <v>61.4</v>
       </c>
       <c r="H288" s="1">
         <f t="shared" si="18"/>
-        <v>7.6532038672967868</v>
+        <v>7.3260703377995338</v>
       </c>
       <c r="I288" s="1">
         <f t="shared" si="19"/>
-        <v>7.1232000000000018E-2</v>
+        <v>7.0272000000000015E-2</v>
       </c>
       <c r="J288">
         <v>6.78</v>
@@ -14027,15 +14027,15 @@
       </c>
       <c r="G289" s="1">
         <f t="shared" si="17"/>
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H289" s="1">
         <f t="shared" si="18"/>
-        <v>7.2622549827912248</v>
+        <v>6.9509496890873574</v>
       </c>
       <c r="I289" s="1">
         <f t="shared" si="19"/>
-        <v>7.0080000000000003E-2</v>
+        <v>6.9120000000000015E-2</v>
       </c>
       <c r="J289">
         <v>6.78</v>
@@ -14072,15 +14072,15 @@
       </c>
       <c r="G290" s="1">
         <f t="shared" si="17"/>
-        <v>75.400000000000006</v>
+        <v>74.600000000000009</v>
       </c>
       <c r="H290" s="1">
         <f t="shared" si="18"/>
-        <v>9.9356363815570621</v>
+        <v>9.7643564541554984</v>
       </c>
       <c r="I290" s="1">
         <f t="shared" si="19"/>
-        <v>0.19248000000000004</v>
+        <v>0.19152000000000005</v>
       </c>
       <c r="J290">
         <v>6.78</v>
@@ -14117,15 +14117,15 @@
       </c>
       <c r="G291" s="1">
         <f t="shared" si="17"/>
-        <v>73</v>
+        <v>72.2</v>
       </c>
       <c r="H291" s="1">
         <f t="shared" si="18"/>
-        <v>9.4307032545607044</v>
+        <v>9.2682016743192595</v>
       </c>
       <c r="I291" s="1">
         <f t="shared" si="19"/>
-        <v>0.18960000000000002</v>
+        <v>0.18864</v>
       </c>
       <c r="J291">
         <v>6.78</v>
@@ -14162,15 +14162,15 @@
       </c>
       <c r="G292" s="1">
         <f t="shared" si="17"/>
-        <v>70.599999999999994</v>
+        <v>69.8</v>
       </c>
       <c r="H292" s="1">
         <f t="shared" si="18"/>
-        <v>8.9515414488671805</v>
+        <v>8.7972651586502018</v>
       </c>
       <c r="I292" s="1">
         <f t="shared" si="19"/>
-        <v>0.18672</v>
+        <v>0.18576000000000004</v>
       </c>
       <c r="J292">
         <v>6.78</v>
@@ -14207,15 +14207,15 @@
       </c>
       <c r="G293" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="H293" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.3499798239224141</v>
       </c>
       <c r="I293" s="1">
         <f t="shared" si="19"/>
-        <v>0.18384</v>
+        <v>0.18288000000000004</v>
       </c>
       <c r="J293">
         <v>6.78</v>
@@ -14252,15 +14252,15 @@
       </c>
       <c r="G294" s="1">
         <f t="shared" si="17"/>
-        <v>73</v>
+        <v>71.8</v>
       </c>
       <c r="H294" s="1">
         <f t="shared" si="18"/>
-        <v>9.4307032545607044</v>
+        <v>9.1880049781907953</v>
       </c>
       <c r="I294" s="1">
         <f t="shared" si="19"/>
-        <v>0.12640000000000001</v>
+        <v>0.12544000000000002</v>
       </c>
       <c r="J294">
         <v>6.78</v>
@@ -14297,15 +14297,15 @@
       </c>
       <c r="G295" s="1">
         <f t="shared" si="17"/>
-        <v>70.599999999999994</v>
+        <v>69.399999999999991</v>
       </c>
       <c r="H295" s="1">
         <f t="shared" si="18"/>
-        <v>8.9515414488671805</v>
+        <v>8.7211155479602773</v>
       </c>
       <c r="I295" s="1">
         <f t="shared" si="19"/>
-        <v>0.12448000000000001</v>
+        <v>0.12352</v>
       </c>
       <c r="J295">
         <v>6.78</v>
@@ -14342,15 +14342,15 @@
       </c>
       <c r="G296" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>67</v>
       </c>
       <c r="H296" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.2776288467733909</v>
       </c>
       <c r="I296" s="1">
         <f t="shared" si="19"/>
-        <v>0.12256</v>
+        <v>0.12160000000000003</v>
       </c>
       <c r="J296">
         <v>6.78</v>
@@ -14387,15 +14387,15 @@
       </c>
       <c r="G297" s="1">
         <f t="shared" si="17"/>
-        <v>65.8</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="H297" s="1">
         <f t="shared" si="18"/>
-        <v>8.064213252098261</v>
+        <v>7.8561249245445515</v>
       </c>
       <c r="I297" s="1">
         <f t="shared" si="19"/>
-        <v>0.12064000000000002</v>
+        <v>0.11968000000000001</v>
       </c>
       <c r="J297">
         <v>6.78</v>
@@ -14432,15 +14432,15 @@
       </c>
       <c r="G298" s="1">
         <f t="shared" si="17"/>
-        <v>70.599999999999994</v>
+        <v>69</v>
       </c>
       <c r="H298" s="1">
         <f t="shared" si="18"/>
-        <v>8.9515414488671805</v>
+        <v>8.6456157322946154</v>
       </c>
       <c r="I298" s="1">
         <f t="shared" si="19"/>
-        <v>9.3359999999999999E-2</v>
+        <v>9.240000000000001E-2</v>
       </c>
       <c r="J298">
         <v>6.78</v>
@@ -14477,15 +14477,15 @@
       </c>
       <c r="G299" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>66.600000000000009</v>
       </c>
       <c r="H299" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.2058882494034666</v>
       </c>
       <c r="I299" s="1">
         <f t="shared" si="19"/>
-        <v>9.1920000000000002E-2</v>
+        <v>9.0960000000000013E-2</v>
       </c>
       <c r="J299">
         <v>6.78</v>
@@ -14522,15 +14522,15 @@
       </c>
       <c r="G300" s="1">
         <f t="shared" si="17"/>
-        <v>65.8</v>
+        <v>64.2</v>
       </c>
       <c r="H300" s="1">
         <f t="shared" si="18"/>
-        <v>8.064213252098261</v>
+        <v>7.7879181462560192</v>
       </c>
       <c r="I300" s="1">
         <f t="shared" si="19"/>
-        <v>9.0480000000000019E-2</v>
+        <v>8.9520000000000002E-2</v>
       </c>
       <c r="J300">
         <v>6.78</v>
@@ -14567,15 +14567,15 @@
       </c>
       <c r="G301" s="1">
         <f t="shared" si="17"/>
-        <v>63.4</v>
+        <v>61.8</v>
       </c>
       <c r="H301" s="1">
         <f t="shared" si="18"/>
-        <v>7.6532038672967868</v>
+        <v>7.390415734640424</v>
       </c>
       <c r="I301" s="1">
         <f t="shared" si="19"/>
-        <v>8.9040000000000022E-2</v>
+        <v>8.8080000000000019E-2</v>
       </c>
       <c r="J301">
         <v>6.78</v>
@@ -14612,15 +14612,15 @@
       </c>
       <c r="G302" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>66.2</v>
       </c>
       <c r="H302" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.1347517750311056</v>
       </c>
       <c r="I302" s="1">
         <f t="shared" si="19"/>
-        <v>7.3536000000000004E-2</v>
+        <v>7.2576000000000002E-2</v>
       </c>
       <c r="J302">
         <v>6.78</v>
@@ -14657,15 +14657,15 @@
       </c>
       <c r="G303" s="1">
         <f t="shared" si="17"/>
-        <v>65.8</v>
+        <v>63.8</v>
       </c>
       <c r="H303" s="1">
         <f t="shared" si="18"/>
-        <v>8.064213252098261</v>
+        <v>7.7202796903675326</v>
       </c>
       <c r="I303" s="1">
         <f t="shared" si="19"/>
-        <v>7.2384000000000018E-2</v>
+        <v>7.1424000000000015E-2</v>
       </c>
       <c r="J303">
         <v>6.78</v>
@@ -14702,15 +14702,15 @@
       </c>
       <c r="G304" s="1">
         <f t="shared" si="17"/>
-        <v>63.4</v>
+        <v>61.4</v>
       </c>
       <c r="H304" s="1">
         <f t="shared" si="18"/>
-        <v>7.6532038672967868</v>
+        <v>7.3260703377995338</v>
       </c>
       <c r="I304" s="1">
         <f t="shared" si="19"/>
-        <v>7.1232000000000018E-2</v>
+        <v>7.0272000000000015E-2</v>
       </c>
       <c r="J304">
         <v>6.78</v>
@@ -14747,15 +14747,15 @@
       </c>
       <c r="G305" s="1">
         <f t="shared" si="17"/>
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H305" s="1">
         <f t="shared" si="18"/>
-        <v>7.2622549827912248</v>
+        <v>6.9509496890873574</v>
       </c>
       <c r="I305" s="1">
         <f t="shared" si="19"/>
-        <v>7.0080000000000003E-2</v>
+        <v>6.9120000000000015E-2</v>
       </c>
       <c r="J305">
         <v>6.78</v>
@@ -14792,15 +14792,15 @@
       </c>
       <c r="G306" s="1">
         <f t="shared" si="17"/>
-        <v>75.400000000000006</v>
+        <v>74.600000000000009</v>
       </c>
       <c r="H306" s="1">
         <f t="shared" si="18"/>
-        <v>9.9356363815570621</v>
+        <v>9.7643564541554984</v>
       </c>
       <c r="I306" s="1">
         <f t="shared" si="19"/>
-        <v>0.19248000000000004</v>
+        <v>0.19152000000000005</v>
       </c>
       <c r="J306">
         <v>6.78</v>
@@ -14837,15 +14837,15 @@
       </c>
       <c r="G307" s="1">
         <f t="shared" si="17"/>
-        <v>73</v>
+        <v>72.2</v>
       </c>
       <c r="H307" s="1">
         <f t="shared" si="18"/>
-        <v>9.4307032545607044</v>
+        <v>9.2682016743192595</v>
       </c>
       <c r="I307" s="1">
         <f t="shared" si="19"/>
-        <v>0.18960000000000002</v>
+        <v>0.18864</v>
       </c>
       <c r="J307">
         <v>6.78</v>
@@ -14882,15 +14882,15 @@
       </c>
       <c r="G308" s="1">
         <f t="shared" si="17"/>
-        <v>70.599999999999994</v>
+        <v>69.8</v>
       </c>
       <c r="H308" s="1">
         <f t="shared" si="18"/>
-        <v>8.9515414488671805</v>
+        <v>8.7972651586502018</v>
       </c>
       <c r="I308" s="1">
         <f t="shared" si="19"/>
-        <v>0.18672</v>
+        <v>0.18576000000000004</v>
       </c>
       <c r="J308">
         <v>6.78</v>
@@ -14927,15 +14927,15 @@
       </c>
       <c r="G309" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="H309" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.3499798239224141</v>
       </c>
       <c r="I309" s="1">
         <f t="shared" si="19"/>
-        <v>0.18384</v>
+        <v>0.18288000000000004</v>
       </c>
       <c r="J309">
         <v>6.78</v>
@@ -14972,15 +14972,15 @@
       </c>
       <c r="G310" s="1">
         <f t="shared" si="17"/>
-        <v>73</v>
+        <v>71.8</v>
       </c>
       <c r="H310" s="1">
         <f t="shared" si="18"/>
-        <v>9.4307032545607044</v>
+        <v>9.1880049781907953</v>
       </c>
       <c r="I310" s="1">
         <f t="shared" si="19"/>
-        <v>0.12640000000000001</v>
+        <v>0.12544000000000002</v>
       </c>
       <c r="J310">
         <v>6.78</v>
@@ -15017,15 +15017,15 @@
       </c>
       <c r="G311" s="1">
         <f t="shared" si="17"/>
-        <v>70.599999999999994</v>
+        <v>69.399999999999991</v>
       </c>
       <c r="H311" s="1">
         <f t="shared" si="18"/>
-        <v>8.9515414488671805</v>
+        <v>8.7211155479602773</v>
       </c>
       <c r="I311" s="1">
         <f t="shared" si="19"/>
-        <v>0.12448000000000001</v>
+        <v>0.12352</v>
       </c>
       <c r="J311">
         <v>6.78</v>
@@ -15062,15 +15062,15 @@
       </c>
       <c r="G312" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>67</v>
       </c>
       <c r="H312" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.2776288467733909</v>
       </c>
       <c r="I312" s="1">
         <f t="shared" si="19"/>
-        <v>0.12256</v>
+        <v>0.12160000000000003</v>
       </c>
       <c r="J312">
         <v>6.78</v>
@@ -15107,15 +15107,15 @@
       </c>
       <c r="G313" s="1">
         <f t="shared" si="17"/>
-        <v>65.8</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="H313" s="1">
         <f t="shared" si="18"/>
-        <v>8.064213252098261</v>
+        <v>7.8561249245445515</v>
       </c>
       <c r="I313" s="1">
         <f t="shared" si="19"/>
-        <v>0.12064000000000002</v>
+        <v>0.11968000000000001</v>
       </c>
       <c r="J313">
         <v>6.78</v>
@@ -15152,15 +15152,15 @@
       </c>
       <c r="G314" s="1">
         <f t="shared" si="17"/>
-        <v>70.599999999999994</v>
+        <v>69</v>
       </c>
       <c r="H314" s="1">
         <f t="shared" si="18"/>
-        <v>8.9515414488671805</v>
+        <v>8.6456157322946154</v>
       </c>
       <c r="I314" s="1">
         <f t="shared" si="19"/>
-        <v>9.3359999999999999E-2</v>
+        <v>9.240000000000001E-2</v>
       </c>
       <c r="J314">
         <v>6.78</v>
@@ -15197,15 +15197,15 @@
       </c>
       <c r="G315" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>66.600000000000009</v>
       </c>
       <c r="H315" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.2058882494034666</v>
       </c>
       <c r="I315" s="1">
         <f t="shared" si="19"/>
-        <v>9.1920000000000002E-2</v>
+        <v>9.0960000000000013E-2</v>
       </c>
       <c r="J315">
         <v>6.78</v>
@@ -15242,15 +15242,15 @@
       </c>
       <c r="G316" s="1">
         <f t="shared" si="17"/>
-        <v>65.8</v>
+        <v>64.2</v>
       </c>
       <c r="H316" s="1">
         <f t="shared" si="18"/>
-        <v>8.064213252098261</v>
+        <v>7.7879181462560192</v>
       </c>
       <c r="I316" s="1">
         <f t="shared" si="19"/>
-        <v>9.0480000000000019E-2</v>
+        <v>8.9520000000000002E-2</v>
       </c>
       <c r="J316">
         <v>6.78</v>
@@ -15287,15 +15287,15 @@
       </c>
       <c r="G317" s="1">
         <f t="shared" si="17"/>
-        <v>63.4</v>
+        <v>61.8</v>
       </c>
       <c r="H317" s="1">
         <f t="shared" si="18"/>
-        <v>7.6532038672967868</v>
+        <v>7.390415734640424</v>
       </c>
       <c r="I317" s="1">
         <f t="shared" si="19"/>
-        <v>8.9040000000000022E-2</v>
+        <v>8.8080000000000019E-2</v>
       </c>
       <c r="J317">
         <v>6.78</v>
@@ -15332,15 +15332,15 @@
       </c>
       <c r="G318" s="1">
         <f t="shared" si="17"/>
-        <v>68.2</v>
+        <v>66.2</v>
       </c>
       <c r="H318" s="1">
         <f t="shared" si="18"/>
-        <v>8.4965383796889427</v>
+        <v>8.1347517750311056</v>
       </c>
       <c r="I318" s="1">
         <f t="shared" si="19"/>
-        <v>7.3536000000000004E-2</v>
+        <v>7.2576000000000002E-2</v>
       </c>
       <c r="J318">
         <v>6.78</v>
@@ -15377,15 +15377,15 @@
       </c>
       <c r="G319" s="1">
         <f t="shared" si="17"/>
-        <v>65.8</v>
+        <v>63.8</v>
       </c>
       <c r="H319" s="1">
         <f t="shared" si="18"/>
-        <v>8.064213252098261</v>
+        <v>7.7202796903675326</v>
       </c>
       <c r="I319" s="1">
         <f t="shared" si="19"/>
-        <v>7.2384000000000018E-2</v>
+        <v>7.1424000000000015E-2</v>
       </c>
       <c r="J319">
         <v>6.78</v>
@@ -15422,15 +15422,15 @@
       </c>
       <c r="G320" s="1">
         <f t="shared" si="17"/>
-        <v>63.4</v>
+        <v>61.4</v>
       </c>
       <c r="H320" s="1">
         <f t="shared" si="18"/>
-        <v>7.6532038672967868</v>
+        <v>7.3260703377995338</v>
       </c>
       <c r="I320" s="1">
         <f t="shared" si="19"/>
-        <v>7.1232000000000018E-2</v>
+        <v>7.0272000000000015E-2</v>
       </c>
       <c r="J320">
         <v>6.78</v>
@@ -15467,15 +15467,15 @@
       </c>
       <c r="G321" s="1">
         <f t="shared" si="17"/>
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H321" s="1">
         <f t="shared" si="18"/>
-        <v>7.2622549827912248</v>
+        <v>6.9509496890873574</v>
       </c>
       <c r="I321" s="1">
         <f t="shared" si="19"/>
-        <v>7.0080000000000003E-2</v>
+        <v>6.9120000000000015E-2</v>
       </c>
       <c r="J321">
         <v>6.78</v>
@@ -15512,15 +15512,15 @@
       </c>
       <c r="G322" s="1">
         <f t="shared" si="17"/>
-        <v>80.400000000000006</v>
+        <v>79.600000000000009</v>
       </c>
       <c r="H322" s="1">
         <f t="shared" si="18"/>
-        <v>10.642783189746096</v>
+        <v>10.469387455299206</v>
       </c>
       <c r="I322" s="1">
         <f t="shared" si="19"/>
-        <v>0.20448000000000002</v>
+        <v>0.20352000000000006</v>
       </c>
       <c r="J322">
         <v>6.78</v>
@@ -15556,16 +15556,16 @@
         <v>90</v>
       </c>
       <c r="G323" s="1">
-        <f t="shared" ref="G323:G386" si="21">F323-(A323-1)*2*(C323+E323)</f>
-        <v>78</v>
+        <f t="shared" ref="G323:G386" si="21">F323-(A323-1)*2*(C323+E323)-2*C323</f>
+        <v>77.2</v>
       </c>
       <c r="H323" s="1">
         <f t="shared" ref="H323:H386" si="22">2.34*0.000001257*(0.5*A323^2*(F323+G323))/(1+2.73*(F323-G323)/(F323+G323))*1000</f>
-        <v>10.131146510460249</v>
+        <v>9.9661842159569396</v>
       </c>
       <c r="I323" s="1">
         <f t="shared" ref="I323:I386" si="23">0.0000000168*4*0.5*(F323+G323)/(0.00007*C323)</f>
-        <v>0.20160000000000003</v>
+        <v>0.20063999999999999</v>
       </c>
       <c r="J323">
         <v>6.78</v>
@@ -15602,15 +15602,15 @@
       </c>
       <c r="G324" s="1">
         <f t="shared" si="21"/>
-        <v>75.599999999999994</v>
+        <v>74.8</v>
       </c>
       <c r="H324" s="1">
         <f t="shared" si="22"/>
-        <v>9.6442951345045653</v>
+        <v>9.4872605302206523</v>
       </c>
       <c r="I324" s="1">
         <f t="shared" si="23"/>
-        <v>0.19872000000000004</v>
+        <v>0.19776000000000002</v>
       </c>
       <c r="J324">
         <v>6.78</v>
@@ -15647,15 +15647,15 @@
       </c>
       <c r="G325" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="H325" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>9.0311793394358695</v>
       </c>
       <c r="I325" s="1">
         <f t="shared" si="23"/>
-        <v>0.19583999999999999</v>
+        <v>0.19488000000000003</v>
       </c>
       <c r="J325">
         <v>6.78</v>
@@ -15692,15 +15692,15 @@
       </c>
       <c r="G326" s="1">
         <f t="shared" si="21"/>
-        <v>78</v>
+        <v>76.8</v>
       </c>
       <c r="H326" s="1">
         <f t="shared" si="22"/>
-        <v>10.131146510460249</v>
+        <v>9.8847177874460144</v>
       </c>
       <c r="I326" s="1">
         <f t="shared" si="23"/>
-        <v>0.13440000000000002</v>
+        <v>0.13344000000000003</v>
       </c>
       <c r="J326">
         <v>6.78</v>
@@ -15737,15 +15737,15 @@
       </c>
       <c r="G327" s="1">
         <f t="shared" si="21"/>
-        <v>75.599999999999994</v>
+        <v>74.399999999999991</v>
       </c>
       <c r="H327" s="1">
         <f t="shared" si="22"/>
-        <v>9.6442951345045653</v>
+        <v>9.4096978367905351</v>
       </c>
       <c r="I327" s="1">
         <f t="shared" si="23"/>
-        <v>0.13248000000000001</v>
+        <v>0.13152</v>
       </c>
       <c r="J327">
         <v>6.78</v>
@@ -15782,15 +15782,15 @@
       </c>
       <c r="G328" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>72</v>
       </c>
       <c r="H328" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>8.9572919846547325</v>
       </c>
       <c r="I328" s="1">
         <f t="shared" si="23"/>
-        <v>0.13056000000000001</v>
+        <v>0.12960000000000002</v>
       </c>
       <c r="J328">
         <v>6.78</v>
@@ -15827,15 +15827,15 @@
       </c>
       <c r="G329" s="1">
         <f t="shared" si="21"/>
-        <v>70.8</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="H329" s="1">
         <f t="shared" si="22"/>
-        <v>8.7391564995047268</v>
+        <v>8.5261918628170097</v>
       </c>
       <c r="I329" s="1">
         <f t="shared" si="23"/>
-        <v>0.12864000000000003</v>
+        <v>0.12768000000000002</v>
       </c>
       <c r="J329">
         <v>6.78</v>
@@ -15872,15 +15872,15 @@
       </c>
       <c r="G330" s="1">
         <f t="shared" si="21"/>
-        <v>75.599999999999994</v>
+        <v>74</v>
       </c>
       <c r="H330" s="1">
         <f t="shared" si="22"/>
-        <v>9.6442951345045653</v>
+        <v>9.3327630670261925</v>
       </c>
       <c r="I330" s="1">
         <f t="shared" si="23"/>
-        <v>9.9360000000000018E-2</v>
+        <v>9.8400000000000015E-2</v>
       </c>
       <c r="J330">
         <v>6.78</v>
@@ -15917,15 +15917,15 @@
       </c>
       <c r="G331" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>71.600000000000009</v>
       </c>
       <c r="H331" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>8.8839962332112261</v>
       </c>
       <c r="I331" s="1">
         <f t="shared" si="23"/>
-        <v>9.7919999999999993E-2</v>
+        <v>9.6960000000000032E-2</v>
       </c>
       <c r="J331">
         <v>6.78</v>
@@ -15962,15 +15962,15 @@
       </c>
       <c r="G332" s="1">
         <f t="shared" si="21"/>
-        <v>70.8</v>
+        <v>69.2</v>
       </c>
       <c r="H332" s="1">
         <f t="shared" si="22"/>
-        <v>8.7391564995047268</v>
+        <v>8.456326956989404</v>
       </c>
       <c r="I332" s="1">
         <f t="shared" si="23"/>
-        <v>9.648000000000001E-2</v>
+        <v>9.5519999999999994E-2</v>
       </c>
       <c r="J332">
         <v>6.78</v>
@@ -16007,15 +16007,15 @@
       </c>
       <c r="G333" s="1">
         <f t="shared" si="21"/>
-        <v>68.400000000000006</v>
+        <v>66.800000000000011</v>
       </c>
       <c r="H333" s="1">
         <f t="shared" si="22"/>
-        <v>8.3182499201059965</v>
+        <v>8.0485614709743096</v>
       </c>
       <c r="I333" s="1">
         <f t="shared" si="23"/>
-        <v>9.5040000000000013E-2</v>
+        <v>9.4080000000000011E-2</v>
       </c>
       <c r="J333">
         <v>6.78</v>
@@ -16052,15 +16052,15 @@
       </c>
       <c r="G334" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>71.2</v>
       </c>
       <c r="H334" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>8.8112863061414224</v>
       </c>
       <c r="I334" s="1">
         <f t="shared" si="23"/>
-        <v>7.8336000000000003E-2</v>
+        <v>7.7376E-2</v>
       </c>
       <c r="J334">
         <v>6.78</v>
@@ -16097,15 +16097,15 @@
       </c>
       <c r="G335" s="1">
         <f t="shared" si="21"/>
-        <v>70.8</v>
+        <v>68.8</v>
       </c>
       <c r="H335" s="1">
         <f t="shared" si="22"/>
-        <v>8.7391564995047268</v>
+        <v>8.38701473557939</v>
       </c>
       <c r="I335" s="1">
         <f t="shared" si="23"/>
-        <v>7.7184000000000016E-2</v>
+        <v>7.6224000000000014E-2</v>
       </c>
       <c r="J335">
         <v>6.78</v>
@@ -16142,15 +16142,15 @@
       </c>
       <c r="G336" s="1">
         <f t="shared" si="21"/>
-        <v>68.400000000000006</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="H336" s="1">
         <f t="shared" si="22"/>
-        <v>8.3182499201059965</v>
+        <v>7.9824568164254543</v>
       </c>
       <c r="I336" s="1">
         <f t="shared" si="23"/>
-        <v>7.6032000000000016E-2</v>
+        <v>7.5072000000000014E-2</v>
       </c>
       <c r="J336">
         <v>6.78</v>
@@ -16187,15 +16187,15 @@
       </c>
       <c r="G337" s="1">
         <f t="shared" si="21"/>
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H337" s="1">
         <f t="shared" si="22"/>
-        <v>7.9168692676056338</v>
+        <v>7.5965211039203471</v>
       </c>
       <c r="I337" s="1">
         <f t="shared" si="23"/>
-        <v>7.4880000000000016E-2</v>
+        <v>7.3920000000000013E-2</v>
       </c>
       <c r="J337">
         <v>6.78</v>
@@ -16232,15 +16232,15 @@
       </c>
       <c r="G338" s="1">
         <f t="shared" si="21"/>
-        <v>80.400000000000006</v>
+        <v>79.600000000000009</v>
       </c>
       <c r="H338" s="1">
         <f t="shared" si="22"/>
-        <v>10.642783189746096</v>
+        <v>10.469387455299206</v>
       </c>
       <c r="I338" s="1">
         <f t="shared" si="23"/>
-        <v>0.20448000000000002</v>
+        <v>0.20352000000000006</v>
       </c>
       <c r="J338">
         <v>6.78</v>
@@ -16277,15 +16277,15 @@
       </c>
       <c r="G339" s="1">
         <f t="shared" si="21"/>
-        <v>78</v>
+        <v>77.2</v>
       </c>
       <c r="H339" s="1">
         <f t="shared" si="22"/>
-        <v>10.131146510460249</v>
+        <v>9.9661842159569396</v>
       </c>
       <c r="I339" s="1">
         <f t="shared" si="23"/>
-        <v>0.20160000000000003</v>
+        <v>0.20063999999999999</v>
       </c>
       <c r="J339">
         <v>6.78</v>
@@ -16322,15 +16322,15 @@
       </c>
       <c r="G340" s="1">
         <f t="shared" si="21"/>
-        <v>75.599999999999994</v>
+        <v>74.8</v>
       </c>
       <c r="H340" s="1">
         <f t="shared" si="22"/>
-        <v>9.6442951345045653</v>
+        <v>9.4872605302206523</v>
       </c>
       <c r="I340" s="1">
         <f t="shared" si="23"/>
-        <v>0.19872000000000004</v>
+        <v>0.19776000000000002</v>
       </c>
       <c r="J340">
         <v>6.78</v>
@@ -16367,15 +16367,15 @@
       </c>
       <c r="G341" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="H341" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>9.0311793394358695</v>
       </c>
       <c r="I341" s="1">
         <f t="shared" si="23"/>
-        <v>0.19583999999999999</v>
+        <v>0.19488000000000003</v>
       </c>
       <c r="J341">
         <v>6.78</v>
@@ -16412,15 +16412,15 @@
       </c>
       <c r="G342" s="1">
         <f t="shared" si="21"/>
-        <v>78</v>
+        <v>76.8</v>
       </c>
       <c r="H342" s="1">
         <f t="shared" si="22"/>
-        <v>10.131146510460249</v>
+        <v>9.8847177874460144</v>
       </c>
       <c r="I342" s="1">
         <f t="shared" si="23"/>
-        <v>0.13440000000000002</v>
+        <v>0.13344000000000003</v>
       </c>
       <c r="J342">
         <v>6.78</v>
@@ -16457,15 +16457,15 @@
       </c>
       <c r="G343" s="1">
         <f t="shared" si="21"/>
-        <v>75.599999999999994</v>
+        <v>74.399999999999991</v>
       </c>
       <c r="H343" s="1">
         <f t="shared" si="22"/>
-        <v>9.6442951345045653</v>
+        <v>9.4096978367905351</v>
       </c>
       <c r="I343" s="1">
         <f t="shared" si="23"/>
-        <v>0.13248000000000001</v>
+        <v>0.13152</v>
       </c>
       <c r="J343">
         <v>6.78</v>
@@ -16502,15 +16502,15 @@
       </c>
       <c r="G344" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>72</v>
       </c>
       <c r="H344" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>8.9572919846547325</v>
       </c>
       <c r="I344" s="1">
         <f t="shared" si="23"/>
-        <v>0.13056000000000001</v>
+        <v>0.12960000000000002</v>
       </c>
       <c r="J344">
         <v>6.78</v>
@@ -16547,15 +16547,15 @@
       </c>
       <c r="G345" s="1">
         <f t="shared" si="21"/>
-        <v>70.8</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="H345" s="1">
         <f t="shared" si="22"/>
-        <v>8.7391564995047268</v>
+        <v>8.5261918628170097</v>
       </c>
       <c r="I345" s="1">
         <f t="shared" si="23"/>
-        <v>0.12864000000000003</v>
+        <v>0.12768000000000002</v>
       </c>
       <c r="J345">
         <v>6.78</v>
@@ -16592,15 +16592,15 @@
       </c>
       <c r="G346" s="1">
         <f t="shared" si="21"/>
-        <v>75.599999999999994</v>
+        <v>74</v>
       </c>
       <c r="H346" s="1">
         <f t="shared" si="22"/>
-        <v>9.6442951345045653</v>
+        <v>9.3327630670261925</v>
       </c>
       <c r="I346" s="1">
         <f t="shared" si="23"/>
-        <v>9.9360000000000018E-2</v>
+        <v>9.8400000000000015E-2</v>
       </c>
       <c r="J346">
         <v>6.78</v>
@@ -16637,15 +16637,15 @@
       </c>
       <c r="G347" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>71.600000000000009</v>
       </c>
       <c r="H347" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>8.8839962332112261</v>
       </c>
       <c r="I347" s="1">
         <f t="shared" si="23"/>
-        <v>9.7919999999999993E-2</v>
+        <v>9.6960000000000032E-2</v>
       </c>
       <c r="J347">
         <v>6.78</v>
@@ -16682,15 +16682,15 @@
       </c>
       <c r="G348" s="1">
         <f t="shared" si="21"/>
-        <v>70.8</v>
+        <v>69.2</v>
       </c>
       <c r="H348" s="1">
         <f t="shared" si="22"/>
-        <v>8.7391564995047268</v>
+        <v>8.456326956989404</v>
       </c>
       <c r="I348" s="1">
         <f t="shared" si="23"/>
-        <v>9.648000000000001E-2</v>
+        <v>9.5519999999999994E-2</v>
       </c>
       <c r="J348">
         <v>6.78</v>
@@ -16727,15 +16727,15 @@
       </c>
       <c r="G349" s="1">
         <f t="shared" si="21"/>
-        <v>68.400000000000006</v>
+        <v>66.800000000000011</v>
       </c>
       <c r="H349" s="1">
         <f t="shared" si="22"/>
-        <v>8.3182499201059965</v>
+        <v>8.0485614709743096</v>
       </c>
       <c r="I349" s="1">
         <f t="shared" si="23"/>
-        <v>9.5040000000000013E-2</v>
+        <v>9.4080000000000011E-2</v>
       </c>
       <c r="J349">
         <v>6.78</v>
@@ -16772,15 +16772,15 @@
       </c>
       <c r="G350" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>71.2</v>
       </c>
       <c r="H350" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>8.8112863061414224</v>
       </c>
       <c r="I350" s="1">
         <f t="shared" si="23"/>
-        <v>7.8336000000000003E-2</v>
+        <v>7.7376E-2</v>
       </c>
       <c r="J350">
         <v>6.78</v>
@@ -16817,15 +16817,15 @@
       </c>
       <c r="G351" s="1">
         <f t="shared" si="21"/>
-        <v>70.8</v>
+        <v>68.8</v>
       </c>
       <c r="H351" s="1">
         <f t="shared" si="22"/>
-        <v>8.7391564995047268</v>
+        <v>8.38701473557939</v>
       </c>
       <c r="I351" s="1">
         <f t="shared" si="23"/>
-        <v>7.7184000000000016E-2</v>
+        <v>7.6224000000000014E-2</v>
       </c>
       <c r="J351">
         <v>6.78</v>
@@ -16862,15 +16862,15 @@
       </c>
       <c r="G352" s="1">
         <f t="shared" si="21"/>
-        <v>68.400000000000006</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="H352" s="1">
         <f t="shared" si="22"/>
-        <v>8.3182499201059965</v>
+        <v>7.9824568164254543</v>
       </c>
       <c r="I352" s="1">
         <f t="shared" si="23"/>
-        <v>7.6032000000000016E-2</v>
+        <v>7.5072000000000014E-2</v>
       </c>
       <c r="J352">
         <v>6.78</v>
@@ -16907,15 +16907,15 @@
       </c>
       <c r="G353" s="1">
         <f t="shared" si="21"/>
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H353" s="1">
         <f t="shared" si="22"/>
-        <v>7.9168692676056338</v>
+        <v>7.5965211039203471</v>
       </c>
       <c r="I353" s="1">
         <f t="shared" si="23"/>
-        <v>7.4880000000000016E-2</v>
+        <v>7.3920000000000013E-2</v>
       </c>
       <c r="J353">
         <v>6.78</v>
@@ -16952,15 +16952,15 @@
       </c>
       <c r="G354" s="1">
         <f t="shared" si="21"/>
-        <v>80.400000000000006</v>
+        <v>79.600000000000009</v>
       </c>
       <c r="H354" s="1">
         <f t="shared" si="22"/>
-        <v>10.642783189746096</v>
+        <v>10.469387455299206</v>
       </c>
       <c r="I354" s="1">
         <f t="shared" si="23"/>
-        <v>0.20448000000000002</v>
+        <v>0.20352000000000006</v>
       </c>
       <c r="J354">
         <v>6.78</v>
@@ -16997,15 +16997,15 @@
       </c>
       <c r="G355" s="1">
         <f t="shared" si="21"/>
-        <v>78</v>
+        <v>77.2</v>
       </c>
       <c r="H355" s="1">
         <f t="shared" si="22"/>
-        <v>10.131146510460249</v>
+        <v>9.9661842159569396</v>
       </c>
       <c r="I355" s="1">
         <f t="shared" si="23"/>
-        <v>0.20160000000000003</v>
+        <v>0.20063999999999999</v>
       </c>
       <c r="J355">
         <v>6.78</v>
@@ -17042,15 +17042,15 @@
       </c>
       <c r="G356" s="1">
         <f t="shared" si="21"/>
-        <v>75.599999999999994</v>
+        <v>74.8</v>
       </c>
       <c r="H356" s="1">
         <f t="shared" si="22"/>
-        <v>9.6442951345045653</v>
+        <v>9.4872605302206523</v>
       </c>
       <c r="I356" s="1">
         <f t="shared" si="23"/>
-        <v>0.19872000000000004</v>
+        <v>0.19776000000000002</v>
       </c>
       <c r="J356">
         <v>6.78</v>
@@ -17087,15 +17087,15 @@
       </c>
       <c r="G357" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="H357" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>9.0311793394358695</v>
       </c>
       <c r="I357" s="1">
         <f t="shared" si="23"/>
-        <v>0.19583999999999999</v>
+        <v>0.19488000000000003</v>
       </c>
       <c r="J357">
         <v>6.78</v>
@@ -17132,15 +17132,15 @@
       </c>
       <c r="G358" s="1">
         <f t="shared" si="21"/>
-        <v>78</v>
+        <v>76.8</v>
       </c>
       <c r="H358" s="1">
         <f t="shared" si="22"/>
-        <v>10.131146510460249</v>
+        <v>9.8847177874460144</v>
       </c>
       <c r="I358" s="1">
         <f t="shared" si="23"/>
-        <v>0.13440000000000002</v>
+        <v>0.13344000000000003</v>
       </c>
       <c r="J358">
         <v>6.78</v>
@@ -17177,15 +17177,15 @@
       </c>
       <c r="G359" s="1">
         <f t="shared" si="21"/>
-        <v>75.599999999999994</v>
+        <v>74.399999999999991</v>
       </c>
       <c r="H359" s="1">
         <f t="shared" si="22"/>
-        <v>9.6442951345045653</v>
+        <v>9.4096978367905351</v>
       </c>
       <c r="I359" s="1">
         <f t="shared" si="23"/>
-        <v>0.13248000000000001</v>
+        <v>0.13152</v>
       </c>
       <c r="J359">
         <v>6.78</v>
@@ -17222,15 +17222,15 @@
       </c>
       <c r="G360" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>72</v>
       </c>
       <c r="H360" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>8.9572919846547325</v>
       </c>
       <c r="I360" s="1">
         <f t="shared" si="23"/>
-        <v>0.13056000000000001</v>
+        <v>0.12960000000000002</v>
       </c>
       <c r="J360">
         <v>6.78</v>
@@ -17267,15 +17267,15 @@
       </c>
       <c r="G361" s="1">
         <f t="shared" si="21"/>
-        <v>70.8</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="H361" s="1">
         <f t="shared" si="22"/>
-        <v>8.7391564995047268</v>
+        <v>8.5261918628170097</v>
       </c>
       <c r="I361" s="1">
         <f t="shared" si="23"/>
-        <v>0.12864000000000003</v>
+        <v>0.12768000000000002</v>
       </c>
       <c r="J361">
         <v>6.78</v>
@@ -17312,15 +17312,15 @@
       </c>
       <c r="G362" s="1">
         <f t="shared" si="21"/>
-        <v>75.599999999999994</v>
+        <v>74</v>
       </c>
       <c r="H362" s="1">
         <f t="shared" si="22"/>
-        <v>9.6442951345045653</v>
+        <v>9.3327630670261925</v>
       </c>
       <c r="I362" s="1">
         <f t="shared" si="23"/>
-        <v>9.9360000000000018E-2</v>
+        <v>9.8400000000000015E-2</v>
       </c>
       <c r="J362">
         <v>6.78</v>
@@ -17357,15 +17357,15 @@
       </c>
       <c r="G363" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>71.600000000000009</v>
       </c>
       <c r="H363" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>8.8839962332112261</v>
       </c>
       <c r="I363" s="1">
         <f t="shared" si="23"/>
-        <v>9.7919999999999993E-2</v>
+        <v>9.6960000000000032E-2</v>
       </c>
       <c r="J363">
         <v>6.78</v>
@@ -17402,15 +17402,15 @@
       </c>
       <c r="G364" s="1">
         <f t="shared" si="21"/>
-        <v>70.8</v>
+        <v>69.2</v>
       </c>
       <c r="H364" s="1">
         <f t="shared" si="22"/>
-        <v>8.7391564995047268</v>
+        <v>8.456326956989404</v>
       </c>
       <c r="I364" s="1">
         <f t="shared" si="23"/>
-        <v>9.648000000000001E-2</v>
+        <v>9.5519999999999994E-2</v>
       </c>
       <c r="J364">
         <v>6.78</v>
@@ -17447,15 +17447,15 @@
       </c>
       <c r="G365" s="1">
         <f t="shared" si="21"/>
-        <v>68.400000000000006</v>
+        <v>66.800000000000011</v>
       </c>
       <c r="H365" s="1">
         <f t="shared" si="22"/>
-        <v>8.3182499201059965</v>
+        <v>8.0485614709743096</v>
       </c>
       <c r="I365" s="1">
         <f t="shared" si="23"/>
-        <v>9.5040000000000013E-2</v>
+        <v>9.4080000000000011E-2</v>
       </c>
       <c r="J365">
         <v>6.78</v>
@@ -17492,15 +17492,15 @@
       </c>
       <c r="G366" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>71.2</v>
       </c>
       <c r="H366" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>8.8112863061414224</v>
       </c>
       <c r="I366" s="1">
         <f t="shared" si="23"/>
-        <v>7.8336000000000003E-2</v>
+        <v>7.7376E-2</v>
       </c>
       <c r="J366">
         <v>6.78</v>
@@ -17537,15 +17537,15 @@
       </c>
       <c r="G367" s="1">
         <f t="shared" si="21"/>
-        <v>70.8</v>
+        <v>68.8</v>
       </c>
       <c r="H367" s="1">
         <f t="shared" si="22"/>
-        <v>8.7391564995047268</v>
+        <v>8.38701473557939</v>
       </c>
       <c r="I367" s="1">
         <f t="shared" si="23"/>
-        <v>7.7184000000000016E-2</v>
+        <v>7.6224000000000014E-2</v>
       </c>
       <c r="J367">
         <v>6.78</v>
@@ -17582,15 +17582,15 @@
       </c>
       <c r="G368" s="1">
         <f t="shared" si="21"/>
-        <v>68.400000000000006</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="H368" s="1">
         <f t="shared" si="22"/>
-        <v>8.3182499201059965</v>
+        <v>7.9824568164254543</v>
       </c>
       <c r="I368" s="1">
         <f t="shared" si="23"/>
-        <v>7.6032000000000016E-2</v>
+        <v>7.5072000000000014E-2</v>
       </c>
       <c r="J368">
         <v>6.78</v>
@@ -17627,15 +17627,15 @@
       </c>
       <c r="G369" s="1">
         <f t="shared" si="21"/>
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H369" s="1">
         <f t="shared" si="22"/>
-        <v>7.9168692676056338</v>
+        <v>7.5965211039203471</v>
       </c>
       <c r="I369" s="1">
         <f t="shared" si="23"/>
-        <v>7.4880000000000016E-2</v>
+        <v>7.3920000000000013E-2</v>
       </c>
       <c r="J369">
         <v>6.78</v>
@@ -17672,15 +17672,15 @@
       </c>
       <c r="G370" s="1">
         <f t="shared" si="21"/>
-        <v>80.400000000000006</v>
+        <v>79.600000000000009</v>
       </c>
       <c r="H370" s="1">
         <f t="shared" si="22"/>
-        <v>10.642783189746096</v>
+        <v>10.469387455299206</v>
       </c>
       <c r="I370" s="1">
         <f t="shared" si="23"/>
-        <v>0.20448000000000002</v>
+        <v>0.20352000000000006</v>
       </c>
       <c r="J370">
         <v>6.78</v>
@@ -17717,15 +17717,15 @@
       </c>
       <c r="G371" s="1">
         <f t="shared" si="21"/>
-        <v>78</v>
+        <v>77.2</v>
       </c>
       <c r="H371" s="1">
         <f t="shared" si="22"/>
-        <v>10.131146510460249</v>
+        <v>9.9661842159569396</v>
       </c>
       <c r="I371" s="1">
         <f t="shared" si="23"/>
-        <v>0.20160000000000003</v>
+        <v>0.20063999999999999</v>
       </c>
       <c r="J371">
         <v>6.78</v>
@@ -17762,15 +17762,15 @@
       </c>
       <c r="G372" s="1">
         <f t="shared" si="21"/>
-        <v>75.599999999999994</v>
+        <v>74.8</v>
       </c>
       <c r="H372" s="1">
         <f t="shared" si="22"/>
-        <v>9.6442951345045653</v>
+        <v>9.4872605302206523</v>
       </c>
       <c r="I372" s="1">
         <f t="shared" si="23"/>
-        <v>0.19872000000000004</v>
+        <v>0.19776000000000002</v>
       </c>
       <c r="J372">
         <v>6.78</v>
@@ -17807,15 +17807,15 @@
       </c>
       <c r="G373" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="H373" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>9.0311793394358695</v>
       </c>
       <c r="I373" s="1">
         <f t="shared" si="23"/>
-        <v>0.19583999999999999</v>
+        <v>0.19488000000000003</v>
       </c>
       <c r="J373">
         <v>6.78</v>
@@ -17852,15 +17852,15 @@
       </c>
       <c r="G374" s="1">
         <f t="shared" si="21"/>
-        <v>78</v>
+        <v>76.8</v>
       </c>
       <c r="H374" s="1">
         <f t="shared" si="22"/>
-        <v>10.131146510460249</v>
+        <v>9.8847177874460144</v>
       </c>
       <c r="I374" s="1">
         <f t="shared" si="23"/>
-        <v>0.13440000000000002</v>
+        <v>0.13344000000000003</v>
       </c>
       <c r="J374">
         <v>6.78</v>
@@ -17897,15 +17897,15 @@
       </c>
       <c r="G375" s="1">
         <f t="shared" si="21"/>
-        <v>75.599999999999994</v>
+        <v>74.399999999999991</v>
       </c>
       <c r="H375" s="1">
         <f t="shared" si="22"/>
-        <v>9.6442951345045653</v>
+        <v>9.4096978367905351</v>
       </c>
       <c r="I375" s="1">
         <f t="shared" si="23"/>
-        <v>0.13248000000000001</v>
+        <v>0.13152</v>
       </c>
       <c r="J375">
         <v>6.78</v>
@@ -17942,15 +17942,15 @@
       </c>
       <c r="G376" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>72</v>
       </c>
       <c r="H376" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>8.9572919846547325</v>
       </c>
       <c r="I376" s="1">
         <f t="shared" si="23"/>
-        <v>0.13056000000000001</v>
+        <v>0.12960000000000002</v>
       </c>
       <c r="J376">
         <v>6.78</v>
@@ -17987,15 +17987,15 @@
       </c>
       <c r="G377" s="1">
         <f t="shared" si="21"/>
-        <v>70.8</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="H377" s="1">
         <f t="shared" si="22"/>
-        <v>8.7391564995047268</v>
+        <v>8.5261918628170097</v>
       </c>
       <c r="I377" s="1">
         <f t="shared" si="23"/>
-        <v>0.12864000000000003</v>
+        <v>0.12768000000000002</v>
       </c>
       <c r="J377">
         <v>6.78</v>
@@ -18032,15 +18032,15 @@
       </c>
       <c r="G378" s="1">
         <f t="shared" si="21"/>
-        <v>75.599999999999994</v>
+        <v>74</v>
       </c>
       <c r="H378" s="1">
         <f t="shared" si="22"/>
-        <v>9.6442951345045653</v>
+        <v>9.3327630670261925</v>
       </c>
       <c r="I378" s="1">
         <f t="shared" si="23"/>
-        <v>9.9360000000000018E-2</v>
+        <v>9.8400000000000015E-2</v>
       </c>
       <c r="J378">
         <v>6.78</v>
@@ -18077,15 +18077,15 @@
       </c>
       <c r="G379" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>71.600000000000009</v>
       </c>
       <c r="H379" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>8.8839962332112261</v>
       </c>
       <c r="I379" s="1">
         <f t="shared" si="23"/>
-        <v>9.7919999999999993E-2</v>
+        <v>9.6960000000000032E-2</v>
       </c>
       <c r="J379">
         <v>6.78</v>
@@ -18122,15 +18122,15 @@
       </c>
       <c r="G380" s="1">
         <f t="shared" si="21"/>
-        <v>70.8</v>
+        <v>69.2</v>
       </c>
       <c r="H380" s="1">
         <f t="shared" si="22"/>
-        <v>8.7391564995047268</v>
+        <v>8.456326956989404</v>
       </c>
       <c r="I380" s="1">
         <f t="shared" si="23"/>
-        <v>9.648000000000001E-2</v>
+        <v>9.5519999999999994E-2</v>
       </c>
       <c r="J380">
         <v>6.78</v>
@@ -18167,15 +18167,15 @@
       </c>
       <c r="G381" s="1">
         <f t="shared" si="21"/>
-        <v>68.400000000000006</v>
+        <v>66.800000000000011</v>
       </c>
       <c r="H381" s="1">
         <f t="shared" si="22"/>
-        <v>8.3182499201059965</v>
+        <v>8.0485614709743096</v>
       </c>
       <c r="I381" s="1">
         <f t="shared" si="23"/>
-        <v>9.5040000000000013E-2</v>
+        <v>9.4080000000000011E-2</v>
       </c>
       <c r="J381">
         <v>6.78</v>
@@ -18212,15 +18212,15 @@
       </c>
       <c r="G382" s="1">
         <f t="shared" si="21"/>
-        <v>73.2</v>
+        <v>71.2</v>
       </c>
       <c r="H382" s="1">
         <f t="shared" si="22"/>
-        <v>9.1807523574331302</v>
+        <v>8.8112863061414224</v>
       </c>
       <c r="I382" s="1">
         <f t="shared" si="23"/>
-        <v>7.8336000000000003E-2</v>
+        <v>7.7376E-2</v>
       </c>
       <c r="J382">
         <v>6.78</v>
@@ -18257,15 +18257,15 @@
       </c>
       <c r="G383" s="1">
         <f t="shared" si="21"/>
-        <v>70.8</v>
+        <v>68.8</v>
       </c>
       <c r="H383" s="1">
         <f t="shared" si="22"/>
-        <v>8.7391564995047268</v>
+        <v>8.38701473557939</v>
       </c>
       <c r="I383" s="1">
         <f t="shared" si="23"/>
-        <v>7.7184000000000016E-2</v>
+        <v>7.6224000000000014E-2</v>
       </c>
       <c r="J383">
         <v>6.78</v>
@@ -18302,15 +18302,15 @@
       </c>
       <c r="G384" s="1">
         <f t="shared" si="21"/>
-        <v>68.400000000000006</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="H384" s="1">
         <f t="shared" si="22"/>
-        <v>8.3182499201059965</v>
+        <v>7.9824568164254543</v>
       </c>
       <c r="I384" s="1">
         <f t="shared" si="23"/>
-        <v>7.6032000000000016E-2</v>
+        <v>7.5072000000000014E-2</v>
       </c>
       <c r="J384">
         <v>6.78</v>
@@ -18347,15 +18347,15 @@
       </c>
       <c r="G385" s="1">
         <f t="shared" si="21"/>
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H385" s="1">
         <f t="shared" si="22"/>
-        <v>7.9168692676056338</v>
+        <v>7.5965211039203471</v>
       </c>
       <c r="I385" s="1">
         <f t="shared" si="23"/>
-        <v>7.4880000000000016E-2</v>
+        <v>7.3920000000000013E-2</v>
       </c>
       <c r="J385">
         <v>6.78</v>
@@ -18392,15 +18392,15 @@
       </c>
       <c r="G386" s="1">
         <f t="shared" si="21"/>
-        <v>80.400000000000006</v>
+        <v>79.600000000000009</v>
       </c>
       <c r="H386" s="1">
         <f t="shared" si="22"/>
-        <v>10.642783189746096</v>
+        <v>10.469387455299206</v>
       </c>
       <c r="I386" s="1">
         <f t="shared" si="23"/>
-        <v>0.20448000000000002</v>
+        <v>0.20352000000000006</v>
       </c>
       <c r="J386">
         <v>6.78</v>
@@ -18436,16 +18436,16 @@
         <v>90</v>
       </c>
       <c r="G387" s="1">
-        <f t="shared" ref="G387:G401" si="25">F387-(A387-1)*2*(C387+E387)</f>
-        <v>78</v>
+        <f t="shared" ref="G387:G401" si="25">F387-(A387-1)*2*(C387+E387)-2*C387</f>
+        <v>77.2</v>
       </c>
       <c r="H387" s="1">
         <f t="shared" ref="H387:H401" si="26">2.34*0.000001257*(0.5*A387^2*(F387+G387))/(1+2.73*(F387-G387)/(F387+G387))*1000</f>
-        <v>10.131146510460249</v>
+        <v>9.9661842159569396</v>
       </c>
       <c r="I387" s="1">
         <f t="shared" ref="I387:I401" si="27">0.0000000168*4*0.5*(F387+G387)/(0.00007*C387)</f>
-        <v>0.20160000000000003</v>
+        <v>0.20063999999999999</v>
       </c>
       <c r="J387">
         <v>6.78</v>
@@ -18482,15 +18482,15 @@
       </c>
       <c r="G388" s="1">
         <f t="shared" si="25"/>
-        <v>75.599999999999994</v>
+        <v>74.8</v>
       </c>
       <c r="H388" s="1">
         <f t="shared" si="26"/>
-        <v>9.6442951345045653</v>
+        <v>9.4872605302206523</v>
       </c>
       <c r="I388" s="1">
         <f t="shared" si="27"/>
-        <v>0.19872000000000004</v>
+        <v>0.19776000000000002</v>
       </c>
       <c r="J388">
         <v>6.78</v>
@@ -18527,15 +18527,15 @@
       </c>
       <c r="G389" s="1">
         <f t="shared" si="25"/>
-        <v>73.2</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="H389" s="1">
         <f t="shared" si="26"/>
-        <v>9.1807523574331302</v>
+        <v>9.0311793394358695</v>
       </c>
       <c r="I389" s="1">
         <f t="shared" si="27"/>
-        <v>0.19583999999999999</v>
+        <v>0.19488000000000003</v>
       </c>
       <c r="J389">
         <v>6.78</v>
@@ -18572,15 +18572,15 @@
       </c>
       <c r="G390" s="1">
         <f t="shared" si="25"/>
-        <v>78</v>
+        <v>76.8</v>
       </c>
       <c r="H390" s="1">
         <f t="shared" si="26"/>
-        <v>10.131146510460249</v>
+        <v>9.8847177874460144</v>
       </c>
       <c r="I390" s="1">
         <f t="shared" si="27"/>
-        <v>0.13440000000000002</v>
+        <v>0.13344000000000003</v>
       </c>
       <c r="J390">
         <v>6.78</v>
@@ -18617,15 +18617,15 @@
       </c>
       <c r="G391" s="1">
         <f t="shared" si="25"/>
-        <v>75.599999999999994</v>
+        <v>74.399999999999991</v>
       </c>
       <c r="H391" s="1">
         <f t="shared" si="26"/>
-        <v>9.6442951345045653</v>
+        <v>9.4096978367905351</v>
       </c>
       <c r="I391" s="1">
         <f t="shared" si="27"/>
-        <v>0.13248000000000001</v>
+        <v>0.13152</v>
       </c>
       <c r="J391">
         <v>6.78</v>
@@ -18662,15 +18662,15 @@
       </c>
       <c r="G392" s="1">
         <f t="shared" si="25"/>
-        <v>73.2</v>
+        <v>72</v>
       </c>
       <c r="H392" s="1">
         <f t="shared" si="26"/>
-        <v>9.1807523574331302</v>
+        <v>8.9572919846547325</v>
       </c>
       <c r="I392" s="1">
         <f t="shared" si="27"/>
-        <v>0.13056000000000001</v>
+        <v>0.12960000000000002</v>
       </c>
       <c r="J392">
         <v>6.78</v>
@@ -18707,15 +18707,15 @@
       </c>
       <c r="G393" s="1">
         <f t="shared" si="25"/>
-        <v>70.8</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="H393" s="1">
         <f t="shared" si="26"/>
-        <v>8.7391564995047268</v>
+        <v>8.5261918628170097</v>
       </c>
       <c r="I393" s="1">
         <f t="shared" si="27"/>
-        <v>0.12864000000000003</v>
+        <v>0.12768000000000002</v>
       </c>
       <c r="J393">
         <v>6.78</v>
@@ -18752,15 +18752,15 @@
       </c>
       <c r="G394" s="1">
         <f t="shared" si="25"/>
-        <v>75.599999999999994</v>
+        <v>74</v>
       </c>
       <c r="H394" s="1">
         <f t="shared" si="26"/>
-        <v>9.6442951345045653</v>
+        <v>9.3327630670261925</v>
       </c>
       <c r="I394" s="1">
         <f t="shared" si="27"/>
-        <v>9.9360000000000018E-2</v>
+        <v>9.8400000000000015E-2</v>
       </c>
       <c r="J394">
         <v>6.78</v>
@@ -18797,15 +18797,15 @@
       </c>
       <c r="G395" s="1">
         <f t="shared" si="25"/>
-        <v>73.2</v>
+        <v>71.600000000000009</v>
       </c>
       <c r="H395" s="1">
         <f t="shared" si="26"/>
-        <v>9.1807523574331302</v>
+        <v>8.8839962332112261</v>
       </c>
       <c r="I395" s="1">
         <f t="shared" si="27"/>
-        <v>9.7919999999999993E-2</v>
+        <v>9.6960000000000032E-2</v>
       </c>
       <c r="J395">
         <v>6.78</v>
@@ -18842,15 +18842,15 @@
       </c>
       <c r="G396" s="1">
         <f t="shared" si="25"/>
-        <v>70.8</v>
+        <v>69.2</v>
       </c>
       <c r="H396" s="1">
         <f t="shared" si="26"/>
-        <v>8.7391564995047268</v>
+        <v>8.456326956989404</v>
       </c>
       <c r="I396" s="1">
         <f t="shared" si="27"/>
-        <v>9.648000000000001E-2</v>
+        <v>9.5519999999999994E-2</v>
       </c>
       <c r="J396">
         <v>6.78</v>
@@ -18887,15 +18887,15 @@
       </c>
       <c r="G397" s="1">
         <f t="shared" si="25"/>
-        <v>68.400000000000006</v>
+        <v>66.800000000000011</v>
       </c>
       <c r="H397" s="1">
         <f t="shared" si="26"/>
-        <v>8.3182499201059965</v>
+        <v>8.0485614709743096</v>
       </c>
       <c r="I397" s="1">
         <f t="shared" si="27"/>
-        <v>9.5040000000000013E-2</v>
+        <v>9.4080000000000011E-2</v>
       </c>
       <c r="J397">
         <v>6.78</v>
@@ -18932,15 +18932,15 @@
       </c>
       <c r="G398" s="1">
         <f t="shared" si="25"/>
-        <v>73.2</v>
+        <v>71.2</v>
       </c>
       <c r="H398" s="1">
         <f t="shared" si="26"/>
-        <v>9.1807523574331302</v>
+        <v>8.8112863061414224</v>
       </c>
       <c r="I398" s="1">
         <f t="shared" si="27"/>
-        <v>7.8336000000000003E-2</v>
+        <v>7.7376E-2</v>
       </c>
       <c r="J398">
         <v>6.78</v>
@@ -18977,15 +18977,15 @@
       </c>
       <c r="G399" s="1">
         <f t="shared" si="25"/>
-        <v>70.8</v>
+        <v>68.8</v>
       </c>
       <c r="H399" s="1">
         <f t="shared" si="26"/>
-        <v>8.7391564995047268</v>
+        <v>8.38701473557939</v>
       </c>
       <c r="I399" s="1">
         <f t="shared" si="27"/>
-        <v>7.7184000000000016E-2</v>
+        <v>7.6224000000000014E-2</v>
       </c>
       <c r="J399">
         <v>6.78</v>
@@ -19022,15 +19022,15 @@
       </c>
       <c r="G400" s="1">
         <f t="shared" si="25"/>
-        <v>68.400000000000006</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="H400" s="1">
         <f t="shared" si="26"/>
-        <v>8.3182499201059965</v>
+        <v>7.9824568164254543</v>
       </c>
       <c r="I400" s="1">
         <f t="shared" si="27"/>
-        <v>7.6032000000000016E-2</v>
+        <v>7.5072000000000014E-2</v>
       </c>
       <c r="J400">
         <v>6.78</v>
@@ -19067,15 +19067,15 @@
       </c>
       <c r="G401" s="1">
         <f t="shared" si="25"/>
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H401" s="1">
         <f t="shared" si="26"/>
-        <v>7.9168692676056338</v>
+        <v>7.5965211039203471</v>
       </c>
       <c r="I401" s="1">
         <f t="shared" si="27"/>
-        <v>7.4880000000000016E-2</v>
+        <v>7.3920000000000013E-2</v>
       </c>
       <c r="J401">
         <v>6.78</v>
@@ -19093,11 +19093,11 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A2:M401">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$I2*0.9&gt;$L2</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>$H2*1.05&lt;$K2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>$I2*0.9&gt;$L2</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
